--- a/data/external_sources/retail_network_sales.xlsx
+++ b/data/external_sources/retail_network_sales.xlsx
@@ -5409,7 +5409,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:O25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5452,98 +5452,92 @@
         <v>Возвраты шт</v>
       </c>
       <c r="N1" t="str">
-        <v>Юр Лицо</v>
+        <v>1</v>
       </c>
       <c r="O1" t="str">
-        <v>Дата</v>
-      </c>
-      <c r="P1" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Наименование</v>
+        <v>"Кровавый" пилинг для лица маркировки "Алтэя"</v>
       </c>
       <c r="B2" t="str">
-        <v>Номенклатура</v>
+        <v>99000076205</v>
       </c>
       <c r="C2" t="str">
-        <v>Артикул</v>
+        <v>krovavii_piling_30ml</v>
       </c>
       <c r="D2" t="str">
-        <v>Штрихкод</v>
+        <v>4670020498208</v>
       </c>
       <c r="E2" t="str">
-        <v>Заказано руб</v>
+        <v>8684</v>
       </c>
       <c r="F2" t="str">
-        <v>Доставлено руб</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>В пути руб</v>
+        <v>8684</v>
       </c>
       <c r="H2" t="str">
-        <v>Отменено руб</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
-        <v>Заказано шт</v>
+        <v>13</v>
       </c>
       <c r="J2" t="str">
-        <v>Доставлено шт</v>
+        <v>0</v>
       </c>
       <c r="K2" t="str">
-        <v>В пути шт</v>
+        <v>13</v>
       </c>
       <c r="L2" t="str">
-        <v>Отменено шт</v>
+        <v>0</v>
       </c>
       <c r="M2" t="str">
-        <v>Возвраты шт</v>
+        <v>0</v>
       </c>
       <c r="N2" t="str">
         <v>1</v>
       </c>
       <c r="O2" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Крем для лица с ретинолом 0.5, сыворотка от морщин и пигментных пятен, Алтея, Ретидерм, 50 мл</v>
+        <v>Гель для проблемной кожи лица и тела, с маркировками Алтея</v>
       </c>
       <c r="B3" t="str">
-        <v>99000076216</v>
+        <v>99000114730</v>
       </c>
       <c r="C3" t="str">
-        <v>retiderm_50ml</v>
+        <v>gel_antiakne_20ml_v2</v>
       </c>
       <c r="D3" t="str">
-        <v>4.61017E+12</v>
+        <v>4660417420110</v>
       </c>
       <c r="E3" t="str">
-        <v>11918</v>
+        <v>7928</v>
       </c>
       <c r="F3" t="str">
         <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>11918</v>
+        <v>7928</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="J3" t="str">
         <v>0</v>
       </c>
       <c r="K3" t="str">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="L3" t="str">
         <v>0</v>
@@ -5555,48 +5549,45 @@
         <v>1</v>
       </c>
       <c r="O3" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P3" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>"Кровавый" пилинг для лица маркировки "Алтэя"</v>
+        <v>Продукция косметическая для ухода за кожей, в том числе в наборах: Маска для проблемной кожи лица м</v>
       </c>
       <c r="B4" t="str">
-        <v>99000076205</v>
+        <v>99000114727</v>
       </c>
       <c r="C4" t="str">
-        <v>krovavii_piling_30ml</v>
+        <v>maska_dlya_lica_100m</v>
       </c>
       <c r="D4" t="str">
-        <v>4.67002E+12</v>
+        <v>4670020498741</v>
       </c>
       <c r="E4" t="str">
-        <v>10181</v>
+        <v>6213</v>
       </c>
       <c r="F4" t="str">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>9597</v>
+        <v>5274</v>
       </c>
       <c r="H4" t="str">
-        <v>0</v>
+        <v>939</v>
       </c>
       <c r="I4" t="str">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="str">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L4" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="str">
         <v>0</v>
@@ -5605,45 +5596,42 @@
         <v>1</v>
       </c>
       <c r="O4" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P4" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Гель для проблемной кожи лица и тела, с маркировками Алтея</v>
+        <v>Крем для лица с ретинолом 0.5, сыворотка от морщин и пигментных пятен, Алтея, Ретидерм, 50 мл</v>
       </c>
       <c r="B5" t="str">
-        <v>99000114730</v>
+        <v>99000076216</v>
       </c>
       <c r="C5" t="str">
-        <v>gel_antiakne_20ml_v2</v>
+        <v>retiderm_50ml</v>
       </c>
       <c r="D5" t="str">
-        <v>4.66042E+12</v>
+        <v>4610172186219</v>
       </c>
       <c r="E5" t="str">
-        <v>9842</v>
+        <v>5944</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>498</v>
       </c>
       <c r="G5" t="str">
-        <v>9842</v>
+        <v>5446</v>
       </c>
       <c r="H5" t="str">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J5" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="str">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L5" t="str">
         <v>0</v>
@@ -5655,45 +5643,42 @@
         <v>1</v>
       </c>
       <c r="O5" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P5" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз, 30мл</v>
+        <v>Крем для волос Упругий завиток, 300 мл</v>
       </c>
       <c r="B6" t="str">
-        <v>99000154005</v>
+        <v>99000114726</v>
       </c>
       <c r="C6" t="str">
-        <v>retinol_boost_krem_d</v>
+        <v>curly_method_300ml</v>
       </c>
       <c r="D6" t="str">
-        <v>4.66042E+12</v>
+        <v>4603320465441</v>
       </c>
       <c r="E6" t="str">
-        <v>8297</v>
+        <v>5815</v>
       </c>
       <c r="F6" t="str">
         <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>8297</v>
+        <v>5815</v>
       </c>
       <c r="H6" t="str">
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J6" t="str">
         <v>0</v>
       </c>
       <c r="K6" t="str">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L6" t="str">
         <v>0</v>
@@ -5705,33 +5690,30 @@
         <v>1</v>
       </c>
       <c r="O6" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P6" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Крем для волос Упругий завиток, 300 мл</v>
+        <v>Пенка для укладки волос</v>
       </c>
       <c r="B7" t="str">
-        <v>99000114726</v>
+        <v>99000125266</v>
       </c>
       <c r="C7" t="str">
-        <v>curly_method_300ml</v>
+        <v>penka_kudryavii_meto</v>
       </c>
       <c r="D7" t="str">
-        <v>4.60332E+12</v>
+        <v>4670020498611</v>
       </c>
       <c r="E7" t="str">
-        <v>6195</v>
+        <v>4831</v>
       </c>
       <c r="F7" t="str">
         <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>6195</v>
+        <v>4831</v>
       </c>
       <c r="H7" t="str">
         <v>0</v>
@@ -5755,48 +5737,45 @@
         <v>1</v>
       </c>
       <c r="O7" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P7" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>РЕТИНАЙТ сыворотка для лица 30 мл</v>
+        <v>Крем-шелк для сухой кожи ног</v>
       </c>
       <c r="B8" t="str">
-        <v>99000125142</v>
+        <v>99000076225</v>
       </c>
       <c r="C8" t="str">
-        <v>retinait_syvorotka_1</v>
+        <v>kremshelk_100ml</v>
       </c>
       <c r="D8" t="str">
-        <v>4.60332E+12</v>
+        <v>4670020498437</v>
       </c>
       <c r="E8" t="str">
-        <v>5736</v>
+        <v>3776</v>
       </c>
       <c r="F8" t="str">
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>4096</v>
+        <v>3776</v>
       </c>
       <c r="H8" t="str">
-        <v>1640</v>
+        <v>0</v>
       </c>
       <c r="I8" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8" t="str">
         <v>0</v>
       </c>
       <c r="K8" t="str">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L8" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="str">
         <v>0</v>
@@ -5805,10 +5784,7 @@
         <v>1</v>
       </c>
       <c r="O8" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P8" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="9">
@@ -5822,28 +5798,28 @@
         <v>retinait_krem_1_50ml</v>
       </c>
       <c r="D9" t="str">
-        <v>4.66042E+12</v>
+        <v>4660417421605</v>
       </c>
       <c r="E9" t="str">
-        <v>5116</v>
+        <v>3075</v>
       </c>
       <c r="F9" t="str">
-        <v>1025</v>
+        <v>0</v>
       </c>
       <c r="G9" t="str">
-        <v>4091</v>
+        <v>3075</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
       </c>
       <c r="I9" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9" t="str">
         <v>0</v>
@@ -5855,45 +5831,42 @@
         <v>1</v>
       </c>
       <c r="O9" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P9" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Пенка для укладки волос</v>
+        <v>Крем от растяжек, Алтея, 200 мл</v>
       </c>
       <c r="B10" t="str">
-        <v>99000125266</v>
+        <v>99000114731</v>
       </c>
       <c r="C10" t="str">
-        <v>penka_kudryavii_meto</v>
+        <v>krem_ot_rastyazhek</v>
       </c>
       <c r="D10" t="str">
-        <v>4.67002E+12</v>
+        <v>4670020497898</v>
       </c>
       <c r="E10" t="str">
-        <v>4759</v>
+        <v>2960</v>
       </c>
       <c r="F10" t="str">
         <v>0</v>
       </c>
       <c r="G10" t="str">
-        <v>4759</v>
+        <v>2960</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" t="str">
         <v>0</v>
       </c>
       <c r="K10" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10" t="str">
         <v>0</v>
@@ -5905,33 +5878,30 @@
         <v>1</v>
       </c>
       <c r="O10" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P10" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Крем-шелк для сухой кожи ног</v>
+        <v>Спрей-сыворотка для волос маркировки Алтея</v>
       </c>
       <c r="B11" t="str">
-        <v>99000076225</v>
+        <v>99000076226</v>
       </c>
       <c r="C11" t="str">
-        <v>kremshelk_100ml</v>
+        <v>termo_sprei_200ml</v>
       </c>
       <c r="D11" t="str">
-        <v>4.67002E+12</v>
+        <v>4670020497980</v>
       </c>
       <c r="E11" t="str">
-        <v>3386</v>
+        <v>2614</v>
       </c>
       <c r="F11" t="str">
         <v>0</v>
       </c>
       <c r="G11" t="str">
-        <v>3386</v>
+        <v>2614</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
@@ -5955,10 +5925,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P11" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="12">
@@ -5972,16 +5939,16 @@
         <v>spicul_gel_mask_75ml</v>
       </c>
       <c r="D12" t="str">
-        <v>4.66042E+12</v>
+        <v>4660417421858</v>
       </c>
       <c r="E12" t="str">
-        <v>3135</v>
+        <v>2523</v>
       </c>
       <c r="F12" t="str">
         <v>0</v>
       </c>
       <c r="G12" t="str">
-        <v>3135</v>
+        <v>2523</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
@@ -6005,45 +5972,42 @@
         <v>1</v>
       </c>
       <c r="O12" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P12" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея, 50 мл</v>
+        <v>Средство косметическое: Воск для волос торговой марки: «Алтея» 15гр</v>
       </c>
       <c r="B13" t="str">
-        <v>99000176496</v>
+        <v>99000131672</v>
       </c>
       <c r="C13" t="str">
-        <v>retinait_krem_1_5_50</v>
+        <v>vosk_stik_15ml</v>
       </c>
       <c r="D13" t="str">
-        <v>4.66042E+12</v>
+        <v>4670207150196</v>
       </c>
       <c r="E13" t="str">
-        <v>2319</v>
+        <v>2080</v>
       </c>
       <c r="F13" t="str">
         <v>0</v>
       </c>
       <c r="G13" t="str">
-        <v>2319</v>
+        <v>2080</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13" t="str">
         <v>0</v>
       </c>
       <c r="K13" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L13" t="str">
         <v>0</v>
@@ -6055,45 +6019,42 @@
         <v>1</v>
       </c>
       <c r="O13" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P13" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Крем от растяжек, Алтея, 200 мл</v>
+        <v>Спрей для роста волос торговой марки Алтея</v>
       </c>
       <c r="B14" t="str">
-        <v>99000114731</v>
+        <v>99000114724</v>
       </c>
       <c r="C14" t="str">
-        <v>krem_ot_rastyazhek</v>
+        <v>sprei_buster_100ml</v>
       </c>
       <c r="D14" t="str">
-        <v>4.67002E+12</v>
+        <v>4603320465359</v>
       </c>
       <c r="E14" t="str">
-        <v>1728</v>
+        <v>1802</v>
       </c>
       <c r="F14" t="str">
         <v>0</v>
       </c>
       <c r="G14" t="str">
-        <v>1728</v>
+        <v>1802</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
       </c>
       <c r="I14" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" t="str">
         <v>0</v>
       </c>
       <c r="K14" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" t="str">
         <v>0</v>
@@ -6105,45 +6066,42 @@
         <v>1</v>
       </c>
       <c r="O14" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P14" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Алтея Сыворотка для лица сыворотка для лица с ниацинамидом для лица антивозрастная, от пигментных пя</v>
+        <v>Ламеллярный крем для рук с мочевиной, увлажняющий и питательный с маслом кокоса, Алтея, 75 мл</v>
       </c>
       <c r="B15" t="str">
-        <v>99000182844</v>
+        <v>99000114729</v>
       </c>
       <c r="C15" t="str">
-        <v>syvorotka_dlya_lica_</v>
+        <v>krem_dlya_ruk_75ml</v>
       </c>
       <c r="D15" t="str">
-        <v>4.60331E+12</v>
+        <v>4660417421452</v>
       </c>
       <c r="E15" t="str">
-        <v>1698</v>
+        <v>1545</v>
       </c>
       <c r="F15" t="str">
         <v>0</v>
       </c>
       <c r="G15" t="str">
-        <v>1698</v>
+        <v>1545</v>
       </c>
       <c r="H15" t="str">
         <v>0</v>
       </c>
       <c r="I15" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" t="str">
         <v>0</v>
       </c>
       <c r="K15" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L15" t="str">
         <v>0</v>
@@ -6155,45 +6113,42 @@
         <v>1</v>
       </c>
       <c r="O15" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P15" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Ретинайт 0,5 экспресс-омоложение Anti-Age Липосомальный комплекс ретинола 0,5 + Ниацинамид 50 мл</v>
+        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз, 30мл</v>
       </c>
       <c r="B16" t="str">
-        <v>99000131675</v>
+        <v>99000154005</v>
       </c>
       <c r="C16" t="str">
-        <v>retinait_krem_05_50m</v>
+        <v>retinol_boost_krem_d</v>
       </c>
       <c r="D16" t="str">
-        <v>4.66042E+12</v>
+        <v>4660417421636</v>
       </c>
       <c r="E16" t="str">
-        <v>1289</v>
+        <v>893</v>
       </c>
       <c r="F16" t="str">
         <v>0</v>
       </c>
       <c r="G16" t="str">
-        <v>1289</v>
+        <v>893</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
       </c>
       <c r="I16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="str">
         <v>0</v>
       </c>
       <c r="K16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" t="str">
         <v>0</v>
@@ -6205,45 +6160,42 @@
         <v>1</v>
       </c>
       <c r="O16" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P16" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Спрей для роста волос торговой марки Алтея</v>
+        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея</v>
       </c>
       <c r="B17" t="str">
-        <v>99000114724</v>
+        <v>99000124418</v>
       </c>
       <c r="C17" t="str">
-        <v>sprei_buster_100ml</v>
+        <v>retinait_krem_025_50</v>
       </c>
       <c r="D17" t="str">
-        <v>4.60332E+12</v>
+        <v>4660417421599</v>
       </c>
       <c r="E17" t="str">
-        <v>1280</v>
+        <v>844</v>
       </c>
       <c r="F17" t="str">
         <v>0</v>
       </c>
       <c r="G17" t="str">
-        <v>1280</v>
+        <v>844</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
       </c>
       <c r="I17" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="str">
         <v>0</v>
       </c>
       <c r="K17" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="str">
         <v>0</v>
@@ -6255,42 +6207,39 @@
         <v>1</v>
       </c>
       <c r="O17" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P17" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Спрей-сыворотка для волос маркировки Алтея</v>
+        <v>Крем для лица spf 50 с защитой UVA/UVB, торговой марки Алтея</v>
       </c>
       <c r="B18" t="str">
-        <v>99000076226</v>
+        <v>99000163832</v>
       </c>
       <c r="C18" t="str">
-        <v>termo_sprei_200ml</v>
+        <v>krem_spf50_50ml</v>
       </c>
       <c r="D18" t="str">
-        <v>4.67002E+12</v>
+        <v>4660417421766</v>
       </c>
       <c r="E18" t="str">
-        <v>1220</v>
+        <v>800</v>
       </c>
       <c r="F18" t="str">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="G18" t="str">
-        <v>604</v>
+        <v>800</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
       </c>
       <c r="I18" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="str">
         <v>1</v>
@@ -6305,33 +6254,30 @@
         <v>1</v>
       </c>
       <c r="O18" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P18" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Cыворотка SPICULBOOST торговой марки Алтея, 30 мл</v>
+        <v>Крем специального назначения «Псоридонт» 50 мл</v>
       </c>
       <c r="B19" t="str">
-        <v>99000179436</v>
+        <v>99000125141</v>
       </c>
       <c r="C19" t="str">
-        <v>spiculboost_30ml</v>
+        <v>psoral_50ml</v>
       </c>
       <c r="D19" t="str">
-        <v>4.63045E+12</v>
+        <v>4660417421087</v>
       </c>
       <c r="E19" t="str">
-        <v>1131</v>
+        <v>760</v>
       </c>
       <c r="F19" t="str">
         <v>0</v>
       </c>
       <c r="G19" t="str">
-        <v>1131</v>
+        <v>760</v>
       </c>
       <c r="H19" t="str">
         <v>0</v>
@@ -6355,45 +6301,42 @@
         <v>1</v>
       </c>
       <c r="O19" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P19" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Средство косметическое: Воск для волос торговой марки: «Алтея» 15гр</v>
+        <v>Ретинайт 0,5 экспресс-омоложение Anti-Age Липосомальный комплекс ретинола 0,5 + Ниацинамид 50 мл</v>
       </c>
       <c r="B20" t="str">
-        <v>99000131672</v>
+        <v>99000131675</v>
       </c>
       <c r="C20" t="str">
-        <v>vosk_stik_15ml</v>
+        <v>retinait_krem_05_50m</v>
       </c>
       <c r="D20" t="str">
-        <v>4.67021E+12</v>
+        <v>4660417421759</v>
       </c>
       <c r="E20" t="str">
-        <v>975</v>
+        <v>744</v>
       </c>
       <c r="F20" t="str">
         <v>0</v>
       </c>
       <c r="G20" t="str">
-        <v>975</v>
+        <v>744</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
       </c>
       <c r="I20" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="str">
         <v>0</v>
       </c>
       <c r="K20" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="str">
         <v>0</v>
@@ -6405,45 +6348,42 @@
         <v>1</v>
       </c>
       <c r="O20" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P20" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Ламеллярный крем для рук с мочевиной, увлажняющий и питательный с маслом кокоса, Алтея, 75 мл</v>
+        <v>Средство косметическое для ухода за волосами: маска для волос восстанавливающая с авокадо и маслом о</v>
       </c>
       <c r="B21" t="str">
-        <v>99000114729</v>
+        <v>99000076210</v>
       </c>
       <c r="C21" t="str">
-        <v>krem_dlya_ruk_75ml</v>
+        <v>maska-batter_250ml</v>
       </c>
       <c r="D21" t="str">
-        <v>4.66042E+12</v>
+        <v>4670020497546</v>
       </c>
       <c r="E21" t="str">
-        <v>928</v>
+        <v>657</v>
       </c>
       <c r="F21" t="str">
         <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>928</v>
+        <v>657</v>
       </c>
       <c r="H21" t="str">
         <v>0</v>
       </c>
       <c r="I21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="str">
         <v>0</v>
       </c>
       <c r="K21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" t="str">
         <v>0</v>
@@ -6455,33 +6395,30 @@
         <v>1</v>
       </c>
       <c r="O21" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P21" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Крем для век пробуждающий маркировки «Алтэя»</v>
+        <v>Средство косметическое профессиональное: маска разогревающая для роста волос торговой марки: Алтея.</v>
       </c>
       <c r="B22" t="str">
-        <v>99000125267</v>
+        <v>99000076208</v>
       </c>
       <c r="C22" t="str">
-        <v>krem_dlya_vek_30ml</v>
+        <v>maska-batter_dlya_ro</v>
       </c>
       <c r="D22" t="str">
-        <v>4.67002E+12</v>
+        <v>4603320465366</v>
       </c>
       <c r="E22" t="str">
-        <v>840</v>
+        <v>650</v>
       </c>
       <c r="F22" t="str">
         <v>0</v>
       </c>
       <c r="G22" t="str">
-        <v>840</v>
+        <v>650</v>
       </c>
       <c r="H22" t="str">
         <v>0</v>
@@ -6505,33 +6442,30 @@
         <v>1</v>
       </c>
       <c r="O22" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P22" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Средство косметическое для ухода за волосами: масло для бороды, маркировка: Алтея.</v>
+        <v>Шампунь от перхоти лечебный с климбазолом Алтея, 250мл</v>
       </c>
       <c r="B23" t="str">
-        <v>99000076215</v>
+        <v>99000076206</v>
       </c>
       <c r="C23" t="str">
-        <v>maslo_dlya_borodi_50</v>
+        <v>shampun_protiv_perho</v>
       </c>
       <c r="D23" t="str">
-        <v>4.61017E+12</v>
+        <v>4670020496679</v>
       </c>
       <c r="E23" t="str">
-        <v>718</v>
+        <v>650</v>
       </c>
       <c r="F23" t="str">
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>718</v>
+        <v>650</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -6555,33 +6489,30 @@
         <v>1</v>
       </c>
       <c r="O23" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P23" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Шампунь для роста волос, от выпадения волос профессиональный, Алтея, 250 мл</v>
+        <v>Средство косметическое для ухода за волосами: масло для бороды, маркировка: Алтея.</v>
       </c>
       <c r="B24" t="str">
-        <v>99000076213</v>
+        <v>99000076215</v>
       </c>
       <c r="C24" t="str">
-        <v>shampun_dlya_rosta_2</v>
+        <v>maslo_dlya_borodi_50</v>
       </c>
       <c r="D24" t="str">
-        <v>4.67002E+12</v>
+        <v>4610172186882</v>
       </c>
       <c r="E24" t="str">
-        <v>695</v>
+        <v>569</v>
       </c>
       <c r="F24" t="str">
         <v>0</v>
       </c>
       <c r="G24" t="str">
-        <v>695</v>
+        <v>569</v>
       </c>
       <c r="H24" t="str">
         <v>0</v>
@@ -6605,33 +6536,30 @@
         <v>1</v>
       </c>
       <c r="O24" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P24" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Шампунь от перхоти лечебный с климбазолом Алтея, 250мл</v>
+        <v>Шампунь для роста волос, от выпадения волос профессиональный, Алтея, 250 мл</v>
       </c>
       <c r="B25" t="str">
-        <v>99000076206</v>
+        <v>99000076213</v>
       </c>
       <c r="C25" t="str">
-        <v>shampun_protiv_perho</v>
+        <v>shampun_dlya_rosta_2</v>
       </c>
       <c r="D25" t="str">
-        <v>4.67002E+12</v>
+        <v>4670020496747</v>
       </c>
       <c r="E25" t="str">
-        <v>680</v>
+        <v>461</v>
       </c>
       <c r="F25" t="str">
         <v>0</v>
       </c>
       <c r="G25" t="str">
-        <v>680</v>
+        <v>461</v>
       </c>
       <c r="H25" t="str">
         <v>0</v>
@@ -6655,172 +6583,19 @@
         <v>1</v>
       </c>
       <c r="O25" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Сыворотка для лица с гиалуроновой кислотой маркировки "Алтэя"</v>
-      </c>
-      <c r="B26" t="str">
-        <v>99000076209</v>
-      </c>
-      <c r="C26" t="str">
-        <v>syvorotka_guk_30ml</v>
-      </c>
-      <c r="D26" t="str">
-        <v>4.67002E+12</v>
-      </c>
-      <c r="E26" t="str">
-        <v>671</v>
-      </c>
-      <c r="F26" t="str">
-        <v>0</v>
-      </c>
-      <c r="G26" t="str">
-        <v>671</v>
-      </c>
-      <c r="H26" t="str">
-        <v>0</v>
-      </c>
-      <c r="I26" t="str">
-        <v>1</v>
-      </c>
-      <c r="J26" t="str">
-        <v>0</v>
-      </c>
-      <c r="K26" t="str">
-        <v>1</v>
-      </c>
-      <c r="L26" t="str">
-        <v>0</v>
-      </c>
-      <c r="M26" t="str">
-        <v>0</v>
-      </c>
-      <c r="N26" t="str">
-        <v>1</v>
-      </c>
-      <c r="O26" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Средства косметические для ухода за бровями: сыворотка для бровей и ресниц, с маркировкой "Алтея", 6</v>
-      </c>
-      <c r="B27" t="str">
-        <v>99000132524</v>
-      </c>
-      <c r="C27" t="str">
-        <v>syvorotka_dlya_rosta</v>
-      </c>
-      <c r="D27" t="str">
-        <v>4.65674E+12</v>
-      </c>
-      <c r="E27" t="str">
-        <v>488</v>
-      </c>
-      <c r="F27" t="str">
-        <v>0</v>
-      </c>
-      <c r="G27" t="str">
-        <v>488</v>
-      </c>
-      <c r="H27" t="str">
-        <v>0</v>
-      </c>
-      <c r="I27" t="str">
-        <v>1</v>
-      </c>
-      <c r="J27" t="str">
-        <v>0</v>
-      </c>
-      <c r="K27" t="str">
-        <v>1</v>
-      </c>
-      <c r="L27" t="str">
-        <v>0</v>
-      </c>
-      <c r="M27" t="str">
-        <v>0</v>
-      </c>
-      <c r="N27" t="str">
-        <v>1</v>
-      </c>
-      <c r="O27" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Гель для бровей с коллагеном и эластином, фиксация на 24 часа, Алтея, 5 мл</v>
-      </c>
-      <c r="B28" t="str">
-        <v>99000114725</v>
-      </c>
-      <c r="C28" t="str">
-        <v>gel_brows_5ml</v>
-      </c>
-      <c r="D28" t="str">
-        <v>4.67657E+12</v>
-      </c>
-      <c r="E28" t="str">
-        <v>400</v>
-      </c>
-      <c r="F28" t="str">
-        <v>0</v>
-      </c>
-      <c r="G28" t="str">
-        <v>400</v>
-      </c>
-      <c r="H28" t="str">
-        <v>0</v>
-      </c>
-      <c r="I28" t="str">
-        <v>1</v>
-      </c>
-      <c r="J28" t="str">
-        <v>0</v>
-      </c>
-      <c r="K28" t="str">
-        <v>1</v>
-      </c>
-      <c r="L28" t="str">
-        <v>0</v>
-      </c>
-      <c r="M28" t="str">
-        <v>0</v>
-      </c>
-      <c r="N28" t="str">
-        <v>1</v>
-      </c>
-      <c r="O28" t="str">
-        <v>46226</v>
-      </c>
-      <c r="P28" t="str">
-        <v/>
+        <v>26.7.2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6851,435 +6626,225 @@
         <v>Seller SKU ID</v>
       </c>
       <c r="J1" t="str">
-        <v>Юр Лицо</v>
+        <v>1</v>
       </c>
       <c r="K1" t="str">
-        <v>Дата</v>
+        <v>24.07.2026</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SKU</v>
+        <v>АЛТЕЯ-PINKREM</v>
       </c>
       <c r="B2" t="str">
-        <v>Наименование</v>
+        <v>Крем для лица увлажняющий питательный с ниацинамидом Алтея 50 мл</v>
       </c>
       <c r="C2" t="str">
-        <v>Категория</v>
+        <v>1</v>
       </c>
       <c r="D2" t="str">
-        <v>Количество</v>
+        <v>0</v>
       </c>
       <c r="E2" t="str">
-        <v>Выручка (руб.)</v>
+        <v>437,95</v>
       </c>
       <c r="F2" t="str">
-        <v>Себестоимость (руб.)</v>
+        <v>147,85</v>
       </c>
       <c r="G2" t="str">
-        <v>Выручка с вычетом комиссии (руб.)</v>
+        <v>315,32</v>
       </c>
       <c r="H2" t="str">
-        <v>Комиссия маркетплейса(руб.)</v>
+        <v>122,63</v>
       </c>
       <c r="I2" t="str">
-        <v>Seller SKU ID</v>
+        <v>pink_pepper_50ml</v>
       </c>
       <c r="J2" t="str">
         <v>1</v>
       </c>
       <c r="K2" t="str">
-        <v>46226</v>
+        <v>24.07.2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>АЛТЕЯ-MASKARS</v>
+        <v>АЛТЕЯ-CUDRKRM</v>
       </c>
       <c r="B3" t="str">
-        <v>Маска для роста волос с перцем Алтея 500 мл</v>
+        <v>Крем для кудрявых и вьющихся волос Алтея 300 мл</v>
       </c>
       <c r="C3" t="str">
-        <v>Маски</v>
+        <v>3</v>
       </c>
       <c r="D3" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="str">
-        <v>384</v>
+        <v>1926</v>
       </c>
       <c r="F3" t="str">
-        <v>136.15</v>
+        <v>396</v>
       </c>
       <c r="G3" t="str">
-        <v>291.84</v>
+        <v>1386,72</v>
       </c>
       <c r="H3" t="str">
-        <v>92.16</v>
+        <v>539,28</v>
       </c>
       <c r="I3" t="str">
-        <v>maska-batter_dlya_rosta_500ml</v>
+        <v>curly_method_300ml</v>
       </c>
       <c r="J3" t="str">
         <v>1</v>
       </c>
       <c r="K3" t="str">
-        <v>46226</v>
+        <v>24.07.2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>АЛТЕЯ-CUDRKRM</v>
+        <v>АЛТЕЯ-ENZIMPD</v>
       </c>
       <c r="B4" t="str">
-        <v>Крем для кудрявых и вьющихся волос Алтея 300 мл</v>
+        <v>Энзимная пудра для умывания тела и лица от прыщей Алтея 80г</v>
       </c>
       <c r="C4" t="str">
-        <v>Кремы</v>
+        <v>1</v>
       </c>
       <c r="D4" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="str">
-        <v>642</v>
+        <v>431,3</v>
       </c>
       <c r="F4" t="str">
-        <v>132</v>
+        <v>114,6</v>
       </c>
       <c r="G4" t="str">
-        <v>462.24</v>
+        <v>310,54</v>
       </c>
       <c r="H4" t="str">
-        <v>179.76</v>
+        <v>120,76</v>
       </c>
       <c r="I4" t="str">
-        <v>curly_method_300ml</v>
+        <v>enzim_pudra_80gr</v>
       </c>
       <c r="J4" t="str">
         <v>1</v>
       </c>
       <c r="K4" t="str">
-        <v>46226</v>
+        <v>24.07.2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>АЛТЕЯ-KRRET15</v>
+        <v>АЛТЕЯ-KREMRST</v>
       </c>
       <c r="B5" t="str">
-        <v>Крем для лица с липосомальным ретинолом 1.5% Ретинайт</v>
+        <v>Крем масло от растяжек для беременных и подростков с эластином Алтея 200 мл</v>
       </c>
       <c r="C5" t="str">
-        <v>Кремы для лица</v>
+        <v>1</v>
       </c>
       <c r="D5" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="str">
-        <v>883.5</v>
+        <v>355</v>
       </c>
       <c r="F5" t="str">
-        <v>114.99</v>
+        <v>151,2</v>
       </c>
       <c r="G5" t="str">
-        <v>636.12</v>
+        <v>255,6</v>
       </c>
       <c r="H5" t="str">
-        <v>247.38</v>
+        <v>99,4</v>
       </c>
       <c r="I5" t="str">
-        <v>retinait_krem_1_5_50ml</v>
+        <v>krem_ot_rastyazhek</v>
       </c>
       <c r="J5" t="str">
         <v>1</v>
       </c>
       <c r="K5" t="str">
-        <v>46226</v>
+        <v>24.07.2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>АЛТЕЯ-RETINT1</v>
+        <v>АЛТЕЯ-SYVTL30</v>
       </c>
       <c r="B6" t="str">
-        <v>Сыворотка с ретинолом 1% для лица от морщин антивозрастная Алтея 30 мл</v>
+        <v>Сыворотка для лица с ниацинамидом антивозрастная от акне пигментации Алтея 30 мл</v>
       </c>
       <c r="C6" t="str">
-        <v>Сыворотки</v>
+        <v>1</v>
       </c>
       <c r="D6" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="str">
-        <v>660</v>
+        <v>474,05</v>
       </c>
       <c r="F6" t="str">
-        <v>143.82</v>
+        <v>148,9</v>
       </c>
       <c r="G6" t="str">
-        <v>429</v>
+        <v>308,13</v>
       </c>
       <c r="H6" t="str">
-        <v>231</v>
+        <v>165,92</v>
       </c>
       <c r="I6" t="str">
-        <v>retinait_syvorotka_1_30ml</v>
+        <v>syvorotka_dlya_lica_30ml</v>
       </c>
       <c r="J6" t="str">
         <v>1</v>
       </c>
       <c r="K6" t="str">
-        <v>46226</v>
+        <v>24.07.2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>АЛТЕЯ-GELDLBR</v>
+        <v>АЛТЕЯ-SHPPERH</v>
       </c>
       <c r="B7" t="str">
-        <v>Гель для бритья мужской охлаждающий с ментолом Алтея 300 мл</v>
+        <v>Шампунь от перхоти лечебный с климбазолом Алтея 250 мл</v>
       </c>
       <c r="C7" t="str">
-        <v>Средства до и после бритья</v>
+        <v>1</v>
       </c>
       <c r="D7" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>522.5</v>
+        <v>428,45</v>
       </c>
       <c r="F7" t="str">
-        <v>125.68</v>
+        <v>106,2</v>
       </c>
       <c r="G7" t="str">
-        <v>376.2</v>
+        <v>308,48</v>
       </c>
       <c r="H7" t="str">
-        <v>146.3</v>
+        <v>119,97</v>
       </c>
       <c r="I7" t="str">
-        <v>gel_dlya_britya_300ml</v>
+        <v>shampun_protiv_perhoti_250ml</v>
       </c>
       <c r="J7" t="str">
         <v>1</v>
       </c>
       <c r="K7" t="str">
-        <v>46226</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>АЛТЕЯ-PENKARS</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Пенка для нарощенных ресниц и для бровей для умывания и очищения ресниц Алтея 150 мл</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Пенка для умывания</v>
-      </c>
-      <c r="D8" t="str">
-        <v>1</v>
-      </c>
-      <c r="E8" t="str">
-        <v>558.6</v>
-      </c>
-      <c r="F8" t="str">
-        <v>90.65</v>
-      </c>
-      <c r="G8" t="str">
-        <v>363.09</v>
-      </c>
-      <c r="H8" t="str">
-        <v>195.51</v>
-      </c>
-      <c r="I8" t="str">
-        <v>nabor_penka_dlya_resnic</v>
-      </c>
-      <c r="J8" t="str">
-        <v>1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>46226</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>АЛТЕЯ-KREMRST</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Крем масло от растяжек для беременных и подростков с эластином Алтея 200 мл</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Средство от растяжек</v>
-      </c>
-      <c r="D9" t="str">
-        <v>1</v>
-      </c>
-      <c r="E9" t="str">
-        <v>355</v>
-      </c>
-      <c r="F9" t="str">
-        <v>151.2</v>
-      </c>
-      <c r="G9" t="str">
-        <v>255.6</v>
-      </c>
-      <c r="H9" t="str">
-        <v>99.4</v>
-      </c>
-      <c r="I9" t="str">
-        <v>krem_ot_rastyazhek</v>
-      </c>
-      <c r="J9" t="str">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>46226</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>SKU</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Наименование</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Категория</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Количество</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Выручка (руб.)</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Себестоимость (руб.)</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Выручка с вычетом комиссии (руб.)</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Комиссия маркетплейса(руб.)</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Seller SKU ID</v>
-      </c>
-      <c r="J10" t="str">
-        <v>2</v>
-      </c>
-      <c r="K10" t="str">
-        <v>46226</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>QEEP-ENZYMPD</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Энзимная пудра для умывания лица и тела</v>
-      </c>
-      <c r="C11" t="str">
-        <v>1</v>
-      </c>
-      <c r="D11" t="str">
-        <v>0</v>
-      </c>
-      <c r="E11" t="str">
-        <v>511.1</v>
-      </c>
-      <c r="F11" t="str">
-        <v>119</v>
-      </c>
-      <c r="G11" t="str">
-        <v>367.99</v>
-      </c>
-      <c r="H11" t="str">
-        <v>143.11</v>
-      </c>
-      <c r="I11" t="str">
-        <v>qeep_enzyme_80g</v>
-      </c>
-      <c r="J11" t="str">
-        <v>2</v>
-      </c>
-      <c r="K11" t="str">
-        <v>46226</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>QEEP-SYVORTV</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Спрей для волос для роста и от выпадения волос qeep 100 мл</v>
-      </c>
-      <c r="C12" t="str">
-        <v>1</v>
-      </c>
-      <c r="D12" t="str">
-        <v>0</v>
-      </c>
-      <c r="E12" t="str">
-        <v>508.25</v>
-      </c>
-      <c r="F12" t="str">
-        <v>135.47</v>
-      </c>
-      <c r="G12" t="str">
-        <v>365.94</v>
-      </c>
-      <c r="H12" t="str">
-        <v>142.31</v>
-      </c>
-      <c r="I12" t="str">
-        <v>qeep_dlyarostavolos_100ml</v>
-      </c>
-      <c r="J12" t="str">
-        <v>2</v>
-      </c>
-      <c r="K12" t="str">
-        <v>46226</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>QEEP-KROVAVP</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Кровавый кислотный пилинг для лица от прыщей с Альфа и бета-гидроксикислотами qeep 30 мл</v>
-      </c>
-      <c r="C13" t="str">
-        <v>1</v>
-      </c>
-      <c r="D13" t="str">
-        <v>0</v>
-      </c>
-      <c r="E13" t="str">
-        <v>550.05</v>
-      </c>
-      <c r="F13" t="str">
-        <v>105.2</v>
-      </c>
-      <c r="G13" t="str">
-        <v>357.53</v>
-      </c>
-      <c r="H13" t="str">
-        <v>192.52</v>
-      </c>
-      <c r="I13" t="str">
-        <v>qeep_bloodypeeling_30ml</v>
-      </c>
-      <c r="J13" t="str">
-        <v>2</v>
-      </c>
-      <c r="K13" t="str">
-        <v>46226</v>
+        <v>24.07.2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/external_sources/retail_network_sales.xlsx
+++ b/data/external_sources/retail_network_sales.xlsx
@@ -10630,7 +10630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10672,1151 +10672,1292 @@
       <c r="M1" t="str">
         <v>Возвраты шт</v>
       </c>
-      <c r="N1">
-        <v>2</v>
-      </c>
-      <c r="O1">
-        <v>46230</v>
+      <c r="N1" t="str">
+        <v>1</v>
+      </c>
+      <c r="O1" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>"Кровавый" пилинг для лица маркировки "Алтэя"</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>99000076205</v>
       </c>
       <c r="C2" t="str">
         <v>krovavii_piling_30ml</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="str">
         <v>4670020498208</v>
       </c>
-      <c r="E2">
-        <v>9352</v>
-      </c>
-      <c r="F2">
-        <v>1336</v>
-      </c>
-      <c r="G2">
-        <v>8016</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>12</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>46230</v>
+      <c r="E2" t="str">
+        <v>11985</v>
+      </c>
+      <c r="F2" t="str">
+        <v>668</v>
+      </c>
+      <c r="G2" t="str">
+        <v>11317</v>
+      </c>
+      <c r="H2" t="str">
+        <v>0</v>
+      </c>
+      <c r="I2" t="str">
+        <v>18</v>
+      </c>
+      <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>17</v>
+      </c>
+      <c r="L2" t="str">
+        <v>0</v>
+      </c>
+      <c r="M2" t="str">
+        <v>0</v>
+      </c>
+      <c r="N2" t="str">
+        <v>1</v>
+      </c>
+      <c r="O2" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Гель для проблемной кожи лица и тела, с маркировками Алтея</v>
-      </c>
-      <c r="B3">
-        <v>99000114730</v>
+        <v>Крем для волос Упругий завиток, 300 мл</v>
+      </c>
+      <c r="B3" t="str">
+        <v>99000114726</v>
       </c>
       <c r="C3" t="str">
-        <v>gel_antiakne_20ml_v2</v>
-      </c>
-      <c r="D3">
-        <v>4660417420110</v>
-      </c>
-      <c r="E3">
-        <v>7928</v>
-      </c>
-      <c r="F3">
-        <v>856</v>
-      </c>
-      <c r="G3">
-        <v>7072</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>19</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>46230</v>
+        <v>curly_method_300ml</v>
+      </c>
+      <c r="D3" t="str">
+        <v>4603320465441</v>
+      </c>
+      <c r="E3" t="str">
+        <v>8424</v>
+      </c>
+      <c r="F3" t="str">
+        <v>903</v>
+      </c>
+      <c r="G3" t="str">
+        <v>7521</v>
+      </c>
+      <c r="H3" t="str">
+        <v>0</v>
+      </c>
+      <c r="I3" t="str">
+        <v>10</v>
+      </c>
+      <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>9</v>
+      </c>
+      <c r="L3" t="str">
+        <v>0</v>
+      </c>
+      <c r="M3" t="str">
+        <v>0</v>
+      </c>
+      <c r="N3" t="str">
+        <v>1</v>
+      </c>
+      <c r="O3" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Крем для волос Упругий завиток, 300 мл</v>
-      </c>
-      <c r="B4">
-        <v>99000114726</v>
+        <v>Гель для проблемной кожи лица и тела, с маркировками Алтея</v>
+      </c>
+      <c r="B4" t="str">
+        <v>99000114730</v>
       </c>
       <c r="C4" t="str">
-        <v>curly_method_300ml</v>
-      </c>
-      <c r="D4">
-        <v>4603320465441</v>
-      </c>
-      <c r="E4">
-        <v>6718</v>
-      </c>
-      <c r="F4">
-        <v>2203</v>
-      </c>
-      <c r="G4">
-        <v>4515</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>46230</v>
+        <v>gel_antiakne_20ml_v2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>4660417420110</v>
+      </c>
+      <c r="E4" t="str">
+        <v>7893</v>
+      </c>
+      <c r="F4" t="str">
+        <v>0</v>
+      </c>
+      <c r="G4" t="str">
+        <v>7446</v>
+      </c>
+      <c r="H4" t="str">
+        <v>447</v>
+      </c>
+      <c r="I4" t="str">
+        <v>18</v>
+      </c>
+      <c r="J4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K4" t="str">
+        <v>17</v>
+      </c>
+      <c r="L4" t="str">
+        <v>1</v>
+      </c>
+      <c r="M4" t="str">
+        <v>0</v>
+      </c>
+      <c r="N4" t="str">
+        <v>1</v>
+      </c>
+      <c r="O4" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>Продукция косметическая для ухода за кожей, в том числе в наборах: Маска для проблемной кожи лица м</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <v>99000114727</v>
       </c>
       <c r="C5" t="str">
         <v>maska_dlya_lica_100m</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="str">
         <v>4670020498741</v>
       </c>
-      <c r="E5">
-        <v>6213</v>
-      </c>
-      <c r="F5">
-        <v>933</v>
-      </c>
-      <c r="G5">
-        <v>4341</v>
-      </c>
-      <c r="H5">
+      <c r="E5" t="str">
+        <v>7428</v>
+      </c>
+      <c r="F5" t="str">
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <v>6489</v>
+      </c>
+      <c r="H5" t="str">
         <v>939</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="str">
+        <v>8</v>
+      </c>
+      <c r="J5" t="str">
+        <v>0</v>
+      </c>
+      <c r="K5" t="str">
         <v>7</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>46230</v>
+      <c r="L5" t="str">
+        <v>1</v>
+      </c>
+      <c r="M5" t="str">
+        <v>0</v>
+      </c>
+      <c r="N5" t="str">
+        <v>1</v>
+      </c>
+      <c r="O5" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Крем для лица с ретинолом 0.5, сыворотка от морщин и пигментных пятен, Алтея, Ретидерм, 50 мл</v>
-      </c>
-      <c r="B6">
-        <v>99000076216</v>
+        <v>Пенка для укладки волос</v>
+      </c>
+      <c r="B6" t="str">
+        <v>99000125266</v>
       </c>
       <c r="C6" t="str">
-        <v>retiderm_50ml</v>
-      </c>
-      <c r="D6">
-        <v>4610172186219</v>
-      </c>
-      <c r="E6">
-        <v>6195</v>
-      </c>
-      <c r="F6">
-        <v>1502</v>
-      </c>
-      <c r="G6">
-        <v>4693</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>26</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>20</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>46230</v>
+        <v>penka_kudryavii_meto</v>
+      </c>
+      <c r="D6" t="str">
+        <v>4670020498611</v>
+      </c>
+      <c r="E6" t="str">
+        <v>6242</v>
+      </c>
+      <c r="F6" t="str">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <v>6242</v>
+      </c>
+      <c r="H6" t="str">
+        <v>0</v>
+      </c>
+      <c r="I6" t="str">
+        <v>9</v>
+      </c>
+      <c r="J6" t="str">
+        <v>0</v>
+      </c>
+      <c r="K6" t="str">
+        <v>9</v>
+      </c>
+      <c r="L6" t="str">
+        <v>0</v>
+      </c>
+      <c r="M6" t="str">
+        <v>0</v>
+      </c>
+      <c r="N6" t="str">
+        <v>1</v>
+      </c>
+      <c r="O6" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Пенка для укладки волос</v>
-      </c>
-      <c r="B7">
-        <v>99000125266</v>
+        <v>Крем специального назначения «Псоридонт» 50 мл</v>
+      </c>
+      <c r="B7" t="str">
+        <v>99000125141</v>
       </c>
       <c r="C7" t="str">
-        <v>penka_kudryavii_meto</v>
-      </c>
-      <c r="D7">
-        <v>4670020498611</v>
-      </c>
-      <c r="E7">
-        <v>5581</v>
-      </c>
-      <c r="F7">
-        <v>1081</v>
-      </c>
-      <c r="G7">
-        <v>4500</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>46230</v>
+        <v>psoral_50ml</v>
+      </c>
+      <c r="D7" t="str">
+        <v>4660417421087</v>
+      </c>
+      <c r="E7" t="str">
+        <v>5112</v>
+      </c>
+      <c r="F7" t="str">
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <v>5112</v>
+      </c>
+      <c r="H7" t="str">
+        <v>0</v>
+      </c>
+      <c r="I7" t="str">
+        <v>7</v>
+      </c>
+      <c r="J7" t="str">
+        <v>0</v>
+      </c>
+      <c r="K7" t="str">
+        <v>7</v>
+      </c>
+      <c r="L7" t="str">
+        <v>0</v>
+      </c>
+      <c r="M7" t="str">
+        <v>0</v>
+      </c>
+      <c r="N7" t="str">
+        <v>1</v>
+      </c>
+      <c r="O7" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Крем-шелк для сухой кожи ног</v>
-      </c>
-      <c r="B8">
-        <v>99000076225</v>
+        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея</v>
+      </c>
+      <c r="B8" t="str">
+        <v>99000124421</v>
       </c>
       <c r="C8" t="str">
-        <v>kremshelk_100ml</v>
-      </c>
-      <c r="D8">
-        <v>4670020498437</v>
-      </c>
-      <c r="E8">
-        <v>3776</v>
-      </c>
-      <c r="F8">
-        <v>1806</v>
-      </c>
-      <c r="G8">
-        <v>1970</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>8</v>
-      </c>
-      <c r="J8">
+        <v>retinait_krem_1_50ml</v>
+      </c>
+      <c r="D8" t="str">
+        <v>4660417421605</v>
+      </c>
+      <c r="E8" t="str">
+        <v>5046</v>
+      </c>
+      <c r="F8" t="str">
+        <v>1025</v>
+      </c>
+      <c r="G8" t="str">
+        <v>4021</v>
+      </c>
+      <c r="H8" t="str">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <v>5</v>
+      </c>
+      <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
         <v>4</v>
       </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>46230</v>
+      <c r="L8" t="str">
+        <v>0</v>
+      </c>
+      <c r="M8" t="str">
+        <v>0</v>
+      </c>
+      <c r="N8" t="str">
+        <v>1</v>
+      </c>
+      <c r="O8" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея</v>
-      </c>
-      <c r="B9">
-        <v>99000124421</v>
+        <v>Спрей для роста волос торговой марки Алтея</v>
+      </c>
+      <c r="B9" t="str">
+        <v>99000114724</v>
       </c>
       <c r="C9" t="str">
-        <v>retinait_krem_1_50ml</v>
-      </c>
-      <c r="D9">
-        <v>4660417421605</v>
-      </c>
-      <c r="E9">
-        <v>3075</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>3075</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>3</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>3</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>46230</v>
+        <v>sprei_buster_100ml</v>
+      </c>
+      <c r="D9" t="str">
+        <v>4603320465359</v>
+      </c>
+      <c r="E9" t="str">
+        <v>4211</v>
+      </c>
+      <c r="F9" t="str">
+        <v>602</v>
+      </c>
+      <c r="G9" t="str">
+        <v>3609</v>
+      </c>
+      <c r="H9" t="str">
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
+        <v>7</v>
+      </c>
+      <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>6</v>
+      </c>
+      <c r="L9" t="str">
+        <v>0</v>
+      </c>
+      <c r="M9" t="str">
+        <v>0</v>
+      </c>
+      <c r="N9" t="str">
+        <v>1</v>
+      </c>
+      <c r="O9" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Крем от растяжек, Алтея, 200 мл</v>
-      </c>
-      <c r="B10">
-        <v>99000114731</v>
+        <v>Продукция косметическая для ухода за кожей для взрослых: гелевая маска со спикулами торговой марки А</v>
+      </c>
+      <c r="B10" t="str">
+        <v>99000177799</v>
       </c>
       <c r="C10" t="str">
-        <v>krem_ot_rastyazhek</v>
-      </c>
-      <c r="D10">
-        <v>4670020497898</v>
-      </c>
-      <c r="E10">
-        <v>2960</v>
-      </c>
-      <c r="F10">
-        <v>1654</v>
-      </c>
-      <c r="G10">
-        <v>1306</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>4</v>
-      </c>
-      <c r="J10">
-        <v>2</v>
-      </c>
-      <c r="K10">
-        <v>2</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10">
-        <v>46230</v>
+        <v>spicul_gel_mask_75ml</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4660417421858</v>
+      </c>
+      <c r="E10" t="str">
+        <v>4208</v>
+      </c>
+      <c r="F10" t="str">
+        <v>0</v>
+      </c>
+      <c r="G10" t="str">
+        <v>4208</v>
+      </c>
+      <c r="H10" t="str">
+        <v>0</v>
+      </c>
+      <c r="I10" t="str">
+        <v>5</v>
+      </c>
+      <c r="J10" t="str">
+        <v>0</v>
+      </c>
+      <c r="K10" t="str">
+        <v>5</v>
+      </c>
+      <c r="L10" t="str">
+        <v>0</v>
+      </c>
+      <c r="M10" t="str">
+        <v>0</v>
+      </c>
+      <c r="N10" t="str">
+        <v>1</v>
+      </c>
+      <c r="O10" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Спрей-сыворотка для волос маркировки Алтея</v>
-      </c>
-      <c r="B11">
-        <v>99000076226</v>
+        <v>Крем для лица с ретинолом 0.5, сыворотка от морщин и пигментных пятен, Алтея, Ретидерм, 50 мл</v>
+      </c>
+      <c r="B11" t="str">
+        <v>99000076216</v>
       </c>
       <c r="C11" t="str">
-        <v>termo_sprei_200ml</v>
-      </c>
-      <c r="D11">
-        <v>4670020497980</v>
-      </c>
-      <c r="E11">
-        <v>2614</v>
-      </c>
-      <c r="F11">
-        <v>472</v>
-      </c>
-      <c r="G11">
-        <v>1683</v>
-      </c>
-      <c r="H11">
-        <v>459</v>
-      </c>
-      <c r="I11">
-        <v>6</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11">
-        <v>4</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>46230</v>
+        <v>retiderm_50ml</v>
+      </c>
+      <c r="D11" t="str">
+        <v>4610172186219</v>
+      </c>
+      <c r="E11" t="str">
+        <v>3821</v>
+      </c>
+      <c r="F11" t="str">
+        <v>0</v>
+      </c>
+      <c r="G11" t="str">
+        <v>3821</v>
+      </c>
+      <c r="H11" t="str">
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
+        <v>17</v>
+      </c>
+      <c r="J11" t="str">
+        <v>0</v>
+      </c>
+      <c r="K11" t="str">
+        <v>17</v>
+      </c>
+      <c r="L11" t="str">
+        <v>0</v>
+      </c>
+      <c r="M11" t="str">
+        <v>0</v>
+      </c>
+      <c r="N11" t="str">
+        <v>1</v>
+      </c>
+      <c r="O11" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Средство косметическое: Воск для волос торговой марки: «Алтея» 15гр</v>
-      </c>
-      <c r="B12">
-        <v>99000131672</v>
+        <v>Крем от растяжек, Алтея, 200 мл</v>
+      </c>
+      <c r="B12" t="str">
+        <v>99000114731</v>
       </c>
       <c r="C12" t="str">
-        <v>vosk_stik_15ml</v>
-      </c>
-      <c r="D12">
-        <v>4670207150196</v>
-      </c>
-      <c r="E12">
-        <v>2573</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>2573</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>6</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>6</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>46230</v>
+        <v>krem_ot_rastyazhek</v>
+      </c>
+      <c r="D12" t="str">
+        <v>4670020497898</v>
+      </c>
+      <c r="E12" t="str">
+        <v>3102</v>
+      </c>
+      <c r="F12" t="str">
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <v>3102</v>
+      </c>
+      <c r="H12" t="str">
+        <v>0</v>
+      </c>
+      <c r="I12" t="str">
+        <v>4</v>
+      </c>
+      <c r="J12" t="str">
+        <v>0</v>
+      </c>
+      <c r="K12" t="str">
+        <v>4</v>
+      </c>
+      <c r="L12" t="str">
+        <v>0</v>
+      </c>
+      <c r="M12" t="str">
+        <v>0</v>
+      </c>
+      <c r="N12" t="str">
+        <v>1</v>
+      </c>
+      <c r="O12" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Продукция косметическая для ухода за кожей для взрослых: гелевая маска со спикулами торговой марки А</v>
-      </c>
-      <c r="B13">
-        <v>99000177799</v>
+        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз, 30мл</v>
+      </c>
+      <c r="B13" t="str">
+        <v>99000154005</v>
       </c>
       <c r="C13" t="str">
-        <v>spicul_gel_mask_75ml</v>
-      </c>
-      <c r="D13">
-        <v>4660417421858</v>
-      </c>
-      <c r="E13">
-        <v>2523</v>
-      </c>
-      <c r="F13">
-        <v>829</v>
-      </c>
-      <c r="G13">
-        <v>1694</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
+        <v>retinol_boost_krem_d</v>
+      </c>
+      <c r="D13" t="str">
+        <v>4660417421636</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2625</v>
+      </c>
+      <c r="F13" t="str">
+        <v>893</v>
+      </c>
+      <c r="G13" t="str">
+        <v>1732</v>
+      </c>
+      <c r="H13" t="str">
+        <v>0</v>
+      </c>
+      <c r="I13" t="str">
         <v>3</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
+      <c r="J13" t="str">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
         <v>2</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
-        <v>46230</v>
+      <c r="L13" t="str">
+        <v>0</v>
+      </c>
+      <c r="M13" t="str">
+        <v>0</v>
+      </c>
+      <c r="N13" t="str">
+        <v>1</v>
+      </c>
+      <c r="O13" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Спрей для роста волос торговой марки Алтея</v>
-      </c>
-      <c r="B14">
-        <v>99000114724</v>
+        <v>Спрей-сыворотка для волос маркировки Алтея</v>
+      </c>
+      <c r="B14" t="str">
+        <v>99000076226</v>
       </c>
       <c r="C14" t="str">
-        <v>sprei_buster_100ml</v>
-      </c>
-      <c r="D14">
-        <v>4603320465359</v>
-      </c>
-      <c r="E14">
-        <v>2391</v>
-      </c>
-      <c r="F14">
-        <v>602</v>
-      </c>
-      <c r="G14">
-        <v>1789</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>4</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>3</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>46230</v>
+        <v>termo_sprei_200ml</v>
+      </c>
+      <c r="D14" t="str">
+        <v>4670020497980</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2344</v>
+      </c>
+      <c r="F14" t="str">
+        <v>0</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2344</v>
+      </c>
+      <c r="H14" t="str">
+        <v>0</v>
+      </c>
+      <c r="I14" t="str">
+        <v>5</v>
+      </c>
+      <c r="J14" t="str">
+        <v>0</v>
+      </c>
+      <c r="K14" t="str">
+        <v>5</v>
+      </c>
+      <c r="L14" t="str">
+        <v>0</v>
+      </c>
+      <c r="M14" t="str">
+        <v>0</v>
+      </c>
+      <c r="N14" t="str">
+        <v>1</v>
+      </c>
+      <c r="O14" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ламеллярный крем для рук с мочевиной, увлажняющий и питательный с маслом кокоса, Алтея, 75 мл</v>
-      </c>
-      <c r="B15">
-        <v>99000114729</v>
+        <v>Шампунь для кудрявых волос торговой марки Алтея, 500 мл</v>
+      </c>
+      <c r="B15" t="str">
+        <v>99000179424</v>
       </c>
       <c r="C15" t="str">
-        <v>krem_dlya_ruk_75ml</v>
-      </c>
-      <c r="D15">
-        <v>4660417421452</v>
-      </c>
-      <c r="E15">
-        <v>1545</v>
-      </c>
-      <c r="F15">
-        <v>1164</v>
-      </c>
-      <c r="G15">
-        <v>381</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>4</v>
-      </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>46230</v>
+        <v>shampun_kudryavii_me</v>
+      </c>
+      <c r="D15" t="str">
+        <v>4640523970310</v>
+      </c>
+      <c r="E15" t="str">
+        <v>1718</v>
+      </c>
+      <c r="F15" t="str">
+        <v>859</v>
+      </c>
+      <c r="G15" t="str">
+        <v>859</v>
+      </c>
+      <c r="H15" t="str">
+        <v>0</v>
+      </c>
+      <c r="I15" t="str">
+        <v>2</v>
+      </c>
+      <c r="J15" t="str">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>1</v>
+      </c>
+      <c r="L15" t="str">
+        <v>0</v>
+      </c>
+      <c r="M15" t="str">
+        <v>0</v>
+      </c>
+      <c r="N15" t="str">
+        <v>1</v>
+      </c>
+      <c r="O15" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз, 30мл</v>
-      </c>
-      <c r="B16">
-        <v>99000154005</v>
+        <v>Крем для лица spf 50 с защитой UVA/UVB, торговой марки Алтея</v>
+      </c>
+      <c r="B16" t="str">
+        <v>99000163832</v>
       </c>
       <c r="C16" t="str">
-        <v>retinol_boost_krem_d</v>
-      </c>
-      <c r="D16">
-        <v>4660417421636</v>
-      </c>
-      <c r="E16">
-        <v>893</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>893</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <v>46230</v>
+        <v>krem_spf50_50ml</v>
+      </c>
+      <c r="D16" t="str">
+        <v>4660417421766</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1600</v>
+      </c>
+      <c r="F16" t="str">
+        <v>0</v>
+      </c>
+      <c r="G16" t="str">
+        <v>1600</v>
+      </c>
+      <c r="H16" t="str">
+        <v>0</v>
+      </c>
+      <c r="I16" t="str">
+        <v>2</v>
+      </c>
+      <c r="J16" t="str">
+        <v>0</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2</v>
+      </c>
+      <c r="L16" t="str">
+        <v>0</v>
+      </c>
+      <c r="M16" t="str">
+        <v>0</v>
+      </c>
+      <c r="N16" t="str">
+        <v>1</v>
+      </c>
+      <c r="O16" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея</v>
-      </c>
-      <c r="B17">
-        <v>99000124418</v>
+        <v>Средство косметическое: Воск для волос торговой марки: «Алтея» 15гр</v>
+      </c>
+      <c r="B17" t="str">
+        <v>99000131672</v>
       </c>
       <c r="C17" t="str">
-        <v>retinait_krem_025_50</v>
-      </c>
-      <c r="D17">
-        <v>4660417421599</v>
-      </c>
-      <c r="E17">
-        <v>844</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>844</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <v>46230</v>
+        <v>vosk_stik_15ml</v>
+      </c>
+      <c r="D17" t="str">
+        <v>4670207150196</v>
+      </c>
+      <c r="E17" t="str">
+        <v>1432</v>
+      </c>
+      <c r="F17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G17" t="str">
+        <v>1432</v>
+      </c>
+      <c r="H17" t="str">
+        <v>0</v>
+      </c>
+      <c r="I17" t="str">
+        <v>3</v>
+      </c>
+      <c r="J17" t="str">
+        <v>0</v>
+      </c>
+      <c r="K17" t="str">
+        <v>3</v>
+      </c>
+      <c r="L17" t="str">
+        <v>0</v>
+      </c>
+      <c r="M17" t="str">
+        <v>0</v>
+      </c>
+      <c r="N17" t="str">
+        <v>1</v>
+      </c>
+      <c r="O17" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Крем для лица spf 50 с защитой UVA/UVB, торговой марки Алтея</v>
-      </c>
-      <c r="B18">
-        <v>99000163832</v>
+        <v>Средство косметическое для ухода за волосами: маска для волос восстанавливающая с авокадо и маслом о</v>
+      </c>
+      <c r="B18" t="str">
+        <v>99000076210</v>
       </c>
       <c r="C18" t="str">
-        <v>krem_spf50_50ml</v>
-      </c>
-      <c r="D18">
-        <v>4660417421766</v>
-      </c>
-      <c r="E18">
-        <v>800</v>
-      </c>
-      <c r="F18">
-        <v>800</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <v>46230</v>
+        <v>maska-batter_250ml</v>
+      </c>
+      <c r="D18" t="str">
+        <v>4670020497546</v>
+      </c>
+      <c r="E18" t="str">
+        <v>1376</v>
+      </c>
+      <c r="F18" t="str">
+        <v>0</v>
+      </c>
+      <c r="G18" t="str">
+        <v>1376</v>
+      </c>
+      <c r="H18" t="str">
+        <v>0</v>
+      </c>
+      <c r="I18" t="str">
+        <v>2</v>
+      </c>
+      <c r="J18" t="str">
+        <v>0</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2</v>
+      </c>
+      <c r="L18" t="str">
+        <v>0</v>
+      </c>
+      <c r="M18" t="str">
+        <v>0</v>
+      </c>
+      <c r="N18" t="str">
+        <v>1</v>
+      </c>
+      <c r="O18" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Крем специального назначения «Псоридонт» 50 мл</v>
-      </c>
-      <c r="B19">
-        <v>99000125141</v>
+        <v>Крем-шелк для сухой кожи ног</v>
+      </c>
+      <c r="B19" t="str">
+        <v>99000076225</v>
       </c>
       <c r="C19" t="str">
-        <v>psoral_50ml</v>
-      </c>
-      <c r="D19">
-        <v>4660417421087</v>
-      </c>
-      <c r="E19">
-        <v>760</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>760</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>46230</v>
+        <v>kremshelk_100ml</v>
+      </c>
+      <c r="D19" t="str">
+        <v>4670020498437</v>
+      </c>
+      <c r="E19" t="str">
+        <v>1335</v>
+      </c>
+      <c r="F19" t="str">
+        <v>0</v>
+      </c>
+      <c r="G19" t="str">
+        <v>1335</v>
+      </c>
+      <c r="H19" t="str">
+        <v>0</v>
+      </c>
+      <c r="I19" t="str">
+        <v>3</v>
+      </c>
+      <c r="J19" t="str">
+        <v>0</v>
+      </c>
+      <c r="K19" t="str">
+        <v>3</v>
+      </c>
+      <c r="L19" t="str">
+        <v>0</v>
+      </c>
+      <c r="M19" t="str">
+        <v>0</v>
+      </c>
+      <c r="N19" t="str">
+        <v>1</v>
+      </c>
+      <c r="O19" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Ретинайт 0,5 экспресс-омоложение Anti-Age Липосомальный комплекс ретинола 0,5 + Ниацинамид 50 мл</v>
-      </c>
-      <c r="B20">
-        <v>99000131675</v>
+        <v>Маска д/лица Лифтинг PDRN и пептиды 75мл</v>
+      </c>
+      <c r="B20" t="str">
+        <v>99000188068</v>
       </c>
       <c r="C20" t="str">
-        <v>retinait_krem_05_50m</v>
-      </c>
-      <c r="D20">
-        <v>4660417421759</v>
-      </c>
-      <c r="E20">
-        <v>744</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>744</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>46230</v>
+        <v>lifting_maska_pdrn_7</v>
+      </c>
+      <c r="D20" t="str">
+        <v>4660417421964</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1165</v>
+      </c>
+      <c r="F20" t="str">
+        <v>0</v>
+      </c>
+      <c r="G20" t="str">
+        <v>1165</v>
+      </c>
+      <c r="H20" t="str">
+        <v>0</v>
+      </c>
+      <c r="I20" t="str">
+        <v>1</v>
+      </c>
+      <c r="J20" t="str">
+        <v>0</v>
+      </c>
+      <c r="K20" t="str">
+        <v>1</v>
+      </c>
+      <c r="L20" t="str">
+        <v>0</v>
+      </c>
+      <c r="M20" t="str">
+        <v>0</v>
+      </c>
+      <c r="N20" t="str">
+        <v>1</v>
+      </c>
+      <c r="O20" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Средство косметическое для ухода за волосами: маска для волос восстанавливающая с авокадо и маслом о</v>
-      </c>
-      <c r="B21">
-        <v>99000076210</v>
+        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея, 50 мл</v>
+      </c>
+      <c r="B21" t="str">
+        <v>99000176496</v>
       </c>
       <c r="C21" t="str">
-        <v>maska-batter_250ml</v>
-      </c>
-      <c r="D21">
-        <v>4670020497546</v>
-      </c>
-      <c r="E21">
-        <v>657</v>
-      </c>
-      <c r="F21">
-        <v>657</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="O21">
-        <v>46230</v>
+        <v>retinait_krem_1_5_50</v>
+      </c>
+      <c r="D21" t="str">
+        <v>4660417421827</v>
+      </c>
+      <c r="E21" t="str">
+        <v>840</v>
+      </c>
+      <c r="F21" t="str">
+        <v>0</v>
+      </c>
+      <c r="G21" t="str">
+        <v>840</v>
+      </c>
+      <c r="H21" t="str">
+        <v>0</v>
+      </c>
+      <c r="I21" t="str">
+        <v>1</v>
+      </c>
+      <c r="J21" t="str">
+        <v>0</v>
+      </c>
+      <c r="K21" t="str">
+        <v>1</v>
+      </c>
+      <c r="L21" t="str">
+        <v>0</v>
+      </c>
+      <c r="M21" t="str">
+        <v>0</v>
+      </c>
+      <c r="N21" t="str">
+        <v>1</v>
+      </c>
+      <c r="O21" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Средство косметическое профессиональное: маска разогревающая для роста волос торговой марки: Алтея.</v>
-      </c>
-      <c r="B22">
-        <v>99000076208</v>
+        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея</v>
+      </c>
+      <c r="B22" t="str">
+        <v>99000124418</v>
       </c>
       <c r="C22" t="str">
-        <v>maska-batter_dlya_ro</v>
-      </c>
-      <c r="D22">
-        <v>4603320465366</v>
-      </c>
-      <c r="E22">
-        <v>650</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>650</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22">
-        <v>46230</v>
+        <v>retinait_krem_025_50</v>
+      </c>
+      <c r="D22" t="str">
+        <v>4660417421599</v>
+      </c>
+      <c r="E22" t="str">
+        <v>796</v>
+      </c>
+      <c r="F22" t="str">
+        <v>0</v>
+      </c>
+      <c r="G22" t="str">
+        <v>796</v>
+      </c>
+      <c r="H22" t="str">
+        <v>0</v>
+      </c>
+      <c r="I22" t="str">
+        <v>1</v>
+      </c>
+      <c r="J22" t="str">
+        <v>0</v>
+      </c>
+      <c r="K22" t="str">
+        <v>1</v>
+      </c>
+      <c r="L22" t="str">
+        <v>0</v>
+      </c>
+      <c r="M22" t="str">
+        <v>0</v>
+      </c>
+      <c r="N22" t="str">
+        <v>1</v>
+      </c>
+      <c r="O22" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Шампунь от перхоти лечебный с климбазолом Алтея, 250мл</v>
-      </c>
-      <c r="B23">
-        <v>99000076206</v>
+        <v>РЕТИНАЙТ сыворотка для лица 30 мл</v>
+      </c>
+      <c r="B23" t="str">
+        <v>99000125142</v>
       </c>
       <c r="C23" t="str">
-        <v>shampun_protiv_perho</v>
-      </c>
-      <c r="D23">
-        <v>4670020496679</v>
-      </c>
-      <c r="E23">
-        <v>650</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>650</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>1</v>
-      </c>
-      <c r="O23">
-        <v>46230</v>
+        <v>retinait_syvorotka_1</v>
+      </c>
+      <c r="D23" t="str">
+        <v>4603320465403</v>
+      </c>
+      <c r="E23" t="str">
+        <v>780</v>
+      </c>
+      <c r="F23" t="str">
+        <v>0</v>
+      </c>
+      <c r="G23" t="str">
+        <v>780</v>
+      </c>
+      <c r="H23" t="str">
+        <v>0</v>
+      </c>
+      <c r="I23" t="str">
+        <v>1</v>
+      </c>
+      <c r="J23" t="str">
+        <v>0</v>
+      </c>
+      <c r="K23" t="str">
+        <v>1</v>
+      </c>
+      <c r="L23" t="str">
+        <v>0</v>
+      </c>
+      <c r="M23" t="str">
+        <v>0</v>
+      </c>
+      <c r="N23" t="str">
+        <v>1</v>
+      </c>
+      <c r="O23" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Средство косметическое для ухода за волосами: масло для бороды, маркировка: Алтея.</v>
-      </c>
-      <c r="B24">
-        <v>99000076215</v>
+        <v>Крем для лица Ретинайт с церамидами, 50 мл</v>
+      </c>
+      <c r="B24" t="str">
+        <v>99000137436</v>
       </c>
       <c r="C24" t="str">
-        <v>maslo_dlya_borodi_50</v>
-      </c>
-      <c r="D24">
-        <v>4610172186882</v>
-      </c>
-      <c r="E24">
-        <v>569</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>569</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24">
-        <v>46230</v>
+        <v>retinait_krem_01_50m</v>
+      </c>
+      <c r="D24" t="str">
+        <v>4660417421629</v>
+      </c>
+      <c r="E24" t="str">
+        <v>717</v>
+      </c>
+      <c r="F24" t="str">
+        <v>0</v>
+      </c>
+      <c r="G24" t="str">
+        <v>717</v>
+      </c>
+      <c r="H24" t="str">
+        <v>0</v>
+      </c>
+      <c r="I24" t="str">
+        <v>1</v>
+      </c>
+      <c r="J24" t="str">
+        <v>0</v>
+      </c>
+      <c r="K24" t="str">
+        <v>1</v>
+      </c>
+      <c r="L24" t="str">
+        <v>0</v>
+      </c>
+      <c r="M24" t="str">
+        <v>0</v>
+      </c>
+      <c r="N24" t="str">
+        <v>1</v>
+      </c>
+      <c r="O24" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>Ретинайт 0,5 экспресс-омоложение Anti-Age Липосомальный комплекс ретинола 0,5 + Ниацинамид 50 мл</v>
+      </c>
+      <c r="B25" t="str">
+        <v>99000131675</v>
+      </c>
+      <c r="C25" t="str">
+        <v>retinait_krem_05_50m</v>
+      </c>
+      <c r="D25" t="str">
+        <v>4660417421759</v>
+      </c>
+      <c r="E25" t="str">
+        <v>702</v>
+      </c>
+      <c r="F25" t="str">
+        <v>0</v>
+      </c>
+      <c r="G25" t="str">
+        <v>702</v>
+      </c>
+      <c r="H25" t="str">
+        <v>0</v>
+      </c>
+      <c r="I25" t="str">
+        <v>1</v>
+      </c>
+      <c r="J25" t="str">
+        <v>0</v>
+      </c>
+      <c r="K25" t="str">
+        <v>1</v>
+      </c>
+      <c r="L25" t="str">
+        <v>0</v>
+      </c>
+      <c r="M25" t="str">
+        <v>0</v>
+      </c>
+      <c r="N25" t="str">
+        <v>1</v>
+      </c>
+      <c r="O25" t="str">
+        <v>28.7.2026</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
         <v>Шампунь для роста волос, от выпадения волос профессиональный, Алтея, 250 мл</v>
       </c>
-      <c r="B25">
+      <c r="B26" t="str">
         <v>99000076213</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C26" t="str">
         <v>shampun_dlya_rosta_2</v>
       </c>
-      <c r="D25">
+      <c r="D26" t="str">
         <v>4670020496747</v>
       </c>
-      <c r="E25">
+      <c r="E26" t="str">
         <v>461</v>
       </c>
-      <c r="F25">
+      <c r="F26" t="str">
+        <v>0</v>
+      </c>
+      <c r="G26" t="str">
         <v>461</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <v>46230</v>
+      <c r="H26" t="str">
+        <v>0</v>
+      </c>
+      <c r="I26" t="str">
+        <v>1</v>
+      </c>
+      <c r="J26" t="str">
+        <v>0</v>
+      </c>
+      <c r="K26" t="str">
+        <v>1</v>
+      </c>
+      <c r="L26" t="str">
+        <v>0</v>
+      </c>
+      <c r="M26" t="str">
+        <v>0</v>
+      </c>
+      <c r="N26" t="str">
+        <v>1</v>
+      </c>
+      <c r="O26" t="str">
+        <v>28.7.2026</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Средство косметическое для ухода за волосами: масло для бороды, маркировка: Алтея.</v>
+      </c>
+      <c r="B27" t="str">
+        <v>99000076215</v>
+      </c>
+      <c r="C27" t="str">
+        <v>maslo_dlya_borodi_50</v>
+      </c>
+      <c r="D27" t="str">
+        <v>4610172186882</v>
+      </c>
+      <c r="E27" t="str">
+        <v>422</v>
+      </c>
+      <c r="F27" t="str">
+        <v>0</v>
+      </c>
+      <c r="G27" t="str">
+        <v>422</v>
+      </c>
+      <c r="H27" t="str">
+        <v>0</v>
+      </c>
+      <c r="I27" t="str">
+        <v>1</v>
+      </c>
+      <c r="J27" t="str">
+        <v>0</v>
+      </c>
+      <c r="K27" t="str">
+        <v>1</v>
+      </c>
+      <c r="L27" t="str">
+        <v>0</v>
+      </c>
+      <c r="M27" t="str">
+        <v>0</v>
+      </c>
+      <c r="N27" t="str">
+        <v>1</v>
+      </c>
+      <c r="O27" t="str">
+        <v>28.7.2026</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Гель для интимной гигиены с молочной кислотой, Алтея, Интимвита, 300 мл</v>
+      </c>
+      <c r="B28" t="str">
+        <v>99000114723</v>
+      </c>
+      <c r="C28" t="str">
+        <v>intimvita_300ml</v>
+      </c>
+      <c r="D28" t="str">
+        <v>4630084865477</v>
+      </c>
+      <c r="E28" t="str">
+        <v>337</v>
+      </c>
+      <c r="F28" t="str">
+        <v>0</v>
+      </c>
+      <c r="G28" t="str">
+        <v>337</v>
+      </c>
+      <c r="H28" t="str">
+        <v>0</v>
+      </c>
+      <c r="I28" t="str">
+        <v>1</v>
+      </c>
+      <c r="J28" t="str">
+        <v>0</v>
+      </c>
+      <c r="K28" t="str">
+        <v>1</v>
+      </c>
+      <c r="L28" t="str">
+        <v>0</v>
+      </c>
+      <c r="M28" t="str">
+        <v>0</v>
+      </c>
+      <c r="N28" t="str">
+        <v>1</v>
+      </c>
+      <c r="O28" t="str">
+        <v>28.7.2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11850,15 +11991,15 @@
         <v>1</v>
       </c>
       <c r="K1" t="str">
-        <v>46230</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>АЛТЕЯ-RETINT1</v>
+        <v>АЛТЕЯ-KRSPF50</v>
       </c>
       <c r="B2" t="str">
-        <v>Сыворотка с ретинолом 1% для лица от морщин антивозрастная Алтея 30 мл</v>
+        <v>Крем солнцезащитный СПФ 50 для лица 50 мл</v>
       </c>
       <c r="C2" t="str">
         <v>1</v>
@@ -11867,33 +12008,33 @@
         <v>0</v>
       </c>
       <c r="E2" t="str">
-        <v>660</v>
+        <v>701,5</v>
       </c>
       <c r="F2" t="str">
-        <v>143.82</v>
+        <v>132,6</v>
       </c>
       <c r="G2" t="str">
-        <v>429</v>
+        <v>455,98</v>
       </c>
       <c r="H2" t="str">
-        <v>231</v>
+        <v>245,52</v>
       </c>
       <c r="I2" t="str">
-        <v>retinait_syvorotka_1_30ml</v>
+        <v>krem_spf50_50ml</v>
       </c>
       <c r="J2" t="str">
         <v>1</v>
       </c>
       <c r="K2" t="str">
-        <v>46230</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>АЛТЕЯ-KREMDLV</v>
+        <v>АЛТЕЯ-RETINT1</v>
       </c>
       <c r="B3" t="str">
-        <v>Крем для век и кожи вокруг глаз жидкие патчи для глаз Алтея 30 мл</v>
+        <v>Сыворотка с ретинолом 1% для лица от морщин антивозрастная Алтея 30 мл</v>
       </c>
       <c r="C3" t="str">
         <v>1</v>
@@ -11902,100 +12043,135 @@
         <v>0</v>
       </c>
       <c r="E3" t="str">
-        <v>547</v>
+        <v>660</v>
       </c>
       <c r="F3" t="str">
-        <v>126.5</v>
+        <v>143,82</v>
       </c>
       <c r="G3" t="str">
-        <v>355.55</v>
+        <v>429</v>
       </c>
       <c r="H3" t="str">
-        <v>191.45</v>
+        <v>231</v>
       </c>
       <c r="I3" t="str">
-        <v>krem_dlya_vek_30ml</v>
+        <v>retinait_syvorotka_1_30ml</v>
       </c>
       <c r="J3" t="str">
         <v>1</v>
       </c>
       <c r="K3" t="str">
-        <v>46230</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>АЛТЕЯ-KREMRST</v>
+        <v>АЛТЕЯ-TERMSPR</v>
       </c>
       <c r="B4" t="str">
-        <v>Крем масло от растяжек для беременных и подростков с эластином Алтея 200 мл</v>
+        <v>Спрей для волос 17 в 1 восстанавливающий с кератином Алтея 200 мл</v>
       </c>
       <c r="C4" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="str">
         <v>0</v>
       </c>
       <c r="E4" t="str">
-        <v>710</v>
+        <v>326</v>
       </c>
       <c r="F4" t="str">
-        <v>302.4</v>
+        <v>116,1</v>
       </c>
       <c r="G4" t="str">
-        <v>511.2</v>
+        <v>234,72</v>
       </c>
       <c r="H4" t="str">
-        <v>198.8</v>
+        <v>91,28</v>
       </c>
       <c r="I4" t="str">
-        <v>krem_ot_rastyazhek</v>
+        <v>termo_sprei_200ml</v>
       </c>
       <c r="J4" t="str">
         <v>1</v>
       </c>
       <c r="K4" t="str">
-        <v>46230</v>
+        <v>28.07.2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>АЛТЕЯ-SHPPERH</v>
+        <v>АЛТЕЯ-KREMRST</v>
       </c>
       <c r="B5" t="str">
-        <v>Шампунь от перхоти лечебный с климбазолом Алтея 250 мл</v>
+        <v>Крем масло от растяжек для беременных и подростков с эластином Алтея 200 мл</v>
       </c>
       <c r="C5" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="str">
         <v>0</v>
       </c>
       <c r="E5" t="str">
-        <v>816.9</v>
+        <v>355</v>
       </c>
       <c r="F5" t="str">
-        <v>212.4</v>
+        <v>151,2</v>
       </c>
       <c r="G5" t="str">
-        <v>588.16</v>
+        <v>255,6</v>
       </c>
       <c r="H5" t="str">
-        <v>228.74</v>
+        <v>99,4</v>
       </c>
       <c r="I5" t="str">
-        <v>shampun_protiv_perhoti_250ml</v>
+        <v>krem_ot_rastyazhek</v>
       </c>
       <c r="J5" t="str">
         <v>1</v>
       </c>
       <c r="K5" t="str">
-        <v>46230</v>
+        <v>28.07.2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>АЛТЕЯ-REMYVRS</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Ремувер для снятия ресниц Алтея 18 г</v>
+      </c>
+      <c r="C6" t="str">
+        <v>1</v>
+      </c>
+      <c r="D6" t="str">
+        <v>0</v>
+      </c>
+      <c r="E6" t="str">
+        <v>341</v>
+      </c>
+      <c r="F6" t="str">
+        <v>80,92</v>
+      </c>
+      <c r="G6" t="str">
+        <v>245,52</v>
+      </c>
+      <c r="H6" t="str">
+        <v>95,48</v>
+      </c>
+      <c r="I6" t="str">
+        <v>nabor_remuver_kremovii</v>
+      </c>
+      <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>28.07.2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/external_sources/retail_network_sales.xlsx
+++ b/data/external_sources/retail_network_sales.xlsx
@@ -411,7 +411,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C1" t="str">
         <v>Дата выгрузки</v>
@@ -638,13 +638,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E2" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/d5/59/68ab6975-901a-4e04-b812-11a05618dea7.jpg</v>
@@ -653,7 +653,7 @@
         <v>Шампунь для кудрявых волос</v>
       </c>
       <c r="G2" t="str">
-        <v>4,640,523,970,310</v>
+        <v>4 640 523 970 310</v>
       </c>
       <c r="H2" t="str">
         <v>АЛТЕЯ</v>
@@ -680,37 +680,37 @@
         <v>Нет</v>
       </c>
       <c r="P2" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="str">
-        <v>0</v>
+        <v>1234</v>
       </c>
       <c r="R2" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="str">
-        <v>1259</v>
+        <v>642</v>
       </c>
       <c r="U2" t="str">
         <v>154</v>
       </c>
       <c r="V2" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" t="str">
-        <v>0</v>
+        <v>1234</v>
       </c>
       <c r="X2" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="str">
-        <v>1259</v>
+        <v>642</v>
       </c>
       <c r="AA2" t="str">
         <v>154</v>
@@ -865,34 +865,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E3" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c7280d72-d323-4237-947d-4008c0dc7662.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e00a36c6-60d1-4483-9902-255f85130f9e.jpg</v>
       </c>
       <c r="F3" t="str">
-        <v>Сыворотка для лица с микроиглами и коллагеном</v>
+        <v>Гелевая маска для лица со спикулами 3000 ppm и микроиглами</v>
       </c>
       <c r="G3" t="str">
-        <v>4,630,446,231,421</v>
+        <v>4 660 417 421 858</v>
       </c>
       <c r="H3" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I3" t="str">
-        <v>MPL589408</v>
+        <v>MPL589441</v>
       </c>
       <c r="J3" t="str">
-        <v>spiculboost_30ml</v>
+        <v>spicul_gel_mask_75ml</v>
       </c>
       <c r="K3" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Маска для лица</v>
       </c>
       <c r="L3" t="str">
         <v>В продаже</v>
@@ -907,40 +907,40 @@
         <v>Нет</v>
       </c>
       <c r="P3" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="str">
-        <v>0</v>
+        <v>727</v>
       </c>
       <c r="R3" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="str">
-        <v>1368</v>
+        <v>750</v>
       </c>
       <c r="U3" t="str">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="V3" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="str">
-        <v>0</v>
+        <v>727</v>
       </c>
       <c r="X3" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="str">
-        <v>1368</v>
+        <v>750</v>
       </c>
       <c r="AA3" t="str">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AB3" t="str">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="BW3" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1092,34 +1092,34 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E4" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/f1/ab/41252906-b46d-4d89-958f-c65e501f9426.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c7280d72-d323-4237-947d-4008c0dc7662.jpg</v>
       </c>
       <c r="F4" t="str">
-        <v>Бальзам для кудрявых волос с кератином</v>
+        <v>Сыворотка для лица с микроиглами и коллагеном</v>
       </c>
       <c r="G4" t="str">
-        <v>4,640,523,970,327</v>
+        <v>4 630 446 231 421</v>
       </c>
       <c r="H4" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I4" t="str">
-        <v>MPL586944</v>
+        <v>MPL589408</v>
       </c>
       <c r="J4" t="str">
-        <v>balzam_kudryavii_metod_500ml</v>
+        <v>spiculboost_30ml</v>
       </c>
       <c r="K4" t="str">
-        <v>Бальзам для укладки волос</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L4" t="str">
         <v>В продаже</v>
@@ -1134,40 +1134,40 @@
         <v>Нет</v>
       </c>
       <c r="P4" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="str">
-        <v>1161</v>
+        <v>0</v>
       </c>
       <c r="R4" t="str">
+        <v>0</v>
+      </c>
+      <c r="S4" t="str">
         <v>2</v>
       </c>
-      <c r="S4" t="str">
-        <v>0</v>
-      </c>
       <c r="T4" t="str">
-        <v>0</v>
+        <v>1454</v>
       </c>
       <c r="U4" t="str">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="V4" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="str">
-        <v>1161</v>
+        <v>0</v>
       </c>
       <c r="X4" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="str">
         <v>2</v>
       </c>
-      <c r="Y4" t="str">
-        <v>0</v>
-      </c>
       <c r="Z4" t="str">
-        <v>0</v>
+        <v>1454</v>
       </c>
       <c r="AA4" t="str">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="str">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="BW4" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1319,34 +1319,34 @@
         <v>1</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E5" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2f576c8d-8046-4678-878e-b25637ae380b.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/f1/ab/41252906-b46d-4d89-958f-c65e501f9426.jpg</v>
       </c>
       <c r="F5" t="str">
-        <v>Крем для Лица с Липосомальным Ретинолом 1.5% Ретинайт</v>
+        <v>Бальзам для кудрявых волос с кератином</v>
       </c>
       <c r="G5" t="str">
-        <v>4,660,417,421,827</v>
+        <v>4 640 523 970 327</v>
       </c>
       <c r="H5" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I5" t="str">
-        <v>MPL583160</v>
+        <v>MPL586944</v>
       </c>
       <c r="J5" t="str">
-        <v>retinait_krem_1_5_50ml</v>
+        <v>balzam_kudryavii_metod_500ml</v>
       </c>
       <c r="K5" t="str">
-        <v>Крем для лица</v>
+        <v>Бальзам для укладки волос</v>
       </c>
       <c r="L5" t="str">
         <v>В продаже</v>
@@ -1361,40 +1361,40 @@
         <v>Нет</v>
       </c>
       <c r="P5" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="str">
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="R5" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="str">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="U5" t="str">
-        <v>281</v>
+        <v>111</v>
       </c>
       <c r="V5" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="str">
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="X5" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="str">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="str">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="AB5" t="str">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="BW5" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1546,34 +1546,34 @@
         <v>1</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E6" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/cb/7a/6d9ba164-a17b-43f1-9832-48efe4aabf92.png</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2f576c8d-8046-4678-878e-b25637ae380b.jpg</v>
       </c>
       <c r="F6" t="str">
-        <v>Сыворотка для лица с ниацинамидом для лица антивозрастная, от пигментных пятен, пигментации</v>
+        <v>Крем для Лица с Липосомальным Ретинолом 1.5% Ретинайт</v>
       </c>
       <c r="G6" t="str">
-        <v>4,603,312,714,069</v>
+        <v>4 660 417 421 827</v>
       </c>
       <c r="H6" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I6" t="str">
-        <v>MPL583154</v>
+        <v>MPL583160</v>
       </c>
       <c r="J6" t="str">
-        <v>syvorotka_dlya_lica_30ml_v2</v>
+        <v>retinait_krem_1_5_50ml</v>
       </c>
       <c r="K6" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L6" t="str">
         <v>В продаже</v>
@@ -1588,40 +1588,40 @@
         <v>Нет</v>
       </c>
       <c r="P6" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="str">
-        <v>1168</v>
+        <v>0</v>
       </c>
       <c r="R6" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T6" t="str">
-        <v>0</v>
+        <v>2757</v>
       </c>
       <c r="U6" t="str">
-        <v>95</v>
+        <v>280</v>
       </c>
       <c r="V6" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="str">
-        <v>1168</v>
+        <v>0</v>
       </c>
       <c r="X6" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="str">
-        <v>0</v>
+        <v>2757</v>
       </c>
       <c r="AA6" t="str">
-        <v>95</v>
+        <v>279</v>
       </c>
       <c r="AB6" t="str">
         <v>0</v>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="BW6" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1773,34 +1773,34 @@
         <v>1</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E7" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2b6f374c-300f-4096-bce3-74be8e0aae55.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/2e/9e/71e42c30-4aa3-44ff-b62c-44b50cfdfa3a.png</v>
       </c>
       <c r="F7" t="str">
-        <v>Сыворотка с ретинолом 0,25% для лица от морщин антивозрастная</v>
+        <v>Крем солнцезащитный для лица</v>
       </c>
       <c r="G7" t="str">
-        <v>4,640,523,970,099</v>
+        <v>4 660 417 421 766</v>
       </c>
       <c r="H7" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I7" t="str">
-        <v>MPL580332</v>
+        <v>MPL583158</v>
       </c>
       <c r="J7" t="str">
-        <v>retinait_syvorotka_025_30ml</v>
+        <v>krem_spf50_50ml</v>
       </c>
       <c r="K7" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Солнцезащитный крем для лица</v>
       </c>
       <c r="L7" t="str">
         <v>В продаже</v>
@@ -1818,10 +1818,10 @@
         <v>1</v>
       </c>
       <c r="Q7" t="str">
-        <v>750</v>
+        <v>605</v>
       </c>
       <c r="R7" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="str">
         <v>0</v>
@@ -1830,16 +1830,16 @@
         <v>0</v>
       </c>
       <c r="U7" t="str">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="V7" t="str">
         <v>1</v>
       </c>
       <c r="W7" t="str">
-        <v>750</v>
+        <v>605</v>
       </c>
       <c r="X7" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="str">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="AA7" t="str">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="AB7" t="str">
         <v>0</v>
@@ -2000,34 +2000,34 @@
         <v>1</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E8" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/d9/54/8d4a32cd-2f2a-4689-a8a5-82e0abc22ea3.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2b6f374c-300f-4096-bce3-74be8e0aae55.jpg</v>
       </c>
       <c r="F8" t="str">
-        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз</v>
+        <v>Сыворотка с ретинолом 0,25% для лица от морщин антивозрастная</v>
       </c>
       <c r="G8" t="str">
-        <v>4,660,417,421,636</v>
+        <v>4 640 523 970 099</v>
       </c>
       <c r="H8" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I8" t="str">
-        <v>MPL580318</v>
+        <v>MPL580332</v>
       </c>
       <c r="J8" t="str">
-        <v>retinol_boost_krem_dlya_vek_30ml</v>
+        <v>retinait_syvorotka_025_30ml</v>
       </c>
       <c r="K8" t="str">
-        <v>Крем для глаз</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L8" t="str">
         <v>В продаже</v>
@@ -2042,40 +2042,40 @@
         <v>Нет</v>
       </c>
       <c r="P8" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="str">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="R8" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S8" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="str">
-        <v>2194</v>
+        <v>1672</v>
       </c>
       <c r="U8" t="str">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="V8" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="str">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="X8" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="str">
-        <v>2194</v>
+        <v>1672</v>
       </c>
       <c r="AA8" t="str">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="AB8" t="str">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="BW8" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2227,34 +2227,34 @@
         <v>1</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E9" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/7af399db-987f-4537-8f7c-c33e02778178.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e15e1be0-e1f4-4e80-9e76-e8fc23c616c9.jpg</v>
       </c>
       <c r="F9" t="str">
-        <v>Крем для лица с ретинолом и церамидами Ретинайт</v>
+        <v>Сыворотка для лица ниацинамидом 5% от прыщей и акне антивозрастная от пигментных пятен</v>
       </c>
       <c r="G9" t="str">
-        <v>4,660,417,421,629</v>
+        <v>4 640 523 970 297</v>
       </c>
       <c r="H9" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I9" t="str">
-        <v>MPL570692</v>
+        <v>MPL580326</v>
       </c>
       <c r="J9" t="str">
-        <v>retinait_krem_01_50ml</v>
+        <v>syvorotka_niacin_05_30ml</v>
       </c>
       <c r="K9" t="str">
-        <v>Крем для лица</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L9" t="str">
         <v>В продаже</v>
@@ -2272,37 +2272,37 @@
         <v>1</v>
       </c>
       <c r="Q9" t="str">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="R9" t="str">
         <v>0</v>
       </c>
       <c r="S9" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="str">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="U9" t="str">
-        <v>195</v>
+        <v>113</v>
       </c>
       <c r="V9" t="str">
         <v>1</v>
       </c>
       <c r="W9" t="str">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="X9" t="str">
         <v>0</v>
       </c>
       <c r="Y9" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="str">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="AA9" t="str">
-        <v>191</v>
+        <v>112</v>
       </c>
       <c r="AB9" t="str">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="AG9" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="str">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="BW9" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2454,34 +2454,34 @@
         <v>1</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E10" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/62/50/b959c799-edb3-4886-ab19-732ee8a7f4d6.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/d9/54/8d4a32cd-2f2a-4689-a8a5-82e0abc22ea3.jpg</v>
       </c>
       <c r="F10" t="str">
-        <v>Гель для бритья мужской охлаждающий с ментолом</v>
+        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз</v>
       </c>
       <c r="G10" t="str">
-        <v>4,603,320,465,458</v>
+        <v>4 660 417 421 636</v>
       </c>
       <c r="H10" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I10" t="str">
-        <v>MPL553832</v>
+        <v>MPL580318</v>
       </c>
       <c r="J10" t="str">
-        <v>gel_dlya_britya_300ml</v>
+        <v>retinol_boost_krem_dlya_vek_30ml</v>
       </c>
       <c r="K10" t="str">
-        <v>Гель для бритья</v>
+        <v>Крем для глаз</v>
       </c>
       <c r="L10" t="str">
         <v>В продаже</v>
@@ -2496,40 +2496,40 @@
         <v>Нет</v>
       </c>
       <c r="P10" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="str">
-        <v>556</v>
+        <v>3000</v>
       </c>
       <c r="R10" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S10" t="str">
         <v>1</v>
       </c>
       <c r="T10" t="str">
-        <v>445</v>
+        <v>765</v>
       </c>
       <c r="U10" t="str">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="V10" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W10" t="str">
-        <v>556</v>
+        <v>3000</v>
       </c>
       <c r="X10" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="str">
         <v>1</v>
       </c>
       <c r="Z10" t="str">
-        <v>445</v>
+        <v>765</v>
       </c>
       <c r="AA10" t="str">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="AB10" t="str">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="BW10" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2681,34 +2681,34 @@
         <v>1</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E11" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2f7a7537-5358-4736-b3fc-a56a54b2e6b9.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/7af399db-987f-4537-8f7c-c33e02778178.jpg</v>
       </c>
       <c r="F11" t="str">
-        <v>Сыворотка для роста ресниц и бровей, гель для роста</v>
+        <v>Крем для лица с ретинолом и церамидами Ретинайт</v>
       </c>
       <c r="G11" t="str">
-        <v>4,656,738,598,843</v>
+        <v>4 660 417 421 629</v>
       </c>
       <c r="H11" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I11" t="str">
-        <v>MPL536269</v>
+        <v>MPL570692</v>
       </c>
       <c r="J11" t="str">
-        <v>syvorotka_dlya_rosta_6ml_v2</v>
+        <v>retinait_krem_01_50ml</v>
       </c>
       <c r="K11" t="str">
-        <v>Гель для роста ресниц и бровей</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L11" t="str">
         <v>В продаже</v>
@@ -2723,40 +2723,40 @@
         <v>Нет</v>
       </c>
       <c r="P11" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="str">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="R11" t="str">
         <v>1</v>
       </c>
       <c r="S11" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11" t="str">
-        <v>0</v>
+        <v>1776</v>
       </c>
       <c r="U11" t="str">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="V11" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="str">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="X11" t="str">
         <v>1</v>
       </c>
       <c r="Y11" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="str">
-        <v>0</v>
+        <v>1776</v>
       </c>
       <c r="AA11" t="str">
-        <v>112</v>
+        <v>188</v>
       </c>
       <c r="AB11" t="str">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="str">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="BQ11" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="str">
         <v>0</v>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="BW11" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2908,34 +2908,34 @@
         <v>1</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E12" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/95/1a/6dd84ed9-0dab-4ad2-8e72-ae7d1736952d.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/62/50/b959c799-edb3-4886-ab19-732ee8a7f4d6.jpg</v>
       </c>
       <c r="F12" t="str">
-        <v>Пенка для укладки кудрявых волос</v>
+        <v>Гель для бритья мужской охлаждающий с ментолом</v>
       </c>
       <c r="G12" t="str">
-        <v>4,670,020,498,611</v>
+        <v>4 603 320 465 458</v>
       </c>
       <c r="H12" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I12" t="str">
-        <v>MPL534436</v>
+        <v>MPL553832</v>
       </c>
       <c r="J12" t="str">
-        <v>penka_kudryavii_metod_150ml</v>
+        <v>gel_dlya_britya_300ml</v>
       </c>
       <c r="K12" t="str">
-        <v>Мусс для укладки волос</v>
+        <v>Гель для бритья</v>
       </c>
       <c r="L12" t="str">
         <v>В продаже</v>
@@ -2950,46 +2950,46 @@
         <v>Нет</v>
       </c>
       <c r="P12" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="str">
-        <v>2430</v>
+        <v>556</v>
       </c>
       <c r="R12" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="str">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="U12" t="str">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="V12" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W12" t="str">
-        <v>1854</v>
+        <v>556</v>
       </c>
       <c r="X12" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="str">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="str">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="str">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="str">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="str">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="AS12" t="str">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="str">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="BK12" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="str">
         <v>0</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="BW12" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3135,34 +3135,34 @@
         <v>1</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E13" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/4822bd34-9fce-40b0-9167-bf7265647db0.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/bc1165dc-d231-4cf6-a720-915675cd6e42.jpg</v>
       </c>
       <c r="F13" t="str">
-        <v>Скраб пилинг для кожи головы</v>
+        <v>Воск стик для укладки и фиксации волос</v>
       </c>
       <c r="G13" t="str">
-        <v>4,660,417,421,476</v>
+        <v>4 670 207 150 196</v>
       </c>
       <c r="H13" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I13" t="str">
-        <v>MPL534263</v>
+        <v>MPL553766</v>
       </c>
       <c r="J13" t="str">
-        <v>skrab_babl_gam_200ml</v>
+        <v>vosk_stik_15ml</v>
       </c>
       <c r="K13" t="str">
-        <v>Скраб для кожи головы</v>
+        <v>Воск для укладки волос</v>
       </c>
       <c r="L13" t="str">
         <v>В продаже</v>
@@ -3177,40 +3177,40 @@
         <v>Нет</v>
       </c>
       <c r="P13" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="str">
-        <v>556</v>
+        <v>0</v>
       </c>
       <c r="R13" t="str">
         <v>0</v>
       </c>
       <c r="S13" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T13" t="str">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="U13" t="str">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="V13" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="str">
-        <v>556</v>
+        <v>0</v>
       </c>
       <c r="X13" t="str">
         <v>0</v>
       </c>
       <c r="Y13" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="str">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="AA13" t="str">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AB13" t="str">
         <v>0</v>
@@ -3228,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="AG13" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="str">
         <v>0</v>
@@ -3362,34 +3362,34 @@
         <v>1</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E14" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c90ca866-48a4-4af9-8f17-1af620906883.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/95/1a/6dd84ed9-0dab-4ad2-8e72-ae7d1736952d.jpg</v>
       </c>
       <c r="F14" t="str">
-        <v>Крем для век и кожи вокруг глаз</v>
+        <v>Пенка для укладки кудрявых волос</v>
       </c>
       <c r="G14" t="str">
-        <v>4,670,020,498,918</v>
+        <v>4 670 020 498 611</v>
       </c>
       <c r="H14" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I14" t="str">
-        <v>MPL534118</v>
+        <v>MPL534436</v>
       </c>
       <c r="J14" t="str">
-        <v>krem_dlya_vek_30ml</v>
+        <v>penka_kudryavii_metod_150ml</v>
       </c>
       <c r="K14" t="str">
-        <v>Крем для лица</v>
+        <v>Мусс для укладки волос</v>
       </c>
       <c r="L14" t="str">
         <v>В продаже</v>
@@ -3404,28 +3404,28 @@
         <v>Нет</v>
       </c>
       <c r="P14" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q14" t="str">
-        <v>0</v>
+        <v>3843</v>
       </c>
       <c r="R14" t="str">
         <v>1</v>
       </c>
       <c r="S14" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="str">
-        <v>1254</v>
+        <v>1691</v>
       </c>
       <c r="U14" t="str">
-        <v>203</v>
+        <v>85</v>
       </c>
       <c r="V14" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W14" t="str">
-        <v>0</v>
+        <v>3843</v>
       </c>
       <c r="X14" t="str">
         <v>1</v>
@@ -3434,10 +3434,10 @@
         <v>2</v>
       </c>
       <c r="Z14" t="str">
-        <v>1254</v>
+        <v>1115</v>
       </c>
       <c r="AA14" t="str">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="AB14" t="str">
         <v>0</v>
@@ -3449,50 +3449,50 @@
         <v>0</v>
       </c>
       <c r="AE14" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="str">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="AG14" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="str">
         <v>5</v>
       </c>
-      <c r="AH14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="str">
-        <v>1</v>
-      </c>
       <c r="AT14" t="str">
         <v>0</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ14" t="str">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="BK14" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL14" t="str">
         <v>0</v>
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="BQ14" t="str">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="str">
         <v>0</v>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="BW14" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3589,34 +3589,34 @@
         <v>1</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E15" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9a2f609a-6b3f-4324-872d-a6560c803def.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/54713ce5-1bd3-4ba5-80d2-781e1b551420.jpg</v>
       </c>
       <c r="F15" t="str">
-        <v>Крем для лица с липосомальным ретинолом 1% Ретинайт</v>
+        <v>Антицеллюитный крем гель для тела от целлюлита</v>
       </c>
       <c r="G15" t="str">
-        <v>4,660,417,421,605</v>
+        <v>4 603 320 465 427</v>
       </c>
       <c r="H15" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I15" t="str">
-        <v>MPL532549</v>
+        <v>MPL534369</v>
       </c>
       <c r="J15" t="str">
-        <v>retinait_krem_1_50ml</v>
+        <v>krem_buster_250ml</v>
       </c>
       <c r="K15" t="str">
-        <v>Крем для лица</v>
+        <v>Крем для тела</v>
       </c>
       <c r="L15" t="str">
         <v>В продаже</v>
@@ -3631,40 +3631,40 @@
         <v>Нет</v>
       </c>
       <c r="P15" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="str">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="R15" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="str">
         <v>2</v>
       </c>
       <c r="T15" t="str">
-        <v>1594</v>
+        <v>804</v>
       </c>
       <c r="U15" t="str">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="V15" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" t="str">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="X15" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="str">
         <v>2</v>
       </c>
       <c r="Z15" t="str">
-        <v>1594</v>
+        <v>804</v>
       </c>
       <c r="AA15" t="str">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="AB15" t="str">
         <v>0</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AH15" t="str">
         <v>0</v>
@@ -3718,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="AS15" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AT15" t="str">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="BK15" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BL15" t="str">
         <v>0</v>
@@ -3790,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="BQ15" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BR15" t="str">
         <v>0</v>
@@ -3816,31 +3816,31 @@
         <v>1</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E16" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/ff447efc-130b-40a7-baf9-b3f41132e53d.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c90ca866-48a4-4af9-8f17-1af620906883.jpg</v>
       </c>
       <c r="F16" t="str">
-        <v>Крем для лица с липосомальным ретинолом 0,25% Ретинайт</v>
+        <v>Крем для век и кожи вокруг глаз</v>
       </c>
       <c r="G16" t="str">
-        <v>4,660,417,421,599</v>
+        <v>4 670 020 498 918</v>
       </c>
       <c r="H16" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I16" t="str">
-        <v>MPL532421</v>
+        <v>MPL534118</v>
       </c>
       <c r="J16" t="str">
-        <v>retinait_krem_025_50ml</v>
+        <v>krem_dlya_vek_30ml</v>
       </c>
       <c r="K16" t="str">
         <v>Крем для лица</v>
@@ -3858,40 +3858,40 @@
         <v>Нет</v>
       </c>
       <c r="P16" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="str">
-        <v>2018</v>
+        <v>1220</v>
       </c>
       <c r="R16" t="str">
         <v>0</v>
       </c>
       <c r="S16" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="str">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="U16" t="str">
-        <v>147</v>
+        <v>204</v>
       </c>
       <c r="V16" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W16" t="str">
-        <v>2018</v>
+        <v>1220</v>
       </c>
       <c r="X16" t="str">
         <v>0</v>
       </c>
       <c r="Y16" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="str">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="AA16" t="str">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="AB16" t="str">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH16" t="str">
         <v>0</v>
@@ -3927,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="AM16" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="str">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="AS16" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AT16" t="str">
         <v>0</v>
@@ -4017,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="BQ16" t="str">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="str">
         <v>0</v>
@@ -4043,34 +4043,34 @@
         <v>1</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E17" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/1b3a299f-fa04-4897-8bd6-2f2523fa8458.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/7b62942f-efab-4a37-bf26-4b4d44ac08ad.jpg</v>
       </c>
       <c r="F17" t="str">
-        <v>Крем точечный против прыщей, акне, комедонов, угрей и черных точек</v>
+        <v>Сыворотка с ретинолом 1% для лица от морщин антивозрастная</v>
       </c>
       <c r="G17" t="str">
-        <v>4,660,417,420,110</v>
+        <v>4 603 320 465 403</v>
       </c>
       <c r="H17" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I17" t="str">
-        <v>MPL497134</v>
+        <v>MPL533706</v>
       </c>
       <c r="J17" t="str">
-        <v>gel_antiakne_20ml_v2</v>
+        <v>retinait_syvorotka_1_30ml</v>
       </c>
       <c r="K17" t="str">
-        <v>Крем для лица</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L17" t="str">
         <v>В продаже</v>
@@ -4085,166 +4085,166 @@
         <v>Нет</v>
       </c>
       <c r="P17" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="str">
-        <v>2393</v>
+        <v>1314</v>
       </c>
       <c r="R17" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="str">
+        <v>0</v>
+      </c>
+      <c r="T17" t="str">
+        <v>0</v>
+      </c>
+      <c r="U17" t="str">
         <v>2</v>
       </c>
-      <c r="T17" t="str">
-        <v>956</v>
-      </c>
-      <c r="U17" t="str">
-        <v>90</v>
-      </c>
       <c r="V17" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W17" t="str">
-        <v>2393</v>
+        <v>1314</v>
       </c>
       <c r="X17" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="str">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="str">
         <v>2</v>
-      </c>
-      <c r="Z17" t="str">
-        <v>956</v>
-      </c>
-      <c r="AA17" t="str">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="str">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BL17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BM17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BN17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BO17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BP17" t="str">
-        <v>0</v>
-      </c>
-      <c r="BQ17" t="str">
-        <v>8</v>
       </c>
       <c r="BR17" t="str">
         <v>0</v>
@@ -4270,34 +4270,34 @@
         <v>1</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E18" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3dab943a-3db8-4732-a73e-22565b77500f.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9a2f609a-6b3f-4324-872d-a6560c803def.jpg</v>
       </c>
       <c r="F18" t="str">
-        <v>Спрей для роста и от выпадения волос</v>
+        <v>Крем для лица с липосомальным ретинолом 1% Ретинайт</v>
       </c>
       <c r="G18" t="str">
-        <v>4,603,320,465,359</v>
+        <v>4 660 417 421 605</v>
       </c>
       <c r="H18" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I18" t="str">
-        <v>MPL484941</v>
+        <v>MPL532549</v>
       </c>
       <c r="J18" t="str">
-        <v>sprei_buster_100ml</v>
+        <v>retinait_krem_1_50ml</v>
       </c>
       <c r="K18" t="str">
-        <v>Спрей для ухода за волосами</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L18" t="str">
         <v>В продаже</v>
@@ -4312,40 +4312,40 @@
         <v>Нет</v>
       </c>
       <c r="P18" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="str">
-        <v>1515</v>
+        <v>1688</v>
       </c>
       <c r="R18" t="str">
         <v>2</v>
       </c>
       <c r="S18" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T18" t="str">
-        <v>1808</v>
+        <v>775</v>
       </c>
       <c r="U18" t="str">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="V18" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W18" t="str">
-        <v>1515</v>
+        <v>1688</v>
       </c>
       <c r="X18" t="str">
         <v>2</v>
       </c>
       <c r="Y18" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="str">
-        <v>1808</v>
+        <v>775</v>
       </c>
       <c r="AA18" t="str">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="AB18" t="str">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="AG18" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AH18" t="str">
         <v>0</v>
@@ -4381,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="AM18" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN18" t="str">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AS18" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AT18" t="str">
         <v>0</v>
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="BK18" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BL18" t="str">
         <v>0</v>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="BQ18" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BR18" t="str">
         <v>0</v>
@@ -4497,34 +4497,34 @@
         <v>1</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E19" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c244b0f9-e819-4adb-bd5b-f607dbc0cf04.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/ff447efc-130b-40a7-baf9-b3f41132e53d.jpg</v>
       </c>
       <c r="F19" t="str">
-        <v>Крем для кудрявых и вьющихся волос</v>
+        <v>Крем для лица с липосомальным ретинолом 0,25% Ретинайт</v>
       </c>
       <c r="G19" t="str">
-        <v>4,603,320,465,441</v>
+        <v>4 660 417 421 599</v>
       </c>
       <c r="H19" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I19" t="str">
-        <v>MPL483098</v>
+        <v>MPL532421</v>
       </c>
       <c r="J19" t="str">
-        <v>curly_method_300ml</v>
+        <v>retinait_krem_025_50ml</v>
       </c>
       <c r="K19" t="str">
-        <v>Крем для укладки волос</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L19" t="str">
         <v>В продаже</v>
@@ -4539,46 +4539,46 @@
         <v>Нет</v>
       </c>
       <c r="P19" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="str">
-        <v>4061</v>
+        <v>699</v>
       </c>
       <c r="R19" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S19" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T19" t="str">
-        <v>1926</v>
+        <v>699</v>
       </c>
       <c r="U19" t="str">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="V19" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W19" t="str">
-        <v>3418</v>
+        <v>699</v>
       </c>
       <c r="X19" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="str">
-        <v>1926</v>
+        <v>699</v>
       </c>
       <c r="AA19" t="str">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="str">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="str">
         <v>0</v>
@@ -4608,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="AM19" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN19" t="str">
         <v>0</v>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="AS19" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT19" t="str">
         <v>0</v>
@@ -4662,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="BE19" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="str">
         <v>0</v>
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="BK19" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL19" t="str">
         <v>0</v>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="BQ19" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BR19" t="str">
         <v>0</v>
@@ -4724,34 +4724,34 @@
         <v>1</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E20" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/fc7f937b-2361-418e-ae9f-3918b47523d7.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/1b3a299f-fa04-4897-8bd6-2f2523fa8458.jpg</v>
       </c>
       <c r="F20" t="str">
-        <v>Разглаживающий крем для волос, для непослушных или кудрявых волос для кончиков</v>
+        <v>Крем точечный против прыщей, акне, комедонов, угрей и черных точек</v>
       </c>
       <c r="G20" t="str">
-        <v>4,603,320,465,465</v>
+        <v>4 660 417 420 110</v>
       </c>
       <c r="H20" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I20" t="str">
-        <v>MPL477653</v>
+        <v>MPL497134</v>
       </c>
       <c r="J20" t="str">
-        <v>silk_hair_300ml</v>
+        <v>gel_antiakne_20ml_v2</v>
       </c>
       <c r="K20" t="str">
-        <v>Крем для укладки волос</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L20" t="str">
         <v>В продаже</v>
@@ -4766,40 +4766,40 @@
         <v>Нет</v>
       </c>
       <c r="P20" t="str">
+        <v>4</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>1532</v>
+      </c>
+      <c r="R20" t="str">
         <v>3</v>
       </c>
-      <c r="Q20" t="str">
-        <v>1356</v>
-      </c>
-      <c r="R20" t="str">
-        <v>1</v>
-      </c>
       <c r="S20" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T20" t="str">
-        <v>476</v>
+        <v>2782</v>
       </c>
       <c r="U20" t="str">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="V20" t="str">
         <v>3</v>
       </c>
       <c r="W20" t="str">
-        <v>1356</v>
+        <v>1149</v>
       </c>
       <c r="X20" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z20" t="str">
-        <v>476</v>
+        <v>2782</v>
       </c>
       <c r="AA20" t="str">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="AB20" t="str">
         <v>0</v>
@@ -4817,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="AG20" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="str">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AM20" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="str">
         <v>0</v>
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="AS20" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="str">
         <v>0</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="BE20" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="str">
         <v>0</v>
@@ -4907,13 +4907,13 @@
         <v>0</v>
       </c>
       <c r="BK20" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL20" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM20" t="str">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="BN20" t="str">
         <v>0</v>
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="BQ20" t="str">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BR20" t="str">
         <v>0</v>
@@ -4943,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="BW20" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4951,34 +4951,34 @@
         <v>1</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E21" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9c79f9bf-96d6-4540-9aab-14f3a9799933.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3dab943a-3db8-4732-a73e-22565b77500f.jpg</v>
       </c>
       <c r="F21" t="str">
-        <v>Кровавый кислотный пилинг для лица от прыщей с Альфа и бета-гидроксикислотами</v>
+        <v>Спрей для роста и от выпадения волос</v>
       </c>
       <c r="G21" t="str">
-        <v>4,670,020,498,208</v>
+        <v>4 603 320 465 359</v>
       </c>
       <c r="H21" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I21" t="str">
-        <v>MPL411098</v>
+        <v>MPL484941</v>
       </c>
       <c r="J21" t="str">
-        <v>krovavii_piling_30ml</v>
+        <v>sprei_buster_100ml</v>
       </c>
       <c r="K21" t="str">
-        <v>Пилинг для лица</v>
+        <v>Спрей для ухода за волосами</v>
       </c>
       <c r="L21" t="str">
         <v>В продаже</v>
@@ -4993,40 +4993,40 @@
         <v>Нет</v>
       </c>
       <c r="P21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="str">
-        <v>513</v>
+        <v>1010</v>
       </c>
       <c r="R21" t="str">
+        <v>1</v>
+      </c>
+      <c r="S21" t="str">
+        <v>0</v>
+      </c>
+      <c r="T21" t="str">
+        <v>0</v>
+      </c>
+      <c r="U21" t="str">
+        <v>84</v>
+      </c>
+      <c r="V21" t="str">
         <v>2</v>
       </c>
-      <c r="S21" t="str">
-        <v>2</v>
-      </c>
-      <c r="T21" t="str">
-        <v>1012</v>
-      </c>
-      <c r="U21" t="str">
-        <v>220</v>
-      </c>
-      <c r="V21" t="str">
-        <v>1</v>
-      </c>
       <c r="W21" t="str">
-        <v>513</v>
+        <v>1010</v>
       </c>
       <c r="X21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="str">
-        <v>1012</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="str">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="AB21" t="str">
         <v>0</v>
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="AG21" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH21" t="str">
         <v>0</v>
@@ -5062,25 +5062,25 @@
         <v>0</v>
       </c>
       <c r="AM21" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="str">
         <v>4</v>
-      </c>
-      <c r="AN21" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="str">
-        <v>6</v>
       </c>
       <c r="AT21" t="str">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="BK21" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BL21" t="str">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="BQ21" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BR21" t="str">
         <v>0</v>
@@ -5178,34 +5178,34 @@
         <v>1</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E22" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/44834e6a-6c3a-4072-80b2-89989f472f81.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c244b0f9-e819-4adb-bd5b-f607dbc0cf04.jpg</v>
       </c>
       <c r="F22" t="str">
-        <v>Маска для роста волос с перцем</v>
+        <v>Крем для кудрявых и вьющихся волос</v>
       </c>
       <c r="G22" t="str">
-        <v>4,603,320,465,366</v>
+        <v>4 603 320 465 441</v>
       </c>
       <c r="H22" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I22" t="str">
-        <v>MPL411097</v>
+        <v>MPL483098</v>
       </c>
       <c r="J22" t="str">
-        <v>maska-batter_dlya_rosta_500ml</v>
+        <v>curly_method_300ml</v>
       </c>
       <c r="K22" t="str">
-        <v>Маска для волос</v>
+        <v>Крем для укладки волос</v>
       </c>
       <c r="L22" t="str">
         <v>В продаже</v>
@@ -5220,40 +5220,40 @@
         <v>Нет</v>
       </c>
       <c r="P22" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="str">
-        <v>497</v>
+        <v>3579</v>
       </c>
       <c r="R22" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S22" t="str">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T22" t="str">
-        <v>0</v>
+        <v>6680</v>
       </c>
       <c r="U22" t="str">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="V22" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W22" t="str">
-        <v>497</v>
+        <v>3579</v>
       </c>
       <c r="X22" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z22" t="str">
-        <v>0</v>
+        <v>6037</v>
       </c>
       <c r="AA22" t="str">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="AB22" t="str">
         <v>0</v>
@@ -5265,10 +5265,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="str">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="AG22" t="str">
         <v>2</v>
@@ -5289,62 +5289,62 @@
         <v>0</v>
       </c>
       <c r="AM22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="str">
+        <v>4</v>
+      </c>
+      <c r="AT22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="str">
         <v>2</v>
       </c>
-      <c r="AN22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="str">
-        <v>2</v>
-      </c>
-      <c r="AT22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE22" t="str">
-        <v>0</v>
-      </c>
       <c r="BF22" t="str">
         <v>0</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>0</v>
       </c>
       <c r="BK22" t="str">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BL22" t="str">
         <v>0</v>
@@ -5379,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="BQ22" t="str">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BR22" t="str">
         <v>0</v>
@@ -5405,34 +5405,34 @@
         <v>1</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E23" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/db6a42fd-0944-471f-966b-32f2132fa06d.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/fc7f937b-2361-418e-ae9f-3918b47523d7.jpg</v>
       </c>
       <c r="F23" t="str">
-        <v>Сыворотка с витамином с, гиалуроновая кислота</v>
+        <v>Разглаживающий крем для волос, для непослушных или кудрявых волос для кончиков</v>
       </c>
       <c r="G23" t="str">
-        <v>4,670,020,498,093</v>
+        <v>4 603 320 465 465</v>
       </c>
       <c r="H23" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I23" t="str">
-        <v>MPL381177</v>
+        <v>MPL477653</v>
       </c>
       <c r="J23" t="str">
-        <v>syvorotka_guk_30ml</v>
+        <v>silk_hair_300ml</v>
       </c>
       <c r="K23" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Крем для укладки волос</v>
       </c>
       <c r="L23" t="str">
         <v>В продаже</v>
@@ -5447,40 +5447,40 @@
         <v>Нет</v>
       </c>
       <c r="P23" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="str">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="R23" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="str">
         <v>1</v>
       </c>
       <c r="T23" t="str">
-        <v>655</v>
+        <v>452</v>
       </c>
       <c r="U23" t="str">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="V23" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" t="str">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="X23" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="str">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="AA23" t="str">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AB23" t="str">
         <v>0</v>
@@ -5498,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="AG23" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH23" t="str">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN23" t="str">
         <v>0</v>
@@ -5528,13 +5528,13 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="str">
-        <v>655</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT23" t="str">
         <v>0</v>
@@ -5552,26 +5552,26 @@
         <v>0</v>
       </c>
       <c r="AY23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="str">
         <v>2</v>
       </c>
-      <c r="AZ23" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="str">
-        <v>1</v>
-      </c>
       <c r="BF23" t="str">
         <v>0</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="BK23" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL23" t="str">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="BQ23" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR23" t="str">
         <v>0</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="BW23" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -5632,34 +5632,34 @@
         <v>1</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E24" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/1e0dc6e9-3db8-4def-b687-323e61f82f64.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e50770dd-caa8-4478-b9f2-0ac1b5692608.jpg</v>
       </c>
       <c r="F24" t="str">
-        <v>Шампунь для роста волос, от выпадения волос профессиональный</v>
+        <v>Тоник для лица от прыщей и черных точек очищающий</v>
       </c>
       <c r="G24" t="str">
-        <v>4,670,020,496,747</v>
+        <v>4 670 020 498 499</v>
       </c>
       <c r="H24" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I24" t="str">
-        <v>MPL381169</v>
+        <v>MPL440013</v>
       </c>
       <c r="J24" t="str">
-        <v>shampun_dlya_rosta_250ml</v>
+        <v>tonik_dlya_lica_200ml</v>
       </c>
       <c r="K24" t="str">
-        <v>Шампунь для волос</v>
+        <v>Тоник для лица</v>
       </c>
       <c r="L24" t="str">
         <v>В продаже</v>
@@ -5674,40 +5674,40 @@
         <v>Нет</v>
       </c>
       <c r="P24" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="str">
-        <v>954</v>
+        <v>0</v>
       </c>
       <c r="R24" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T24" t="str">
-        <v>885</v>
+        <v>288</v>
       </c>
       <c r="U24" t="str">
-        <v>199</v>
+        <v>1</v>
       </c>
       <c r="V24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="str">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="X24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="str">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="str">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="str">
         <v>0</v>
@@ -5725,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="AG24" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="str">
         <v>0</v>
@@ -5737,13 +5737,13 @@
         <v>0</v>
       </c>
       <c r="AK24" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="str">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="AM24" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN24" t="str">
         <v>0</v>
@@ -5761,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="AS24" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="str">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AY24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="str">
         <v>0</v>
@@ -5800,13 +5800,13 @@
         <v>0</v>
       </c>
       <c r="BF24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="str">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="BH24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI24" t="str">
         <v>0</v>
@@ -5815,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="BK24" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL24" t="str">
         <v>0</v>
@@ -5827,13 +5827,13 @@
         <v>0</v>
       </c>
       <c r="BO24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP24" t="str">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="BQ24" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR24" t="str">
         <v>0</v>
@@ -5859,34 +5859,34 @@
         <v>1</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E25" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c2abf989-9fc4-4168-8006-a2f0a7996e13.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/89bcceec-1c50-47a2-8033-c4a8bed335b7.jpg</v>
       </c>
       <c r="F25" t="str">
-        <v>Крем для лица с ретинолом, Ретидерм</v>
+        <v>Гель для бровей с коллагеном и эластином, фиксация на 24 часа</v>
       </c>
       <c r="G25" t="str">
-        <v>4,610,172,186,219</v>
+        <v>4 676 574 657 436</v>
       </c>
       <c r="H25" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I25" t="str">
-        <v>MPL381168</v>
+        <v>MPL411155</v>
       </c>
       <c r="J25" t="str">
-        <v>retiderm_50ml</v>
+        <v>gel_brows_5ml</v>
       </c>
       <c r="K25" t="str">
-        <v>Крем для лица</v>
+        <v>Гель для бровей</v>
       </c>
       <c r="L25" t="str">
         <v>В продаже</v>
@@ -5901,40 +5901,40 @@
         <v>Нет</v>
       </c>
       <c r="P25" t="str">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="str">
-        <v>3005</v>
+        <v>338</v>
       </c>
       <c r="R25" t="str">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="S25" t="str">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T25" t="str">
-        <v>2626</v>
+        <v>0</v>
       </c>
       <c r="U25" t="str">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="V25" t="str">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="W25" t="str">
-        <v>3005</v>
+        <v>338</v>
       </c>
       <c r="X25" t="str">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="str">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="str">
-        <v>2626</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="str">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="AB25" t="str">
         <v>0</v>
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="AG25" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH25" t="str">
         <v>0</v>
@@ -5970,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="AM25" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="str">
         <v>0</v>
@@ -6060,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="BQ25" t="str">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BR25" t="str">
         <v>0</v>
@@ -6086,34 +6086,34 @@
         <v>1</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E26" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3b0cad57-5015-4075-b4f5-949c25941740.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9c79f9bf-96d6-4540-9aab-14f3a9799933.jpg</v>
       </c>
       <c r="F26" t="str">
-        <v>Маска для волос профессиональная с кератином восстанавливающая, бальзам для волос</v>
+        <v>Кровавый кислотный пилинг для лица от прыщей с Альфа и бета-гидроксикислотами</v>
       </c>
       <c r="G26" t="str">
-        <v>4,670,020,497,546</v>
+        <v>4 670 020 498 208</v>
       </c>
       <c r="H26" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I26" t="str">
-        <v>MPL381090</v>
+        <v>MPL411098</v>
       </c>
       <c r="J26" t="str">
-        <v>maska-batter_250ml</v>
+        <v>krovavii_piling_30ml</v>
       </c>
       <c r="K26" t="str">
-        <v>Маска для волос</v>
+        <v>Пилинг для лица</v>
       </c>
       <c r="L26" t="str">
         <v>В продаже</v>
@@ -6128,149 +6128,149 @@
         <v>Нет</v>
       </c>
       <c r="P26" t="str">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>1566</v>
+      </c>
+      <c r="R26" t="str">
+        <v>1</v>
+      </c>
+      <c r="S26" t="str">
+        <v>6</v>
+      </c>
+      <c r="T26" t="str">
+        <v>3351</v>
+      </c>
+      <c r="U26" t="str">
+        <v>209</v>
+      </c>
+      <c r="V26" t="str">
+        <v>3</v>
+      </c>
+      <c r="W26" t="str">
+        <v>1566</v>
+      </c>
+      <c r="X26" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="str">
+        <v>5</v>
+      </c>
+      <c r="Z26" t="str">
+        <v>2838</v>
+      </c>
+      <c r="AA26" t="str">
+        <v>179</v>
+      </c>
+      <c r="AB26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="str">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="str">
+        <v>513</v>
+      </c>
+      <c r="AG26" t="str">
         <v>2</v>
       </c>
-      <c r="Q26" t="str">
-        <v>1105</v>
-      </c>
-      <c r="R26" t="str">
-        <v>0</v>
-      </c>
-      <c r="S26" t="str">
+      <c r="AH26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="str">
+        <v>4</v>
+      </c>
+      <c r="AN26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="str">
+        <v>6</v>
+      </c>
+      <c r="AT26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="str">
         <v>2</v>
       </c>
-      <c r="T26" t="str">
-        <v>954</v>
-      </c>
-      <c r="U26" t="str">
-        <v>150</v>
-      </c>
-      <c r="V26" t="str">
-        <v>1</v>
-      </c>
-      <c r="W26" t="str">
-        <v>628</v>
-      </c>
-      <c r="X26" t="str">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="str">
-        <v>2</v>
-      </c>
-      <c r="Z26" t="str">
-        <v>954</v>
-      </c>
-      <c r="AA26" t="str">
-        <v>132</v>
-      </c>
-      <c r="AB26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="str">
-        <v>1</v>
-      </c>
-      <c r="AH26" t="str">
-        <v>1</v>
-      </c>
-      <c r="AI26" t="str">
-        <v>477</v>
-      </c>
-      <c r="AJ26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="str">
+      <c r="AZ26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="str">
         <v>6</v>
       </c>
-      <c r="AN26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="str">
-        <v>3</v>
-      </c>
-      <c r="AT26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="str">
-        <v>1</v>
-      </c>
-      <c r="AZ26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="str">
-        <v>2</v>
-      </c>
-      <c r="BF26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK26" t="str">
-        <v>2</v>
-      </c>
       <c r="BL26" t="str">
         <v>0</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>0</v>
       </c>
       <c r="BQ26" t="str">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BR26" t="str">
         <v>0</v>
@@ -6313,34 +6313,34 @@
         <v>1</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E27" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/99bc620d-d1e4-4442-99ce-a427a86be9b8.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/44834e6a-6c3a-4072-80b2-89989f472f81.jpg</v>
       </c>
       <c r="F27" t="str">
-        <v>Крем от растяжек для беременных и подростков с эластином</v>
+        <v>Маска для роста волос с перцем</v>
       </c>
       <c r="G27" t="str">
-        <v>4,670,020,497,898</v>
+        <v>4 603 320 465 366</v>
       </c>
       <c r="H27" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I27" t="str">
-        <v>MPL379167</v>
+        <v>MPL411097</v>
       </c>
       <c r="J27" t="str">
-        <v>krem_ot_rastyazhek</v>
+        <v>maska-batter_dlya_rosta_500ml</v>
       </c>
       <c r="K27" t="str">
-        <v>Крем для тела</v>
+        <v>Маска для волос</v>
       </c>
       <c r="L27" t="str">
         <v>В продаже</v>
@@ -6355,40 +6355,40 @@
         <v>Нет</v>
       </c>
       <c r="P27" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="str">
-        <v>1952</v>
+        <v>497</v>
       </c>
       <c r="R27" t="str">
         <v>2</v>
       </c>
       <c r="S27" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T27" t="str">
-        <v>628</v>
+        <v>1628</v>
       </c>
       <c r="U27" t="str">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="V27" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W27" t="str">
-        <v>1952</v>
+        <v>497</v>
       </c>
       <c r="X27" t="str">
         <v>2</v>
       </c>
       <c r="Y27" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z27" t="str">
-        <v>628</v>
+        <v>1628</v>
       </c>
       <c r="AA27" t="str">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="AB27" t="str">
         <v>0</v>
@@ -6406,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="AG27" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="str">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AM27" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN27" t="str">
         <v>0</v>
@@ -6460,7 +6460,7 @@
         <v>0</v>
       </c>
       <c r="AY27" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="str">
         <v>0</v>
@@ -6478,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="BE27" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="str">
         <v>0</v>
@@ -6496,7 +6496,7 @@
         <v>0</v>
       </c>
       <c r="BK27" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BL27" t="str">
         <v>0</v>
@@ -6514,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="BQ27" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BR27" t="str">
         <v>0</v>
@@ -6540,34 +6540,34 @@
         <v>1</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E28" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/fb6b51e2-810a-4d7f-8792-27b4578444b2.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/1e0dc6e9-3db8-4def-b687-323e61f82f64.jpg</v>
       </c>
       <c r="F28" t="str">
-        <v>Крем для лица антивозрастной, крем филлер вокруг глаз, с коллагеном с ниацинамидом</v>
+        <v>Шампунь для роста волос, от выпадения волос профессиональный</v>
       </c>
       <c r="G28" t="str">
-        <v>4,657,786,831,418</v>
+        <v>4 670 020 496 747</v>
       </c>
       <c r="H28" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I28" t="str">
-        <v>MPL379166</v>
+        <v>MPL381169</v>
       </c>
       <c r="J28" t="str">
-        <v>krem-filler_15ml</v>
+        <v>shampun_dlya_rosta_250ml</v>
       </c>
       <c r="K28" t="str">
-        <v>Крем для лица</v>
+        <v>Шампунь для волос</v>
       </c>
       <c r="L28" t="str">
         <v>В продаже</v>
@@ -6585,37 +6585,37 @@
         <v>2</v>
       </c>
       <c r="Q28" t="str">
-        <v>690</v>
+        <v>885</v>
       </c>
       <c r="R28" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S28" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T28" t="str">
-        <v>0</v>
+        <v>1296</v>
       </c>
       <c r="U28" t="str">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="V28" t="str">
         <v>2</v>
       </c>
       <c r="W28" t="str">
-        <v>690</v>
+        <v>885</v>
       </c>
       <c r="X28" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y28" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="str">
-        <v>0</v>
+        <v>819</v>
       </c>
       <c r="AA28" t="str">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="AB28" t="str">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="AG28" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="str">
         <v>0</v>
@@ -6651,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="AM28" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN28" t="str">
         <v>0</v>
@@ -6669,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="AS28" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="str">
         <v>0</v>
@@ -6687,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="AY28" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ28" t="str">
         <v>0</v>
@@ -6717,10 +6717,10 @@
         <v>0</v>
       </c>
       <c r="BI28" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ28" t="str">
-        <v>0</v>
+        <v>477</v>
       </c>
       <c r="BK28" t="str">
         <v>2</v>
@@ -6741,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="BQ28" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BR28" t="str">
         <v>0</v>
@@ -6767,34 +6767,34 @@
         <v>1</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E29" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/00ca3a8d-eecb-4cc4-8710-a0b7ddef9727.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c2abf989-9fc4-4168-8006-a2f0a7996e13.jpg</v>
       </c>
       <c r="F29" t="str">
-        <v>Ламеллярный крем для рук с мочевиной, увлажняющий и питательный с маслом кокоса</v>
+        <v>Крем для лица с ретинолом, Ретидерм</v>
       </c>
       <c r="G29" t="str">
-        <v>4,660,417,421,889</v>
+        <v>4 610 172 186 219</v>
       </c>
       <c r="H29" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I29" t="str">
-        <v>MPL379165</v>
+        <v>MPL381168</v>
       </c>
       <c r="J29" t="str">
-        <v>krem_dlya_ruk_75ml</v>
+        <v>retiderm_50ml</v>
       </c>
       <c r="K29" t="str">
-        <v>Крем для рук</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L29" t="str">
         <v>В продаже</v>
@@ -6809,40 +6809,40 @@
         <v>Нет</v>
       </c>
       <c r="P29" t="str">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Q29" t="str">
-        <v>716</v>
+        <v>4091</v>
       </c>
       <c r="R29" t="str">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="S29" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T29" t="str">
-        <v>1024</v>
+        <v>2685</v>
       </c>
       <c r="U29" t="str">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="V29" t="str">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="W29" t="str">
-        <v>716</v>
+        <v>4091</v>
       </c>
       <c r="X29" t="str">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z29" t="str">
-        <v>1024</v>
+        <v>2685</v>
       </c>
       <c r="AA29" t="str">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="AB29" t="str">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="AG29" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="str">
         <v>0</v>
@@ -6878,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="AM29" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN29" t="str">
         <v>0</v>
@@ -6896,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="AS29" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="str">
         <v>0</v>
@@ -6914,7 +6914,7 @@
         <v>0</v>
       </c>
       <c r="AY29" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="str">
         <v>0</v>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="BK29" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL29" t="str">
         <v>0</v>
@@ -6959,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="BN29" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO29" t="str">
         <v>0</v>
@@ -6968,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="BQ29" t="str">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BR29" t="str">
         <v>0</v>
@@ -6994,34 +6994,34 @@
         <v>1</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E30" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e00a36c6-60d1-4483-9902-255f85130f9e.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3b0cad57-5015-4075-b4f5-949c25941740.jpg</v>
       </c>
       <c r="F30" t="str">
-        <v>Гелевая маска для лица со спикулами 3000 ppm и микроиглами</v>
+        <v>Маска для волос профессиональная с кератином восстанавливающая, бальзам для волос</v>
       </c>
       <c r="G30" t="str">
-        <v>4,660,417,421,858</v>
+        <v>4 670 020 497 546</v>
       </c>
       <c r="H30" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I30" t="str">
-        <v>MPL589441</v>
+        <v>MPL381090</v>
       </c>
       <c r="J30" t="str">
-        <v>spicul_gel_mask_75ml</v>
+        <v>maska-batter_250ml</v>
       </c>
       <c r="K30" t="str">
-        <v>Маска для лица</v>
+        <v>Маска для волос</v>
       </c>
       <c r="L30" t="str">
         <v>В продаже</v>
@@ -7036,113 +7036,113 @@
         <v>Нет</v>
       </c>
       <c r="P30" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="str">
-        <v>0</v>
+        <v>479</v>
       </c>
       <c r="R30" t="str">
+        <v>0</v>
+      </c>
+      <c r="S30" t="str">
+        <v>2</v>
+      </c>
+      <c r="T30" t="str">
+        <v>1123</v>
+      </c>
+      <c r="U30" t="str">
+        <v>146</v>
+      </c>
+      <c r="V30" t="str">
+        <v>0</v>
+      </c>
+      <c r="W30" t="str">
+        <v>0</v>
+      </c>
+      <c r="X30" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="str">
+        <v>646</v>
+      </c>
+      <c r="AA30" t="str">
+        <v>127</v>
+      </c>
+      <c r="AB30" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="str">
+        <v>479</v>
+      </c>
+      <c r="AD30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="str">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="str">
+        <v>477</v>
+      </c>
+      <c r="AM30" t="str">
+        <v>5</v>
+      </c>
+      <c r="AN30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="str">
         <v>3</v>
       </c>
-      <c r="S30" t="str">
-        <v>0</v>
-      </c>
-      <c r="T30" t="str">
-        <v>0</v>
-      </c>
-      <c r="U30" t="str">
-        <v>60</v>
-      </c>
-      <c r="V30" t="str">
-        <v>0</v>
-      </c>
-      <c r="W30" t="str">
-        <v>0</v>
-      </c>
-      <c r="X30" t="str">
+      <c r="AT30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="str">
         <v>3</v>
       </c>
-      <c r="Y30" t="str">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="str">
-        <v>60</v>
-      </c>
-      <c r="AB30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="str">
-        <v>0</v>
-      </c>
       <c r="AZ30" t="str">
         <v>0</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>0</v>
       </c>
       <c r="BE30" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF30" t="str">
         <v>0</v>
@@ -7177,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="BK30" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL30" t="str">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="BQ30" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR30" t="str">
         <v>0</v>
@@ -7221,34 +7221,34 @@
         <v>1</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E31" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/2e/9e/71e42c30-4aa3-44ff-b62c-44b50cfdfa3a.png</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/bbccc824-8896-4e69-bd67-4be5d9a9aaf7.jpg</v>
       </c>
       <c r="F31" t="str">
-        <v>Крем солнцезащитный для лица</v>
+        <v>Крем с мочевиной увлажняющий, 10% мочевина</v>
       </c>
       <c r="G31" t="str">
-        <v>4,660,417,421,766</v>
+        <v>4 611 113 000 977</v>
       </c>
       <c r="H31" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I31" t="str">
-        <v>MPL583158</v>
+        <v>MPL379168</v>
       </c>
       <c r="J31" t="str">
-        <v>krem_spf50_50ml</v>
+        <v>kremshelk_100ml</v>
       </c>
       <c r="K31" t="str">
-        <v>Солнцезащитный крем для лица</v>
+        <v>Крем для тела</v>
       </c>
       <c r="L31" t="str">
         <v>В продаже</v>
@@ -7269,16 +7269,16 @@
         <v>0</v>
       </c>
       <c r="R31" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="str">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="U31" t="str">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="V31" t="str">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>0</v>
       </c>
       <c r="X31" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="str">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="AA31" t="str">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="AB31" t="str">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="BW31" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -7448,34 +7448,34 @@
         <v>1</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E32" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e15e1be0-e1f4-4e80-9e76-e8fc23c616c9.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/99bc620d-d1e4-4442-99ce-a427a86be9b8.jpg</v>
       </c>
       <c r="F32" t="str">
-        <v>Сыворотка для лица ниацинамидом 5% от прыщей и акне антивозрастная от пигментных пятен</v>
+        <v>Крем от растяжек для беременных и подростков с эластином</v>
       </c>
       <c r="G32" t="str">
-        <v>4,640,523,970,297</v>
+        <v>4 670 020 497 898</v>
       </c>
       <c r="H32" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I32" t="str">
-        <v>MPL580326</v>
+        <v>MPL379167</v>
       </c>
       <c r="J32" t="str">
-        <v>syvorotka_niacin_05_30ml</v>
+        <v>krem_ot_rastyazhek</v>
       </c>
       <c r="K32" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Крем для тела</v>
       </c>
       <c r="L32" t="str">
         <v>В продаже</v>
@@ -7490,13 +7490,13 @@
         <v>Нет</v>
       </c>
       <c r="P32" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="str">
-        <v>0</v>
+        <v>1456</v>
       </c>
       <c r="R32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S32" t="str">
         <v>0</v>
@@ -7505,16 +7505,16 @@
         <v>0</v>
       </c>
       <c r="U32" t="str">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="V32" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W32" t="str">
-        <v>0</v>
+        <v>1456</v>
       </c>
       <c r="X32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y32" t="str">
         <v>0</v>
@@ -7523,7 +7523,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="str">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="AB32" t="str">
         <v>0</v>
@@ -7541,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="AG32" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH32" t="str">
         <v>0</v>
@@ -7559,7 +7559,7 @@
         <v>0</v>
       </c>
       <c r="AM32" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN32" t="str">
         <v>0</v>
@@ -7577,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="AS32" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT32" t="str">
         <v>0</v>
@@ -7595,7 +7595,7 @@
         <v>0</v>
       </c>
       <c r="AY32" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ32" t="str">
         <v>0</v>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="BE32" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF32" t="str">
         <v>0</v>
@@ -7631,7 +7631,7 @@
         <v>0</v>
       </c>
       <c r="BK32" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL32" t="str">
         <v>0</v>
@@ -7649,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="BQ32" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BR32" t="str">
         <v>0</v>
@@ -7667,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="BW32" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -7675,34 +7675,34 @@
         <v>1</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E33" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/bc1165dc-d231-4cf6-a720-915675cd6e42.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/00ca3a8d-eecb-4cc4-8710-a0b7ddef9727.jpg</v>
       </c>
       <c r="F33" t="str">
-        <v>Воск стик для укладки и фиксации волос</v>
+        <v>Ламеллярный крем для рук с мочевиной, увлажняющий и питательный с маслом кокоса</v>
       </c>
       <c r="G33" t="str">
-        <v>4,670,207,150,196</v>
+        <v>4 660 417 421 889</v>
       </c>
       <c r="H33" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I33" t="str">
-        <v>MPL553766</v>
+        <v>MPL379165</v>
       </c>
       <c r="J33" t="str">
-        <v>vosk_stik_15ml</v>
+        <v>krem_dlya_ruk_75ml</v>
       </c>
       <c r="K33" t="str">
-        <v>Воск для укладки волос</v>
+        <v>Крем для рук</v>
       </c>
       <c r="L33" t="str">
         <v>В продаже</v>
@@ -7717,28 +7717,28 @@
         <v>Нет</v>
       </c>
       <c r="P33" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="str">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="R33" t="str">
         <v>0</v>
       </c>
       <c r="S33" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="str">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="U33" t="str">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="V33" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" t="str">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="X33" t="str">
         <v>0</v>
@@ -7750,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="AA33" t="str">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="AB33" t="str">
         <v>0</v>
@@ -7762,13 +7762,13 @@
         <v>0</v>
       </c>
       <c r="AE33" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="str">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AG33" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="str">
         <v>0</v>
@@ -7804,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="AS33" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT33" t="str">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="AY33" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ33" t="str">
         <v>0</v>
@@ -7858,7 +7858,7 @@
         <v>0</v>
       </c>
       <c r="BK33" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL33" t="str">
         <v>0</v>
@@ -7876,7 +7876,7 @@
         <v>0</v>
       </c>
       <c r="BQ33" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BR33" t="str">
         <v>0</v>
@@ -7902,34 +7902,34 @@
         <v>1</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E34" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/54713ce5-1bd3-4ba5-80d2-781e1b551420.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/cb/7a/6d9ba164-a17b-43f1-9832-48efe4aabf92.png</v>
       </c>
       <c r="F34" t="str">
-        <v>Антицеллюитный крем гель для тела от целлюлита</v>
+        <v>Сыворотка для лица с ниацинамидом для лица антивозрастная, от пигментных пятен, пигментации</v>
       </c>
       <c r="G34" t="str">
-        <v>4,603,320,465,427</v>
+        <v>4 603 312 714 069</v>
       </c>
       <c r="H34" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I34" t="str">
-        <v>MPL534369</v>
+        <v>MPL583154</v>
       </c>
       <c r="J34" t="str">
-        <v>krem_buster_250ml</v>
+        <v>syvorotka_dlya_lica_30ml_v2</v>
       </c>
       <c r="K34" t="str">
-        <v>Крем для тела</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L34" t="str">
         <v>В продаже</v>
@@ -7950,7 +7950,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S34" t="str">
         <v>0</v>
@@ -7959,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="str">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="V34" t="str">
         <v>0</v>
@@ -7968,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="X34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y34" t="str">
         <v>0</v>
@@ -7977,7 +7977,7 @@
         <v>0</v>
       </c>
       <c r="AA34" t="str">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="AB34" t="str">
         <v>0</v>
@@ -7995,7 +7995,7 @@
         <v>0</v>
       </c>
       <c r="AG34" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="str">
         <v>0</v>
@@ -8013,7 +8013,7 @@
         <v>0</v>
       </c>
       <c r="AM34" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="str">
         <v>0</v>
@@ -8031,7 +8031,7 @@
         <v>0</v>
       </c>
       <c r="AS34" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="str">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="AY34" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="str">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="BK34" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL34" t="str">
         <v>0</v>
@@ -8103,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="BQ34" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BR34" t="str">
         <v>0</v>
@@ -8129,34 +8129,34 @@
         <v>1</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E35" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/6d0f15ac-c0b3-4b73-a297-8d570a168876.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2f7a7537-5358-4736-b3fc-a56a54b2e6b9.jpg</v>
       </c>
       <c r="F35" t="str">
-        <v>Крем для лица увлажняющий питательный с ниацинамидом</v>
+        <v>Сыворотка для роста ресниц и бровей, гель для роста</v>
       </c>
       <c r="G35" t="str">
-        <v>4,603,320,465,342</v>
+        <v>4 656 738 598 843</v>
       </c>
       <c r="H35" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I35" t="str">
-        <v>MPL533896</v>
+        <v>MPL536269</v>
       </c>
       <c r="J35" t="str">
-        <v>pink_pepper_50ml</v>
+        <v>syvorotka_dlya_rosta_6ml_v2</v>
       </c>
       <c r="K35" t="str">
-        <v>Крем для лица</v>
+        <v>Гель для роста ресниц и бровей</v>
       </c>
       <c r="L35" t="str">
         <v>В продаже</v>
@@ -8186,7 +8186,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="str">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="V35" t="str">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="str">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AB35" t="str">
         <v>0</v>
@@ -8356,34 +8356,34 @@
         <v>1</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C36" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E36" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/7b62942f-efab-4a37-bf26-4b4d44ac08ad.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/4822bd34-9fce-40b0-9167-bf7265647db0.jpg</v>
       </c>
       <c r="F36" t="str">
-        <v>Сыворотка с ретинолом 1% для лица от морщин антивозрастная</v>
+        <v>Скраб пилинг для кожи головы</v>
       </c>
       <c r="G36" t="str">
-        <v>4,603,320,465,403</v>
+        <v>4 660 417 421 476</v>
       </c>
       <c r="H36" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I36" t="str">
-        <v>MPL533706</v>
+        <v>MPL534263</v>
       </c>
       <c r="J36" t="str">
-        <v>retinait_syvorotka_1_30ml</v>
+        <v>skrab_babl_gam_200ml</v>
       </c>
       <c r="K36" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Скраб для кожи головы</v>
       </c>
       <c r="L36" t="str">
         <v>В продаже</v>
@@ -8413,44 +8413,44 @@
         <v>0</v>
       </c>
       <c r="U36" t="str">
+        <v>69</v>
+      </c>
+      <c r="V36" t="str">
+        <v>0</v>
+      </c>
+      <c r="W36" t="str">
+        <v>0</v>
+      </c>
+      <c r="X36" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="str">
+        <v>67</v>
+      </c>
+      <c r="AB36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="str">
         <v>2</v>
       </c>
-      <c r="V36" t="str">
-        <v>0</v>
-      </c>
-      <c r="W36" t="str">
-        <v>0</v>
-      </c>
-      <c r="X36" t="str">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="str">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="str">
-        <v>0</v>
-      </c>
       <c r="AH36" t="str">
         <v>0</v>
       </c>
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="BQ36" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR36" t="str">
         <v>0</v>
@@ -8583,34 +8583,34 @@
         <v>1</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C37" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E37" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/01/b1/a0f0ab5e-7d32-428e-8d45-ea94ae31836d.png</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/6d0f15ac-c0b3-4b73-a297-8d570a168876.jpg</v>
       </c>
       <c r="F37" t="str">
-        <v>Масло для волос несмываемое</v>
+        <v>Крем для лица увлажняющий питательный с ниацинамидом</v>
       </c>
       <c r="G37" t="str">
-        <v>4,610,172,181,559</v>
+        <v>4 603 320 465 342</v>
       </c>
       <c r="H37" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I37" t="str">
-        <v>MPL498116</v>
+        <v>MPL533896</v>
       </c>
       <c r="J37" t="str">
-        <v>maslo_dlya_volos_parf_110ml_</v>
+        <v>pink_pepper_50ml</v>
       </c>
       <c r="K37" t="str">
-        <v>Масло для волос</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L37" t="str">
         <v>В продаже</v>
@@ -8784,7 +8784,7 @@
         <v>0</v>
       </c>
       <c r="BQ37" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR37" t="str">
         <v>0</v>
@@ -8802,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="BW37" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -8810,34 +8810,34 @@
         <v>1</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C38" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E38" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/63e4e620-5efc-4ad7-bbfb-077d4e99ec12.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/01/b1/a0f0ab5e-7d32-428e-8d45-ea94ae31836d.png</v>
       </c>
       <c r="F38" t="str">
-        <v>Крем для укладки волос</v>
+        <v>Масло для волос несмываемое</v>
       </c>
       <c r="G38" t="str">
-        <v>4,603,320,465,304</v>
+        <v>4 610 172 181 559</v>
       </c>
       <c r="H38" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I38" t="str">
-        <v>MPL485625</v>
+        <v>MPL498116</v>
       </c>
       <c r="J38" t="str">
-        <v>matte_wax_50ml</v>
+        <v>maslo_dlya_volos_parf_110ml_</v>
       </c>
       <c r="K38" t="str">
-        <v>Воск для укладки волос</v>
+        <v>Масло для волос</v>
       </c>
       <c r="L38" t="str">
         <v>В продаже</v>
@@ -8867,7 +8867,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="str">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="V38" t="str">
         <v>0</v>
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="AA38" t="str">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="str">
         <v>0</v>
@@ -8903,7 +8903,7 @@
         <v>0</v>
       </c>
       <c r="AG38" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="str">
         <v>0</v>
@@ -8939,7 +8939,7 @@
         <v>0</v>
       </c>
       <c r="AS38" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="str">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="BQ38" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR38" t="str">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="BW38" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -9037,34 +9037,34 @@
         <v>1</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C39" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E39" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e50770dd-caa8-4478-b9f2-0ac1b5692608.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/63e4e620-5efc-4ad7-bbfb-077d4e99ec12.jpg</v>
       </c>
       <c r="F39" t="str">
-        <v>Тоник для лица от прыщей и черных точек очищающий</v>
+        <v>Крем для укладки волос</v>
       </c>
       <c r="G39" t="str">
-        <v>4,670,020,498,499</v>
+        <v>4 603 320 465 304</v>
       </c>
       <c r="H39" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I39" t="str">
-        <v>MPL440013</v>
+        <v>MPL485625</v>
       </c>
       <c r="J39" t="str">
-        <v>tonik_dlya_lica_200ml</v>
+        <v>matte_wax_50ml</v>
       </c>
       <c r="K39" t="str">
-        <v>Тоник для лица</v>
+        <v>Воск для укладки волос</v>
       </c>
       <c r="L39" t="str">
         <v>В продаже</v>
@@ -9094,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="str">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="V39" t="str">
         <v>0</v>
@@ -9112,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="AA39" t="str">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AB39" t="str">
         <v>0</v>
@@ -9130,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="AG39" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH39" t="str">
         <v>0</v>
@@ -9148,7 +9148,7 @@
         <v>0</v>
       </c>
       <c r="AM39" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="str">
         <v>0</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="AS39" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT39" t="str">
         <v>0</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="BQ39" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR39" t="str">
         <v>0</v>
@@ -9264,34 +9264,34 @@
         <v>1</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C40" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E40" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/89bcceec-1c50-47a2-8033-c4a8bed335b7.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/a3901563-1960-431d-af08-2b59339f6884.jpg</v>
       </c>
       <c r="F40" t="str">
-        <v>Гель для бровей с коллагеном и эластином, фиксация на 24 часа</v>
+        <v>Гель для душа женский парфюмированный</v>
       </c>
       <c r="G40" t="str">
-        <v>4,676,574,657,436</v>
+        <v>4 603 320 465 267</v>
       </c>
       <c r="H40" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I40" t="str">
-        <v>MPL411155</v>
+        <v>MPL411108</v>
       </c>
       <c r="J40" t="str">
-        <v>gel_brows_5ml</v>
+        <v>gel_parfum_tabacco_vanille_450ml</v>
       </c>
       <c r="K40" t="str">
-        <v>Гель для бровей</v>
+        <v>Парфюмированный гель для душа</v>
       </c>
       <c r="L40" t="str">
         <v>В продаже</v>
@@ -9321,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="str">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="V40" t="str">
         <v>0</v>
@@ -9339,7 +9339,7 @@
         <v>0</v>
       </c>
       <c r="AA40" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="str">
         <v>0</v>
@@ -9357,7 +9357,7 @@
         <v>0</v>
       </c>
       <c r="AG40" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="str">
         <v>0</v>
@@ -9465,7 +9465,7 @@
         <v>0</v>
       </c>
       <c r="BQ40" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BR40" t="str">
         <v>0</v>
@@ -9491,34 +9491,34 @@
         <v>1</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C41" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E41" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/a3901563-1960-431d-af08-2b59339f6884.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/b7/3a/109f8e49-63d9-4359-967c-defcd581f3a9.jpg</v>
       </c>
       <c r="F41" t="str">
-        <v>Гель для душа женский парфюмированный</v>
+        <v>Маска для лица очищающая</v>
       </c>
       <c r="G41" t="str">
-        <v>4,603,320,465,267</v>
+        <v>4 670 020 498 741</v>
       </c>
       <c r="H41" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I41" t="str">
-        <v>MPL411108</v>
+        <v>MPL411103</v>
       </c>
       <c r="J41" t="str">
-        <v>gel_parfum_tabacco_vanille_450ml</v>
+        <v>maska_dlya_lica_100ml</v>
       </c>
       <c r="K41" t="str">
-        <v>Парфюмированный гель для душа</v>
+        <v>Маска для лица</v>
       </c>
       <c r="L41" t="str">
         <v>В продаже</v>
@@ -9548,133 +9548,133 @@
         <v>0</v>
       </c>
       <c r="U41" t="str">
+        <v>174</v>
+      </c>
+      <c r="V41" t="str">
+        <v>0</v>
+      </c>
+      <c r="W41" t="str">
+        <v>0</v>
+      </c>
+      <c r="X41" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="str">
+        <v>156</v>
+      </c>
+      <c r="AB41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="str">
+        <v>4</v>
+      </c>
+      <c r="AN41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="str">
+        <v>2</v>
+      </c>
+      <c r="AT41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="str">
+        <v>2</v>
+      </c>
+      <c r="AZ41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ41" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK41" t="str">
         <v>3</v>
-      </c>
-      <c r="V41" t="str">
-        <v>0</v>
-      </c>
-      <c r="W41" t="str">
-        <v>0</v>
-      </c>
-      <c r="X41" t="str">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="str">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="str">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BF41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ41" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK41" t="str">
-        <v>0</v>
       </c>
       <c r="BL41" t="str">
         <v>0</v>
@@ -9718,34 +9718,34 @@
         <v>1</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C42" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E42" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/b7/3a/109f8e49-63d9-4359-967c-defcd581f3a9.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/df/68/aa39874f-cb9a-4865-95c7-af9a92706ab5.jpg</v>
       </c>
       <c r="F42" t="str">
-        <v>Маска для лица очищающая</v>
+        <v>Солевой спрей для объема и укладки волос с фиксацией</v>
       </c>
       <c r="G42" t="str">
-        <v>4,670,020,498,741</v>
+        <v>4 670 020 498 413</v>
       </c>
       <c r="H42" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I42" t="str">
-        <v>MPL411103</v>
+        <v>MPL411095</v>
       </c>
       <c r="J42" t="str">
-        <v>maska_dlya_lica_100ml</v>
+        <v>solevoy_sprei_200ml</v>
       </c>
       <c r="K42" t="str">
-        <v>Маска для лица</v>
+        <v>Спрей для укладки волос</v>
       </c>
       <c r="L42" t="str">
         <v>В продаже</v>
@@ -9775,7 +9775,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="str">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="V42" t="str">
         <v>0</v>
@@ -9793,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="AA42" t="str">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="str">
         <v>0</v>
@@ -9811,7 +9811,7 @@
         <v>0</v>
       </c>
       <c r="AG42" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH42" t="str">
         <v>0</v>
@@ -9829,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="AM42" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN42" t="str">
         <v>0</v>
@@ -9847,44 +9847,44 @@
         <v>0</v>
       </c>
       <c r="AS42" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="str">
         <v>2</v>
       </c>
-      <c r="AT42" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW42" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX42" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY42" t="str">
-        <v>2</v>
-      </c>
-      <c r="AZ42" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA42" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB42" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC42" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD42" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE42" t="str">
-        <v>0</v>
-      </c>
       <c r="BF42" t="str">
         <v>0</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>0</v>
       </c>
       <c r="BK42" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL42" t="str">
         <v>0</v>
@@ -9919,7 +9919,7 @@
         <v>0</v>
       </c>
       <c r="BQ42" t="str">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BR42" t="str">
         <v>0</v>
@@ -9945,34 +9945,34 @@
         <v>1</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C43" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E43" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/df/68/aa39874f-cb9a-4865-95c7-af9a92706ab5.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e8b7722e-10fd-4f95-8988-f043f9a8d54a.jpg</v>
       </c>
       <c r="F43" t="str">
-        <v>Солевой спрей для объема и укладки волос с фиксацией</v>
+        <v>Термозащита для волос профессиональная с кератином, cыворотка для волос</v>
       </c>
       <c r="G43" t="str">
-        <v>4,670,020,498,413</v>
+        <v>4 670 020 497 980</v>
       </c>
       <c r="H43" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I43" t="str">
-        <v>MPL411095</v>
+        <v>MPL381178</v>
       </c>
       <c r="J43" t="str">
-        <v>solevoy_sprei_200ml</v>
+        <v>termo_sprei_200ml</v>
       </c>
       <c r="K43" t="str">
-        <v>Спрей для укладки волос</v>
+        <v>Спрей для ухода за волосами</v>
       </c>
       <c r="L43" t="str">
         <v>В продаже</v>
@@ -10002,7 +10002,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="str">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="V43" t="str">
         <v>0</v>
@@ -10038,7 +10038,7 @@
         <v>0</v>
       </c>
       <c r="AG43" t="str">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="str">
         <v>0</v>
@@ -10056,7 +10056,7 @@
         <v>0</v>
       </c>
       <c r="AM43" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="str">
         <v>0</v>
@@ -10110,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="BE43" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="str">
         <v>0</v>
@@ -10146,7 +10146,7 @@
         <v>0</v>
       </c>
       <c r="BQ43" t="str">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BR43" t="str">
         <v>0</v>
@@ -10164,7 +10164,7 @@
         <v>0</v>
       </c>
       <c r="BW43" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -10172,34 +10172,34 @@
         <v>1</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C44" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E44" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e8b7722e-10fd-4f95-8988-f043f9a8d54a.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/db6a42fd-0944-471f-966b-32f2132fa06d.jpg</v>
       </c>
       <c r="F44" t="str">
-        <v>Термозащита для волос профессиональная с кератином, cыворотка для волос</v>
+        <v>Сыворотка с витамином с, гиалуроновая кислота</v>
       </c>
       <c r="G44" t="str">
-        <v>4,670,020,497,980</v>
+        <v>4 670 020 498 093</v>
       </c>
       <c r="H44" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I44" t="str">
-        <v>MPL381178</v>
+        <v>MPL381177</v>
       </c>
       <c r="J44" t="str">
-        <v>termo_sprei_200ml</v>
+        <v>syvorotka_guk_30ml</v>
       </c>
       <c r="K44" t="str">
-        <v>Спрей для ухода за волосами</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L44" t="str">
         <v>В продаже</v>
@@ -10229,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="str">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="V44" t="str">
         <v>0</v>
@@ -10283,7 +10283,7 @@
         <v>0</v>
       </c>
       <c r="AM44" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN44" t="str">
         <v>0</v>
@@ -10301,7 +10301,7 @@
         <v>0</v>
       </c>
       <c r="AS44" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT44" t="str">
         <v>0</v>
@@ -10319,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="AY44" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ44" t="str">
         <v>0</v>
@@ -10337,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="BE44" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF44" t="str">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="BK44" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL44" t="str">
         <v>0</v>
@@ -10373,7 +10373,7 @@
         <v>0</v>
       </c>
       <c r="BQ44" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR44" t="str">
         <v>0</v>
@@ -10391,7 +10391,7 @@
         <v>0</v>
       </c>
       <c r="BW44" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -10399,13 +10399,13 @@
         <v>1</v>
       </c>
       <c r="B45" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C45" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E45" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/4e59ebb9-c860-44ad-ab36-d1cd7b03c07c.jpg</v>
@@ -10414,7 +10414,7 @@
         <v>Сыворотка для лица с ниацинамидом от прыщей пигментации</v>
       </c>
       <c r="G45" t="str">
-        <v>4,670,020,497,034</v>
+        <v>4 670 020 497 034</v>
       </c>
       <c r="H45" t="str">
         <v>АЛТЕЯ</v>
@@ -10626,13 +10626,13 @@
         <v>1</v>
       </c>
       <c r="B46" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C46" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E46" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/ff069309-0bd5-496a-9db7-5d55bfca9f49.jpg</v>
@@ -10641,7 +10641,7 @@
         <v>Крем-стик для ног от натирания, карандаш от мозолей, мозольный пластырь</v>
       </c>
       <c r="G46" t="str">
-        <v>4,690,222,978,568</v>
+        <v>4 690 222 978 568</v>
       </c>
       <c r="H46" t="str">
         <v>АЛТЕЯ</v>
@@ -10853,13 +10853,13 @@
         <v>1</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C47" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E47" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e300d073-2466-4d42-b162-188d6e4c89a6.jpg</v>
@@ -10868,7 +10868,7 @@
         <v>Шампунь от перхоти с климбазолом</v>
       </c>
       <c r="G47" t="str">
-        <v>4,670,020,496,679</v>
+        <v>4 670 020 496 679</v>
       </c>
       <c r="H47" t="str">
         <v>АЛТЕЯ</v>
@@ -11080,13 +11080,13 @@
         <v>1</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C48" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E48" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/796c257d-557a-4cbd-a342-dac9361e9ce2.jpg</v>
@@ -11095,7 +11095,7 @@
         <v>Ремувер для снятия ресниц</v>
       </c>
       <c r="G48" t="str">
-        <v>4,629,945,399,213</v>
+        <v>4 629 945 399 213</v>
       </c>
       <c r="H48" t="str">
         <v>АЛТЕЯ</v>
@@ -11137,7 +11137,7 @@
         <v>0</v>
       </c>
       <c r="U48" t="str">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="V48" t="str">
         <v>0</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="AA48" t="str">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="AB48" t="str">
         <v>0</v>
@@ -11307,13 +11307,13 @@
         <v>1</v>
       </c>
       <c r="B49" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C49" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E49" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/43e5f404-ab6b-47c4-8f2b-da61e673c04d.jpg</v>
@@ -11322,7 +11322,7 @@
         <v>Гель для удаления кутикулы, ремувер для кутикулы</v>
       </c>
       <c r="G49" t="str">
-        <v>4,607,050,974,747</v>
+        <v>4 607 050 974 747</v>
       </c>
       <c r="H49" t="str">
         <v>АЛТЕЯ</v>
@@ -11534,13 +11534,13 @@
         <v>1</v>
       </c>
       <c r="B50" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C50" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E50" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9a35a678-ddd0-4f4c-92c1-71678e998c87.jpg</v>
@@ -11549,7 +11549,7 @@
         <v>Пилинг для кожи головы профессиональный скраб от перхоти</v>
       </c>
       <c r="G50" t="str">
-        <v>4,670,020,496,761</v>
+        <v>4 670 020 496 761</v>
       </c>
       <c r="H50" t="str">
         <v>АЛТЕЯ</v>
@@ -11761,13 +11761,13 @@
         <v>1</v>
       </c>
       <c r="B51" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C51" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E51" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e1035672-2f2c-40fe-bdd1-29e73f438dda.jpg</v>
@@ -11776,7 +11776,7 @@
         <v>Пенка для умывания, для снятия макияжа, от постакне</v>
       </c>
       <c r="G51" t="str">
-        <v>4,630,084,864,777</v>
+        <v>4 630 084 864 777</v>
       </c>
       <c r="H51" t="str">
         <v>АЛТЕЯ</v>
@@ -11988,13 +11988,13 @@
         <v>1</v>
       </c>
       <c r="B52" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C52" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E52" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/32ea3c9d-10a8-4da9-b546-ac3df4e3e821.jpg</v>
@@ -12003,7 +12003,7 @@
         <v>Масло для бороды, средство для роста, уход за бородой, смягчающее</v>
       </c>
       <c r="G52" t="str">
-        <v>4,610,172,186,882</v>
+        <v>4 610 172 186 882</v>
       </c>
       <c r="H52" t="str">
         <v>АЛТЕЯ</v>
@@ -12215,34 +12215,34 @@
         <v>1</v>
       </c>
       <c r="B53" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C53" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E53" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/bbccc824-8896-4e69-bd67-4be5d9a9aaf7.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/fb6b51e2-810a-4d7f-8792-27b4578444b2.jpg</v>
       </c>
       <c r="F53" t="str">
-        <v>Крем с мочевиной увлажняющий, 10% мочевина</v>
+        <v>Крем для лица антивозрастной, крем филлер вокруг глаз, с коллагеном с ниацинамидом</v>
       </c>
       <c r="G53" t="str">
-        <v>4,611,113,000,977</v>
+        <v>4 657 786 831 418</v>
       </c>
       <c r="H53" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I53" t="str">
-        <v>MPL379168</v>
+        <v>MPL379166</v>
       </c>
       <c r="J53" t="str">
-        <v>kremshelk_100ml</v>
+        <v>krem-filler_15ml</v>
       </c>
       <c r="K53" t="str">
-        <v>Крем для тела</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L53" t="str">
         <v>В продаже</v>
@@ -12263,161 +12263,161 @@
         <v>0</v>
       </c>
       <c r="R53" t="str">
+        <v>0</v>
+      </c>
+      <c r="S53" t="str">
+        <v>0</v>
+      </c>
+      <c r="T53" t="str">
+        <v>0</v>
+      </c>
+      <c r="U53" t="str">
+        <v>29</v>
+      </c>
+      <c r="V53" t="str">
+        <v>0</v>
+      </c>
+      <c r="W53" t="str">
+        <v>0</v>
+      </c>
+      <c r="X53" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="str">
+        <v>18</v>
+      </c>
+      <c r="AB53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS53" t="str">
+        <v>2</v>
+      </c>
+      <c r="AT53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY53" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK53" t="str">
+        <v>2</v>
+      </c>
+      <c r="BL53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BN53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BO53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="str">
+        <v>0</v>
+      </c>
+      <c r="BQ53" t="str">
         <v>3</v>
       </c>
-      <c r="S53" t="str">
-        <v>0</v>
-      </c>
-      <c r="T53" t="str">
-        <v>0</v>
-      </c>
-      <c r="U53" t="str">
-        <v>148</v>
-      </c>
-      <c r="V53" t="str">
-        <v>0</v>
-      </c>
-      <c r="W53" t="str">
-        <v>0</v>
-      </c>
-      <c r="X53" t="str">
-        <v>3</v>
-      </c>
-      <c r="Y53" t="str">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="str">
-        <v>146</v>
-      </c>
-      <c r="AB53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY53" t="str">
-        <v>0</v>
-      </c>
-      <c r="AZ53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BF53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BL53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BM53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BN53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BO53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BP53" t="str">
-        <v>0</v>
-      </c>
-      <c r="BQ53" t="str">
-        <v>0</v>
-      </c>
       <c r="BR53" t="str">
         <v>0</v>
       </c>
@@ -12434,7 +12434,7 @@
         <v>0</v>
       </c>
       <c r="BW53" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -12442,13 +12442,13 @@
         <v>1</v>
       </c>
       <c r="B54" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C54" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E54" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/6b2c57d3-a40c-42b1-be7c-16e926442f48.jpg</v>
@@ -12457,7 +12457,7 @@
         <v>Гель для бровей с эффектом ламинирования</v>
       </c>
       <c r="G54" t="str">
-        <v>4,609,893,777,394</v>
+        <v>4 609 893 777 394</v>
       </c>
       <c r="H54" t="str">
         <v>АЛТЕЯ</v>
@@ -12669,13 +12669,13 @@
         <v>1</v>
       </c>
       <c r="B55" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C55" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E55" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3f7506e1-6d7b-4bee-ab9f-f0ef40a8a272.jpg</v>
@@ -12684,7 +12684,7 @@
         <v>Энзимная пудра для умывания лица и тела</v>
       </c>
       <c r="G55" t="str">
-        <v>4,670,020,498,017</v>
+        <v>4 670 020 498 017</v>
       </c>
       <c r="H55" t="str">
         <v>АЛТЕЯ</v>
@@ -12896,13 +12896,13 @@
         <v>1</v>
       </c>
       <c r="B56" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C56" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E56" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/13/4c/1fd02476-339d-45f4-abca-db41c844b1b7.jpg</v>
@@ -12911,7 +12911,7 @@
         <v>Сыворотка для лица увлажняющая с PDRN 10000 ppm</v>
       </c>
       <c r="G56" t="str">
-        <v>4,660,417,421,896</v>
+        <v>4 660 417 421 896</v>
       </c>
       <c r="H56" t="str">
         <v>АЛТЕЯ</v>
@@ -13123,13 +13123,13 @@
         <v>1</v>
       </c>
       <c r="B57" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C57" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E57" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/91847533-cb64-4445-99b2-78cd6d971bb8.jpg</v>
@@ -13138,7 +13138,7 @@
         <v>Шампунь разглаживающий с BADD для восстановления волос</v>
       </c>
       <c r="G57" t="str">
-        <v>7,693,733,020,006</v>
+        <v>7 693 733 020 006</v>
       </c>
       <c r="H57" t="str">
         <v>АЛТЕЯ</v>
@@ -13350,13 +13350,13 @@
         <v>1</v>
       </c>
       <c r="B58" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C58" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E58" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/c0/79/74ec1d22-a2e4-4738-940b-34d263f718bf.jpg</v>
@@ -13365,7 +13365,7 @@
         <v>Пробиотическая гель-пенка для умывания проблемной кожи</v>
       </c>
       <c r="G58" t="str">
-        <v>4,660,417,422,022</v>
+        <v>4 660 417 422 022</v>
       </c>
       <c r="H58" t="str">
         <v>АЛТЕЯ</v>
@@ -13577,13 +13577,13 @@
         <v>1</v>
       </c>
       <c r="B59" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C59" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E59" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/f2/31/37575b2b-76ab-4d35-9929-aa2dfcdf7bf6.jpg</v>
@@ -13592,7 +13592,7 @@
         <v>Маска-пленка для лица с PDRN, коллагеном и гиалуроновой кислотой, с пептидами</v>
       </c>
       <c r="G59" t="str">
-        <v>4,660,417,421,964</v>
+        <v>4 660 417 421 964</v>
       </c>
       <c r="H59" t="str">
         <v>АЛТЕЯ</v>
@@ -13804,13 +13804,13 @@
         <v>1</v>
       </c>
       <c r="B60" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C60" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E60" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/fc/f6/be192d64-456d-4082-892e-58b3852bb6f3.jpg</v>
@@ -13819,7 +13819,7 @@
         <v>Сыворотка для лица, Интенсивное увлажнение</v>
       </c>
       <c r="G60" t="str">
-        <v>4,660,417,422,008</v>
+        <v>4 660 417 422 008</v>
       </c>
       <c r="H60" t="str">
         <v>АЛТЕЯ</v>
@@ -14031,13 +14031,13 @@
         <v>1</v>
       </c>
       <c r="B61" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C61" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E61" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/c2/09/206c885d-46ee-4221-8068-e5e20d1fafba.jpg</v>
@@ -14046,7 +14046,7 @@
         <v>Гель для кудрявых волос</v>
       </c>
       <c r="G61" t="str">
-        <v>4,660,417,422,039</v>
+        <v>4 660 417 422 039</v>
       </c>
       <c r="H61" t="str">
         <v>АЛТЕЯ</v>
@@ -14258,13 +14258,13 @@
         <v>1</v>
       </c>
       <c r="B62" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C62" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E62" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/26/17/58467fe1-4682-493c-b6fe-7d86223be0d2.jpg</v>
@@ -14273,7 +14273,7 @@
         <v>Крем для лица антивозрастной со спикулами и ПДРН</v>
       </c>
       <c r="G62" t="str">
-        <v>4,660,417,421,933</v>
+        <v>4 660 417 421 933</v>
       </c>
       <c r="H62" t="str">
         <v>АЛТЕЯ</v>
@@ -14485,13 +14485,13 @@
         <v>1</v>
       </c>
       <c r="B63" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C63" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E63" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/e9/29/0552627e-dd63-4b3c-9bac-d180ba298db2.jpg</v>
@@ -14500,7 +14500,7 @@
         <v>Термозащитное масло для волос</v>
       </c>
       <c r="G63" t="str">
-        <v>4,640,523,970,334</v>
+        <v>4 640 523 970 334</v>
       </c>
       <c r="H63" t="str">
         <v>АЛТЕЯ</v>
@@ -14712,13 +14712,13 @@
         <v>1</v>
       </c>
       <c r="B64" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C64" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E64" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/49/ec/4efc7277-a846-43d6-9cf8-8bf4da9c0b43.png</v>
@@ -14727,7 +14727,7 @@
         <v>Набор уходовой косметики для лица антивозрастной</v>
       </c>
       <c r="G64" t="str">
-        <v>4,660,401,460,108</v>
+        <v>4 660 401 460 108</v>
       </c>
       <c r="H64" t="str">
         <v>АЛТЕЯ</v>
@@ -14939,13 +14939,13 @@
         <v>1</v>
       </c>
       <c r="B65" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C65" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E65" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/7d/8f/6308e0cd-1281-4291-b6a2-e033c0496987.png</v>
@@ -14954,7 +14954,7 @@
         <v>Набор Крем для лица Ретинайт 0,25% + Крем для лица Ретинайт 0,5%</v>
       </c>
       <c r="G65" t="str">
-        <v>4,660,401,460,092</v>
+        <v>4 660 401 460 092</v>
       </c>
       <c r="H65" t="str">
         <v>АЛТЕЯ</v>
@@ -15166,13 +15166,13 @@
         <v>1</v>
       </c>
       <c r="B66" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C66" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E66" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/33/42/29be8dc2-5569-4753-b4ea-fecfc4c1befc.jpg</v>
@@ -15181,7 +15181,7 @@
         <v>Маска для волос с кератином увлажняющая</v>
       </c>
       <c r="G66" t="str">
-        <v>4,630,446,234,156</v>
+        <v>4 630 446 234 156</v>
       </c>
       <c r="H66" t="str">
         <v>АЛТЕЯ</v>
@@ -15393,13 +15393,13 @@
         <v>1</v>
       </c>
       <c r="B67" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C67" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E67" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/6b/47/4fc77091-eef9-4c17-a375-3e5fddac18ba.png</v>
@@ -15408,7 +15408,7 @@
         <v>Сыворотка для лица с ретинолом</v>
       </c>
       <c r="G67" t="str">
-        <v>4,640,523,970,082</v>
+        <v>4 640 523 970 082</v>
       </c>
       <c r="H67" t="str">
         <v>АЛТЕЯ</v>
@@ -15620,13 +15620,13 @@
         <v>1</v>
       </c>
       <c r="B68" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C68" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E68" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/1b/13/4d1d3551-7e04-4a23-83c1-02e6de3d304b.png</v>
@@ -15635,7 +15635,7 @@
         <v>Крем для лица с липосомальным ретинолом 0,5% Ретинайт</v>
       </c>
       <c r="G68" t="str">
-        <v>4,660,417,421,759</v>
+        <v>4 660 417 421 759</v>
       </c>
       <c r="H68" t="str">
         <v>АЛТЕЯ</v>
@@ -15847,13 +15847,13 @@
         <v>1</v>
       </c>
       <c r="B69" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C69" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E69" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/7a/bc/b90cc621-17b9-4a6b-bbe5-5b96ab70d97b.png</v>
@@ -15862,7 +15862,7 @@
         <v>Энзимная пудра для умывания тела и лица, от прыщей</v>
       </c>
       <c r="G69" t="str">
-        <v>4,645,565,747,487</v>
+        <v>4 645 565 747 487</v>
       </c>
       <c r="H69" t="str">
         <v>АЛТЕЯ</v>
@@ -16074,13 +16074,13 @@
         <v>1</v>
       </c>
       <c r="B70" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C70" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E70" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/bc/66/ce5d0003-e31e-44a0-8886-3bcc7a09c230.png</v>
@@ -16089,7 +16089,7 @@
         <v>Гель для интимной гигиены с молочной кислотой</v>
       </c>
       <c r="G70" t="str">
-        <v>4,630,084,865,477</v>
+        <v>4 630 084 865 477</v>
       </c>
       <c r="H70" t="str">
         <v>АЛТЕЯ</v>
@@ -16301,13 +16301,13 @@
         <v>1</v>
       </c>
       <c r="B71" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C71" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E71" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/51/92/6fdb97d7-0c18-4cf5-b27b-98c1e58f126b.png</v>
@@ -16316,7 +16316,7 @@
         <v>Точечный крем от прыщей. Корректор точечный против прыщей, крем от акне</v>
       </c>
       <c r="G71" t="str">
-        <v>4,670,020,498,482</v>
+        <v>4 670 020 498 482</v>
       </c>
       <c r="H71" t="str">
         <v>АЛТЕЯ</v>
@@ -16528,13 +16528,13 @@
         <v>1</v>
       </c>
       <c r="B72" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C72" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E72" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/fef136d7-44af-4d9a-b127-fe9c96f44802.jpg</v>
@@ -16543,7 +16543,7 @@
         <v>Гель для душа мужской парфюмированный</v>
       </c>
       <c r="G72" t="str">
-        <v>4,603,320,465,274</v>
+        <v>4 603 320 465 274</v>
       </c>
       <c r="H72" t="str">
         <v>АЛТЕЯ</v>
@@ -16755,13 +16755,13 @@
         <v>1</v>
       </c>
       <c r="B73" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C73" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E73" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/ac/bb/069ebeb7-cacb-480b-a0ae-b9b3f9618e75.png</v>
@@ -16770,7 +16770,7 @@
         <v>Сыворотка для роста ресниц и бровей, гель для роста</v>
       </c>
       <c r="G73" t="str">
-        <v>4,685,518,825,374</v>
+        <v>4 685 518 825 374</v>
       </c>
       <c r="H73" t="str">
         <v>АЛТЕЯ</v>
@@ -16982,13 +16982,13 @@
         <v>1</v>
       </c>
       <c r="B74" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C74" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E74" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/f9/e4/8a36e421-834c-4220-99ab-f5e60d7902e3.png</v>
@@ -16997,7 +16997,7 @@
         <v>Масло для волос парфюмированное, сыворотка для волос</v>
       </c>
       <c r="G74" t="str">
-        <v>4,610,172,186,875</v>
+        <v>4 610 172 186 875</v>
       </c>
       <c r="H74" t="str">
         <v>АЛТЕЯ</v>
@@ -17209,13 +17209,13 @@
         <v>1</v>
       </c>
       <c r="B75" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C75" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E75" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/c6/5d/235e7692-36db-4a03-8ad4-3a438f44675e.png</v>
@@ -17224,7 +17224,7 @@
         <v>Гель для интимной гигиены с молочной кислотой Интимвита</v>
       </c>
       <c r="G75" t="str">
-        <v>4,630,084,864,616</v>
+        <v>4 630 084 864 616</v>
       </c>
       <c r="H75" t="str">
         <v>АЛТЕЯ</v>
@@ -17436,13 +17436,13 @@
         <v>1</v>
       </c>
       <c r="B76" t="str">
-        <v>2026-07-27</v>
+        <v>2026-07-29</v>
       </c>
       <c r="C76" t="str">
-        <v>2026-07-28</v>
+        <v>2026-07-30</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-07-27-2026-07-27</v>
+        <v>2026-07-29-2026-07-29</v>
       </c>
       <c r="E76" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/16/28/d514e8ae-6afc-470a-b2e0-4d81ff9eda79.png</v>
@@ -17451,7 +17451,7 @@
         <v>Гидрофильное масло для снятия макияжа с лавандой</v>
       </c>
       <c r="G76" t="str">
-        <v>4,610,172,186,202</v>
+        <v>4 610 172 186 202</v>
       </c>
       <c r="H76" t="str">
         <v>АЛТЕЯ</v>
@@ -17667,7 +17667,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:O23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17713,10 +17713,7 @@
         <v>1</v>
       </c>
       <c r="O1" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P1" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="2">
@@ -17730,31 +17727,31 @@
         <v>krovavii_piling_30ml</v>
       </c>
       <c r="D2" t="str">
-        <v>4.67002E+12</v>
+        <v>4670020498208</v>
       </c>
       <c r="E2" t="str">
-        <v>11985</v>
+        <v>13092</v>
       </c>
       <c r="F2" t="str">
-        <v>668</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>11317</v>
+        <v>11765</v>
       </c>
       <c r="H2" t="str">
-        <v>0</v>
+        <v>1327</v>
       </c>
       <c r="I2" t="str">
+        <v>20</v>
+      </c>
+      <c r="J2" t="str">
+        <v>0</v>
+      </c>
+      <c r="K2" t="str">
         <v>18</v>
       </c>
-      <c r="J2" t="str">
-        <v>1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>17</v>
-      </c>
       <c r="L2" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="str">
         <v>0</v>
@@ -17763,46 +17760,43 @@
         <v>1</v>
       </c>
       <c r="O2" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Крем для волос Упругий завиток, 300 мл</v>
+        <v>Пенка для укладки волос</v>
       </c>
       <c r="B3" t="str">
-        <v>99000114726</v>
+        <v>99000125266</v>
       </c>
       <c r="C3" t="str">
-        <v>curly_method_300ml</v>
+        <v>penka_kudryavii_meto</v>
       </c>
       <c r="D3" t="str">
-        <v>4.60332E+12</v>
+        <v>4670020498611</v>
       </c>
       <c r="E3" t="str">
-        <v>8424</v>
+        <v>8000</v>
       </c>
       <c r="F3" t="str">
-        <v>903</v>
+        <v>750</v>
       </c>
       <c r="G3" t="str">
-        <v>7521</v>
+        <v>7250</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
       <c r="I3" t="str">
+        <v>11</v>
+      </c>
+      <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
         <v>10</v>
       </c>
-      <c r="J3" t="str">
-        <v>1</v>
-      </c>
-      <c r="K3" t="str">
-        <v>9</v>
-      </c>
       <c r="L3" t="str">
         <v>0</v>
       </c>
@@ -17813,48 +17807,45 @@
         <v>1</v>
       </c>
       <c r="O3" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P3" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Гель для проблемной кожи лица и тела, с маркировками Алтея</v>
+        <v>Крем для лица с ретинолом 0.5, сыворотка от морщин и пигментных пятен, Алтея, Ретидерм, 50 мл</v>
       </c>
       <c r="B4" t="str">
-        <v>99000114730</v>
+        <v>99000076216</v>
       </c>
       <c r="C4" t="str">
-        <v>gel_antiakne_20ml_v2</v>
+        <v>retiderm_50ml</v>
       </c>
       <c r="D4" t="str">
-        <v>4.66042E+12</v>
+        <v>4610172186219</v>
       </c>
       <c r="E4" t="str">
-        <v>7893</v>
+        <v>6153</v>
       </c>
       <c r="F4" t="str">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="G4" t="str">
-        <v>7446</v>
+        <v>5902</v>
       </c>
       <c r="H4" t="str">
-        <v>447</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J4" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="str">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L4" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="str">
         <v>0</v>
@@ -17863,48 +17854,45 @@
         <v>1</v>
       </c>
       <c r="O4" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P4" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Продукция косметическая для ухода за кожей, в том числе в наборах: Маска для проблемной кожи лица м</v>
+        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея</v>
       </c>
       <c r="B5" t="str">
-        <v>99000114727</v>
+        <v>99000124421</v>
       </c>
       <c r="C5" t="str">
-        <v>maska_dlya_lica_100m</v>
+        <v>retinait_krem_1_50ml</v>
       </c>
       <c r="D5" t="str">
-        <v>4.67002E+12</v>
+        <v>4660417421605</v>
       </c>
       <c r="E5" t="str">
-        <v>7428</v>
+        <v>6150</v>
       </c>
       <c r="F5" t="str">
         <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>6489</v>
+        <v>6150</v>
       </c>
       <c r="H5" t="str">
-        <v>939</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J5" t="str">
         <v>0</v>
       </c>
       <c r="K5" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="str">
         <v>0</v>
@@ -17913,45 +17901,42 @@
         <v>1</v>
       </c>
       <c r="O5" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P5" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Пенка для укладки волос</v>
+        <v>Продукция косметическая для ухода за кожей, в том числе в наборах: Маска для проблемной кожи лица м</v>
       </c>
       <c r="B6" t="str">
-        <v>99000125266</v>
+        <v>99000114727</v>
       </c>
       <c r="C6" t="str">
-        <v>penka_kudryavii_meto</v>
+        <v>maska_dlya_lica_100m</v>
       </c>
       <c r="D6" t="str">
-        <v>4.67002E+12</v>
+        <v>4670020498741</v>
       </c>
       <c r="E6" t="str">
-        <v>6242</v>
+        <v>6059</v>
       </c>
       <c r="F6" t="str">
         <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>6242</v>
+        <v>6059</v>
       </c>
       <c r="H6" t="str">
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J6" t="str">
         <v>0</v>
       </c>
       <c r="K6" t="str">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L6" t="str">
         <v>0</v>
@@ -17963,48 +17948,45 @@
         <v>1</v>
       </c>
       <c r="O6" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P6" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Крем специального назначения «Псоридонт» 50 мл</v>
+        <v>Крем-шелк для сухой кожи ног</v>
       </c>
       <c r="B7" t="str">
-        <v>99000125141</v>
+        <v>99000076225</v>
       </c>
       <c r="C7" t="str">
-        <v>psoral_50ml</v>
+        <v>kremshelk_100ml</v>
       </c>
       <c r="D7" t="str">
-        <v>4.66042E+12</v>
+        <v>4670020498437</v>
       </c>
       <c r="E7" t="str">
-        <v>5112</v>
+        <v>5138</v>
       </c>
       <c r="F7" t="str">
         <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>5112</v>
+        <v>4635</v>
       </c>
       <c r="H7" t="str">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="I7" t="str">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J7" t="str">
         <v>0</v>
       </c>
       <c r="K7" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L7" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="str">
         <v>0</v>
@@ -18013,48 +17995,45 @@
         <v>1</v>
       </c>
       <c r="O7" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P7" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея</v>
+        <v>Гель для проблемной кожи лица и тела, с маркировками Алтея</v>
       </c>
       <c r="B8" t="str">
-        <v>99000124421</v>
+        <v>99000114730</v>
       </c>
       <c r="C8" t="str">
-        <v>retinait_krem_1_50ml</v>
+        <v>gel_antiakne_20ml_v2</v>
       </c>
       <c r="D8" t="str">
-        <v>4.66042E+12</v>
+        <v>4660417420110</v>
       </c>
       <c r="E8" t="str">
-        <v>5046</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="str">
-        <v>1025</v>
+        <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>4021</v>
+        <v>3504</v>
       </c>
       <c r="H8" t="str">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="I8" t="str">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J8" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="str">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L8" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="str">
         <v>0</v>
@@ -18063,45 +18042,42 @@
         <v>1</v>
       </c>
       <c r="O8" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P8" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Спрей для роста волос торговой марки Алтея</v>
+        <v>Крем для волос Упругий завиток, 300 мл</v>
       </c>
       <c r="B9" t="str">
-        <v>99000114724</v>
+        <v>99000114726</v>
       </c>
       <c r="C9" t="str">
-        <v>sprei_buster_100ml</v>
+        <v>curly_method_300ml</v>
       </c>
       <c r="D9" t="str">
-        <v>4.60332E+12</v>
+        <v>4603320465441</v>
       </c>
       <c r="E9" t="str">
-        <v>4211</v>
+        <v>3590</v>
       </c>
       <c r="F9" t="str">
-        <v>602</v>
+        <v>0</v>
       </c>
       <c r="G9" t="str">
-        <v>3609</v>
+        <v>3590</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
       </c>
       <c r="I9" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L9" t="str">
         <v>0</v>
@@ -18113,45 +18089,42 @@
         <v>1</v>
       </c>
       <c r="O9" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P9" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Продукция косметическая для ухода за кожей для взрослых: гелевая маска со спикулами торговой марки А</v>
+        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз, 30мл</v>
       </c>
       <c r="B10" t="str">
-        <v>99000177799</v>
+        <v>99000154005</v>
       </c>
       <c r="C10" t="str">
-        <v>spicul_gel_mask_75ml</v>
+        <v>retinol_boost_krem_d</v>
       </c>
       <c r="D10" t="str">
-        <v>4.66042E+12</v>
+        <v>4660417421636</v>
       </c>
       <c r="E10" t="str">
-        <v>4208</v>
+        <v>2679</v>
       </c>
       <c r="F10" t="str">
         <v>0</v>
       </c>
       <c r="G10" t="str">
-        <v>4208</v>
+        <v>2679</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J10" t="str">
         <v>0</v>
       </c>
       <c r="K10" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L10" t="str">
         <v>0</v>
@@ -18163,45 +18136,42 @@
         <v>1</v>
       </c>
       <c r="O10" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P10" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Крем для лица с ретинолом 0.5, сыворотка от морщин и пигментных пятен, Алтея, Ретидерм, 50 мл</v>
+        <v>Крем от растяжек, Алтея, 200 мл</v>
       </c>
       <c r="B11" t="str">
-        <v>99000076216</v>
+        <v>99000114731</v>
       </c>
       <c r="C11" t="str">
-        <v>retiderm_50ml</v>
+        <v>krem_ot_rastyazhek</v>
       </c>
       <c r="D11" t="str">
-        <v>4.61017E+12</v>
+        <v>4670020497898</v>
       </c>
       <c r="E11" t="str">
-        <v>3821</v>
+        <v>2484</v>
       </c>
       <c r="F11" t="str">
         <v>0</v>
       </c>
       <c r="G11" t="str">
-        <v>3821</v>
+        <v>2484</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J11" t="str">
         <v>0</v>
       </c>
       <c r="K11" t="str">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L11" t="str">
         <v>0</v>
@@ -18213,33 +18183,30 @@
         <v>1</v>
       </c>
       <c r="O11" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P11" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Крем от растяжек, Алтея, 200 мл</v>
+        <v>Спрей для роста волос торговой марки Алтея</v>
       </c>
       <c r="B12" t="str">
-        <v>99000114731</v>
+        <v>99000114724</v>
       </c>
       <c r="C12" t="str">
-        <v>krem_ot_rastyazhek</v>
+        <v>sprei_buster_100ml</v>
       </c>
       <c r="D12" t="str">
-        <v>4.67002E+12</v>
+        <v>4603320465359</v>
       </c>
       <c r="E12" t="str">
-        <v>3102</v>
+        <v>2260</v>
       </c>
       <c r="F12" t="str">
         <v>0</v>
       </c>
       <c r="G12" t="str">
-        <v>3102</v>
+        <v>2260</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
@@ -18263,42 +18230,39 @@
         <v>1</v>
       </c>
       <c r="O12" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P12" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз, 30мл</v>
+        <v>Крем специального назначения «Псоридонт» 50 мл</v>
       </c>
       <c r="B13" t="str">
-        <v>99000154005</v>
+        <v>99000125141</v>
       </c>
       <c r="C13" t="str">
-        <v>retinol_boost_krem_d</v>
+        <v>psoral_50ml</v>
       </c>
       <c r="D13" t="str">
-        <v>4.66042E+12</v>
+        <v>4660417421087</v>
       </c>
       <c r="E13" t="str">
-        <v>2625</v>
+        <v>1520</v>
       </c>
       <c r="F13" t="str">
-        <v>893</v>
+        <v>0</v>
       </c>
       <c r="G13" t="str">
-        <v>1732</v>
+        <v>1520</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="str">
         <v>2</v>
@@ -18313,45 +18277,42 @@
         <v>1</v>
       </c>
       <c r="O13" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P13" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Спрей-сыворотка для волос маркировки Алтея</v>
+        <v>Средство косметическое: Воск для волос торговой марки: «Алтея» 15гр</v>
       </c>
       <c r="B14" t="str">
-        <v>99000076226</v>
+        <v>99000131672</v>
       </c>
       <c r="C14" t="str">
-        <v>termo_sprei_200ml</v>
+        <v>vosk_stik_15ml</v>
       </c>
       <c r="D14" t="str">
-        <v>4.67002E+12</v>
+        <v>4670207150196</v>
       </c>
       <c r="E14" t="str">
-        <v>2344</v>
+        <v>1395</v>
       </c>
       <c r="F14" t="str">
         <v>0</v>
       </c>
       <c r="G14" t="str">
-        <v>2344</v>
+        <v>1395</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
       </c>
       <c r="I14" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J14" t="str">
         <v>0</v>
       </c>
       <c r="K14" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L14" t="str">
         <v>0</v>
@@ -18363,33 +18324,30 @@
         <v>1</v>
       </c>
       <c r="O14" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P14" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Шампунь для кудрявых волос торговой марки Алтея, 500 мл</v>
+        <v>Алтея Сыворотка для лица сыворотка для лица с ниацинамидом для лица антивозрастная, от пигментных пя</v>
       </c>
       <c r="B15" t="str">
-        <v>99000179424</v>
+        <v>99000182844</v>
       </c>
       <c r="C15" t="str">
-        <v>shampun_kudryavii_me</v>
+        <v>syvorotka_dlya_lica_</v>
       </c>
       <c r="D15" t="str">
-        <v>4.64052E+12</v>
+        <v>4603312714069</v>
       </c>
       <c r="E15" t="str">
-        <v>1718</v>
+        <v>1280</v>
       </c>
       <c r="F15" t="str">
-        <v>859</v>
+        <v>0</v>
       </c>
       <c r="G15" t="str">
-        <v>859</v>
+        <v>1280</v>
       </c>
       <c r="H15" t="str">
         <v>0</v>
@@ -18398,10 +18356,10 @@
         <v>2</v>
       </c>
       <c r="J15" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="str">
         <v>0</v>
@@ -18413,45 +18371,42 @@
         <v>1</v>
       </c>
       <c r="O15" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P15" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Крем для лица spf 50 с защитой UVA/UVB, торговой марки Алтея</v>
+        <v>Лосьон для волос бальзам для кудрявых волос, 500 мл</v>
       </c>
       <c r="B16" t="str">
-        <v>99000163832</v>
+        <v>99000177794</v>
       </c>
       <c r="C16" t="str">
-        <v>krem_spf50_50ml</v>
+        <v>balzam_kudryavii_met</v>
       </c>
       <c r="D16" t="str">
-        <v>4.66042E+12</v>
+        <v>4640523970327</v>
       </c>
       <c r="E16" t="str">
-        <v>1600</v>
+        <v>1263</v>
       </c>
       <c r="F16" t="str">
         <v>0</v>
       </c>
       <c r="G16" t="str">
-        <v>1600</v>
+        <v>1263</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
       </c>
       <c r="I16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="str">
         <v>0</v>
       </c>
       <c r="K16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" t="str">
         <v>0</v>
@@ -18463,45 +18418,42 @@
         <v>1</v>
       </c>
       <c r="O16" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P16" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Средство косметическое: Воск для волос торговой марки: «Алтея» 15гр</v>
+        <v>Cыворотка SPICULBOOST торговой марки Алтея, 30 мл</v>
       </c>
       <c r="B17" t="str">
-        <v>99000131672</v>
+        <v>99000179436</v>
       </c>
       <c r="C17" t="str">
-        <v>vosk_stik_15ml</v>
+        <v>spiculboost_30ml</v>
       </c>
       <c r="D17" t="str">
-        <v>4.67021E+12</v>
+        <v>4630446231421</v>
       </c>
       <c r="E17" t="str">
-        <v>1432</v>
+        <v>897</v>
       </c>
       <c r="F17" t="str">
         <v>0</v>
       </c>
       <c r="G17" t="str">
-        <v>1432</v>
+        <v>897</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
       </c>
       <c r="I17" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="str">
         <v>0</v>
       </c>
       <c r="K17" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L17" t="str">
         <v>0</v>
@@ -18513,45 +18465,42 @@
         <v>1</v>
       </c>
       <c r="O17" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P17" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Средство косметическое для ухода за волосами: маска для волос восстанавливающая с авокадо и маслом о</v>
+        <v>Продукция косметическая для ухода за кожей для взрослых: гелевая маска со спикулами торговой марки А</v>
       </c>
       <c r="B18" t="str">
-        <v>99000076210</v>
+        <v>99000177799</v>
       </c>
       <c r="C18" t="str">
-        <v>maska-batter_250ml</v>
+        <v>spicul_gel_mask_75ml</v>
       </c>
       <c r="D18" t="str">
-        <v>4.67002E+12</v>
+        <v>4660417421858</v>
       </c>
       <c r="E18" t="str">
-        <v>1376</v>
+        <v>847</v>
       </c>
       <c r="F18" t="str">
         <v>0</v>
       </c>
       <c r="G18" t="str">
-        <v>1376</v>
+        <v>847</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
       </c>
       <c r="I18" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="str">
         <v>0</v>
       </c>
       <c r="K18" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="str">
         <v>0</v>
@@ -18563,45 +18512,42 @@
         <v>1</v>
       </c>
       <c r="O18" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P18" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Крем-шелк для сухой кожи ног</v>
+        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея</v>
       </c>
       <c r="B19" t="str">
-        <v>99000076225</v>
+        <v>99000124418</v>
       </c>
       <c r="C19" t="str">
-        <v>kremshelk_100ml</v>
+        <v>retinait_krem_025_50</v>
       </c>
       <c r="D19" t="str">
-        <v>4.67002E+12</v>
+        <v>4660417421599</v>
       </c>
       <c r="E19" t="str">
-        <v>1335</v>
+        <v>844</v>
       </c>
       <c r="F19" t="str">
         <v>0</v>
       </c>
       <c r="G19" t="str">
-        <v>1335</v>
+        <v>844</v>
       </c>
       <c r="H19" t="str">
         <v>0</v>
       </c>
       <c r="I19" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" t="str">
         <v>0</v>
       </c>
       <c r="K19" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19" t="str">
         <v>0</v>
@@ -18613,33 +18559,30 @@
         <v>1</v>
       </c>
       <c r="O19" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P19" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Маска д/лица Лифтинг PDRN и пептиды 75мл</v>
+        <v>Ретинайт 0,5 экспресс-омоложение Anti-Age Липосомальный комплекс ретинола 0,5 + Ниацинамид 50 мл</v>
       </c>
       <c r="B20" t="str">
-        <v>99000188068</v>
+        <v>99000131675</v>
       </c>
       <c r="C20" t="str">
-        <v>lifting_maska_pdrn_7</v>
+        <v>retinait_krem_05_50m</v>
       </c>
       <c r="D20" t="str">
-        <v>4.66042E+12</v>
+        <v>4660417421759</v>
       </c>
       <c r="E20" t="str">
-        <v>1165</v>
+        <v>744</v>
       </c>
       <c r="F20" t="str">
         <v>0</v>
       </c>
       <c r="G20" t="str">
-        <v>1165</v>
+        <v>744</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
@@ -18663,45 +18606,42 @@
         <v>1</v>
       </c>
       <c r="O20" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P20" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея, 50 мл</v>
+        <v>Гель для бровей с коллагеном и эластином, фиксация на 24 часа, Алтея, 5 мл</v>
       </c>
       <c r="B21" t="str">
-        <v>99000176496</v>
+        <v>99000114725</v>
       </c>
       <c r="C21" t="str">
-        <v>retinait_krem_1_5_50</v>
+        <v>gel_brows_5ml</v>
       </c>
       <c r="D21" t="str">
-        <v>4.66042E+12</v>
+        <v>4676574657436</v>
       </c>
       <c r="E21" t="str">
-        <v>840</v>
+        <v>660</v>
       </c>
       <c r="F21" t="str">
         <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>840</v>
+        <v>660</v>
       </c>
       <c r="H21" t="str">
         <v>0</v>
       </c>
       <c r="I21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="str">
         <v>0</v>
       </c>
       <c r="K21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="str">
         <v>0</v>
@@ -18713,33 +18653,30 @@
         <v>1</v>
       </c>
       <c r="O21" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P21" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея</v>
+        <v>Спрей-сыворотка для волос маркировки Алтея</v>
       </c>
       <c r="B22" t="str">
-        <v>99000124418</v>
+        <v>99000076226</v>
       </c>
       <c r="C22" t="str">
-        <v>retinait_krem_025_50</v>
+        <v>termo_sprei_200ml</v>
       </c>
       <c r="D22" t="str">
-        <v>4.66042E+12</v>
+        <v>4670020497980</v>
       </c>
       <c r="E22" t="str">
-        <v>796</v>
+        <v>472</v>
       </c>
       <c r="F22" t="str">
         <v>0</v>
       </c>
       <c r="G22" t="str">
-        <v>796</v>
+        <v>472</v>
       </c>
       <c r="H22" t="str">
         <v>0</v>
@@ -18763,33 +18700,30 @@
         <v>1</v>
       </c>
       <c r="O22" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P22" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>РЕТИНАЙТ сыворотка для лица 30 мл</v>
+        <v>Ламеллярный крем для рук с мочевиной, увлажняющий и питательный с маслом кокоса, Алтея, 75 мл</v>
       </c>
       <c r="B23" t="str">
-        <v>99000125142</v>
+        <v>99000114729</v>
       </c>
       <c r="C23" t="str">
-        <v>retinait_syvorotka_1</v>
+        <v>krem_dlya_ruk_75ml</v>
       </c>
       <c r="D23" t="str">
-        <v>4.60332E+12</v>
+        <v>4660417421452</v>
       </c>
       <c r="E23" t="str">
-        <v>780</v>
+        <v>371</v>
       </c>
       <c r="F23" t="str">
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>780</v>
+        <v>371</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -18813,272 +18747,19 @@
         <v>1</v>
       </c>
       <c r="O23" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Крем для лица Ретинайт с церамидами, 50 мл</v>
-      </c>
-      <c r="B24" t="str">
-        <v>99000137436</v>
-      </c>
-      <c r="C24" t="str">
-        <v>retinait_krem_01_50m</v>
-      </c>
-      <c r="D24" t="str">
-        <v>4.66042E+12</v>
-      </c>
-      <c r="E24" t="str">
-        <v>717</v>
-      </c>
-      <c r="F24" t="str">
-        <v>0</v>
-      </c>
-      <c r="G24" t="str">
-        <v>717</v>
-      </c>
-      <c r="H24" t="str">
-        <v>0</v>
-      </c>
-      <c r="I24" t="str">
-        <v>1</v>
-      </c>
-      <c r="J24" t="str">
-        <v>0</v>
-      </c>
-      <c r="K24" t="str">
-        <v>1</v>
-      </c>
-      <c r="L24" t="str">
-        <v>0</v>
-      </c>
-      <c r="M24" t="str">
-        <v>0</v>
-      </c>
-      <c r="N24" t="str">
-        <v>1</v>
-      </c>
-      <c r="O24" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Ретинайт 0,5 экспресс-омоложение Anti-Age Липосомальный комплекс ретинола 0,5 + Ниацинамид 50 мл</v>
-      </c>
-      <c r="B25" t="str">
-        <v>99000131675</v>
-      </c>
-      <c r="C25" t="str">
-        <v>retinait_krem_05_50m</v>
-      </c>
-      <c r="D25" t="str">
-        <v>4.66042E+12</v>
-      </c>
-      <c r="E25" t="str">
-        <v>702</v>
-      </c>
-      <c r="F25" t="str">
-        <v>0</v>
-      </c>
-      <c r="G25" t="str">
-        <v>702</v>
-      </c>
-      <c r="H25" t="str">
-        <v>0</v>
-      </c>
-      <c r="I25" t="str">
-        <v>1</v>
-      </c>
-      <c r="J25" t="str">
-        <v>0</v>
-      </c>
-      <c r="K25" t="str">
-        <v>1</v>
-      </c>
-      <c r="L25" t="str">
-        <v>0</v>
-      </c>
-      <c r="M25" t="str">
-        <v>0</v>
-      </c>
-      <c r="N25" t="str">
-        <v>1</v>
-      </c>
-      <c r="O25" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Шампунь для роста волос, от выпадения волос профессиональный, Алтея, 250 мл</v>
-      </c>
-      <c r="B26" t="str">
-        <v>99000076213</v>
-      </c>
-      <c r="C26" t="str">
-        <v>shampun_dlya_rosta_2</v>
-      </c>
-      <c r="D26" t="str">
-        <v>4.67002E+12</v>
-      </c>
-      <c r="E26" t="str">
-        <v>461</v>
-      </c>
-      <c r="F26" t="str">
-        <v>0</v>
-      </c>
-      <c r="G26" t="str">
-        <v>461</v>
-      </c>
-      <c r="H26" t="str">
-        <v>0</v>
-      </c>
-      <c r="I26" t="str">
-        <v>1</v>
-      </c>
-      <c r="J26" t="str">
-        <v>0</v>
-      </c>
-      <c r="K26" t="str">
-        <v>1</v>
-      </c>
-      <c r="L26" t="str">
-        <v>0</v>
-      </c>
-      <c r="M26" t="str">
-        <v>0</v>
-      </c>
-      <c r="N26" t="str">
-        <v>1</v>
-      </c>
-      <c r="O26" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Средство косметическое для ухода за волосами: масло для бороды, маркировка: Алтея.</v>
-      </c>
-      <c r="B27" t="str">
-        <v>99000076215</v>
-      </c>
-      <c r="C27" t="str">
-        <v>maslo_dlya_borodi_50</v>
-      </c>
-      <c r="D27" t="str">
-        <v>4.61017E+12</v>
-      </c>
-      <c r="E27" t="str">
-        <v>422</v>
-      </c>
-      <c r="F27" t="str">
-        <v>0</v>
-      </c>
-      <c r="G27" t="str">
-        <v>422</v>
-      </c>
-      <c r="H27" t="str">
-        <v>0</v>
-      </c>
-      <c r="I27" t="str">
-        <v>1</v>
-      </c>
-      <c r="J27" t="str">
-        <v>0</v>
-      </c>
-      <c r="K27" t="str">
-        <v>1</v>
-      </c>
-      <c r="L27" t="str">
-        <v>0</v>
-      </c>
-      <c r="M27" t="str">
-        <v>0</v>
-      </c>
-      <c r="N27" t="str">
-        <v>1</v>
-      </c>
-      <c r="O27" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Гель для интимной гигиены с молочной кислотой, Алтея, Интимвита, 300 мл</v>
-      </c>
-      <c r="B28" t="str">
-        <v>99000114723</v>
-      </c>
-      <c r="C28" t="str">
-        <v>intimvita_300ml</v>
-      </c>
-      <c r="D28" t="str">
-        <v>4.63008E+12</v>
-      </c>
-      <c r="E28" t="str">
-        <v>337</v>
-      </c>
-      <c r="F28" t="str">
-        <v>0</v>
-      </c>
-      <c r="G28" t="str">
-        <v>337</v>
-      </c>
-      <c r="H28" t="str">
-        <v>0</v>
-      </c>
-      <c r="I28" t="str">
-        <v>1</v>
-      </c>
-      <c r="J28" t="str">
-        <v>0</v>
-      </c>
-      <c r="K28" t="str">
-        <v>1</v>
-      </c>
-      <c r="L28" t="str">
-        <v>0</v>
-      </c>
-      <c r="M28" t="str">
-        <v>0</v>
-      </c>
-      <c r="N28" t="str">
-        <v>1</v>
-      </c>
-      <c r="O28" t="str">
-        <v>46231</v>
-      </c>
-      <c r="P28" t="str">
-        <v/>
+        <v>29.7.2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -19112,15 +18793,15 @@
         <v>1</v>
       </c>
       <c r="K1" t="str">
-        <v>46231</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>АЛТЕЯ-KRSPF50</v>
+        <v>АЛТЕЯ-SYVNIAC</v>
       </c>
       <c r="B2" t="str">
-        <v>Крем солнцезащитный СПФ 50 для лица 50 мл</v>
+        <v>Сыворотка для лица ниацинамидом 5% от прыщей и акне антивозрастная от пигментных пятен</v>
       </c>
       <c r="C2" t="str">
         <v>1</v>
@@ -19129,68 +18810,68 @@
         <v>0</v>
       </c>
       <c r="E2" t="str">
-        <v>701.5</v>
+        <v>669,6</v>
       </c>
       <c r="F2" t="str">
-        <v>132.6</v>
+        <v>120</v>
       </c>
       <c r="G2" t="str">
-        <v>455.98</v>
+        <v>435,24</v>
       </c>
       <c r="H2" t="str">
-        <v>245.52</v>
+        <v>234,36</v>
       </c>
       <c r="I2" t="str">
-        <v>krem_spf50_50ml</v>
+        <v>syvorotka_niacin_05_30ml</v>
       </c>
       <c r="J2" t="str">
         <v>1</v>
       </c>
       <c r="K2" t="str">
-        <v>46231</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>АЛТЕЯ-RETINT1</v>
+        <v>АЛТЕЯ-PSORAL5</v>
       </c>
       <c r="B3" t="str">
-        <v>Сыворотка с ретинолом 1% для лица от морщин антивозрастная Алтея 30 мл</v>
+        <v>Мазь от псориаза и дерматита крем от зуда Алтея Псорал 50 мл</v>
       </c>
       <c r="C3" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="str">
         <v>0</v>
       </c>
       <c r="E3" t="str">
-        <v>660</v>
+        <v>782</v>
       </c>
       <c r="F3" t="str">
-        <v>143.82</v>
+        <v>262,84</v>
       </c>
       <c r="G3" t="str">
-        <v>429</v>
+        <v>508,3</v>
       </c>
       <c r="H3" t="str">
-        <v>231</v>
+        <v>273,7</v>
       </c>
       <c r="I3" t="str">
-        <v>retinait_syvorotka_1_30ml</v>
+        <v>psoral_50ml</v>
       </c>
       <c r="J3" t="str">
         <v>1</v>
       </c>
       <c r="K3" t="str">
-        <v>46231</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>АЛТЕЯ-TERMSPR</v>
+        <v>АЛТЕЯ-GELDLBR</v>
       </c>
       <c r="B4" t="str">
-        <v>Спрей для волос 17 в 1 восстанавливающий с кератином Алтея 200 мл</v>
+        <v>Гель для бритья мужской охлаждающий с ментолом Алтея 300 мл</v>
       </c>
       <c r="C4" t="str">
         <v>1</v>
@@ -19199,33 +18880,33 @@
         <v>0</v>
       </c>
       <c r="E4" t="str">
-        <v>326</v>
+        <v>529,25</v>
       </c>
       <c r="F4" t="str">
-        <v>116.1</v>
+        <v>125,68</v>
       </c>
       <c r="G4" t="str">
-        <v>234.72</v>
+        <v>381,06</v>
       </c>
       <c r="H4" t="str">
-        <v>91.28</v>
+        <v>148,19</v>
       </c>
       <c r="I4" t="str">
-        <v>termo_sprei_200ml</v>
+        <v>gel_dlya_britya_300ml</v>
       </c>
       <c r="J4" t="str">
         <v>1</v>
       </c>
       <c r="K4" t="str">
-        <v>46231</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>АЛТЕЯ-KREMRST</v>
+        <v>АЛТЕЯ-PENKAKD</v>
       </c>
       <c r="B5" t="str">
-        <v>Крем масло от растяжек для беременных и подростков с эластином Алтея 200 мл</v>
+        <v>Пенка для укладки кудрявых волос Алтея 150 мл</v>
       </c>
       <c r="C5" t="str">
         <v>1</v>
@@ -19234,33 +18915,33 @@
         <v>0</v>
       </c>
       <c r="E5" t="str">
-        <v>355</v>
+        <v>527,45</v>
       </c>
       <c r="F5" t="str">
-        <v>151.2</v>
+        <v>137,7</v>
       </c>
       <c r="G5" t="str">
-        <v>255.6</v>
+        <v>379,76</v>
       </c>
       <c r="H5" t="str">
-        <v>99.4</v>
+        <v>147,69</v>
       </c>
       <c r="I5" t="str">
-        <v>krem_ot_rastyazhek</v>
+        <v>penka_kudryavii_metod_150ml</v>
       </c>
       <c r="J5" t="str">
         <v>1</v>
       </c>
       <c r="K5" t="str">
-        <v>46231</v>
+        <v>29.07.2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>АЛТЕЯ-REMYVRS</v>
+        <v>АЛТЕЯ-RETIDER</v>
       </c>
       <c r="B6" t="str">
-        <v>Ремувер для снятия ресниц Алтея 18 г</v>
+        <v>Крем для лица с ретинолом 0.5 антивозрастной от морщин Алтея Ретидерм 50 мл</v>
       </c>
       <c r="C6" t="str">
         <v>1</v>
@@ -19269,30 +18950,65 @@
         <v>0</v>
       </c>
       <c r="E6" t="str">
-        <v>341</v>
+        <v>249,45</v>
       </c>
       <c r="F6" t="str">
-        <v>80.92</v>
+        <v>91,54</v>
       </c>
       <c r="G6" t="str">
-        <v>245.52</v>
+        <v>179,6</v>
       </c>
       <c r="H6" t="str">
-        <v>95.48</v>
+        <v>69,85</v>
       </c>
       <c r="I6" t="str">
-        <v>nabor_remuver_kremovii</v>
+        <v>retiderm_50ml</v>
       </c>
       <c r="J6" t="str">
         <v>1</v>
       </c>
       <c r="K6" t="str">
-        <v>46231</v>
+        <v>29.07.2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>АЛТЕЯ-SHPPERH</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Шампунь от перхоти лечебный с климбазолом Алтея 250 мл</v>
+      </c>
+      <c r="C7" t="str">
+        <v>1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>0</v>
+      </c>
+      <c r="E7" t="str">
+        <v>388,45</v>
+      </c>
+      <c r="F7" t="str">
+        <v>106,2</v>
+      </c>
+      <c r="G7" t="str">
+        <v>279,68</v>
+      </c>
+      <c r="H7" t="str">
+        <v>108,77</v>
+      </c>
+      <c r="I7" t="str">
+        <v>shampun_protiv_perhoti_250ml</v>
+      </c>
+      <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>29.07.2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/external_sources/retail_network_sales.xlsx
+++ b/data/external_sources/retail_network_sales.xlsx
@@ -408,10 +408,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C1" t="str">
         <v>Дата выгрузки</v>
@@ -638,13 +638,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E2" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/d5/59/68ab6975-901a-4e04-b812-11a05618dea7.jpg</v>
@@ -680,40 +680,40 @@
         <v>Нет</v>
       </c>
       <c r="P2" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>0</v>
+      </c>
+      <c r="R2" t="str">
+        <v>1</v>
+      </c>
+      <c r="S2" t="str">
         <v>2</v>
       </c>
-      <c r="Q2" t="str">
-        <v>1234</v>
-      </c>
-      <c r="R2" t="str">
-        <v>0</v>
-      </c>
-      <c r="S2" t="str">
-        <v>1</v>
-      </c>
       <c r="T2" t="str">
-        <v>642</v>
+        <v>1367</v>
       </c>
       <c r="U2" t="str">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="V2" t="str">
+        <v>0</v>
+      </c>
+      <c r="W2" t="str">
+        <v>0</v>
+      </c>
+      <c r="X2" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="str">
         <v>2</v>
       </c>
-      <c r="W2" t="str">
-        <v>1234</v>
-      </c>
-      <c r="X2" t="str">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="str">
-        <v>1</v>
-      </c>
       <c r="Z2" t="str">
-        <v>642</v>
+        <v>1367</v>
       </c>
       <c r="AA2" t="str">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="AB2" t="str">
         <v>0</v>
@@ -865,13 +865,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E3" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e00a36c6-60d1-4483-9902-255f85130f9e.jpg</v>
@@ -907,10 +907,10 @@
         <v>Нет</v>
       </c>
       <c r="P3" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="str">
-        <v>727</v>
+        <v>1477</v>
       </c>
       <c r="R3" t="str">
         <v>3</v>
@@ -919,16 +919,16 @@
         <v>1</v>
       </c>
       <c r="T3" t="str">
-        <v>750</v>
+        <v>634</v>
       </c>
       <c r="U3" t="str">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="V3" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" t="str">
-        <v>727</v>
+        <v>1477</v>
       </c>
       <c r="X3" t="str">
         <v>3</v>
@@ -937,10 +937,10 @@
         <v>1</v>
       </c>
       <c r="Z3" t="str">
-        <v>750</v>
+        <v>634</v>
       </c>
       <c r="AA3" t="str">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AB3" t="str">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E4" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c7280d72-d323-4237-947d-4008c0dc7662.jpg</v>
@@ -1143,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="str">
-        <v>1454</v>
+        <v>726</v>
       </c>
       <c r="U4" t="str">
         <v>2</v>
@@ -1161,10 +1161,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="str">
-        <v>1454</v>
+        <v>726</v>
       </c>
       <c r="AA4" t="str">
         <v>0</v>
@@ -1319,13 +1319,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E5" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/f1/ab/41252906-b46d-4d89-958f-c65e501f9426.jpg</v>
@@ -1361,40 +1361,40 @@
         <v>Нет</v>
       </c>
       <c r="P5" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="str">
-        <v>882</v>
+        <v>0</v>
       </c>
       <c r="R5" t="str">
         <v>1</v>
       </c>
       <c r="S5" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="str">
-        <v>0</v>
+        <v>2914</v>
       </c>
       <c r="U5" t="str">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="V5" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="str">
-        <v>882</v>
+        <v>0</v>
       </c>
       <c r="X5" t="str">
         <v>1</v>
       </c>
       <c r="Y5" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z5" t="str">
-        <v>0</v>
+        <v>2914</v>
       </c>
       <c r="AA5" t="str">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="str">
         <v>0</v>
@@ -1546,13 +1546,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E6" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2f576c8d-8046-4678-878e-b25637ae380b.jpg</v>
@@ -1588,40 +1588,40 @@
         <v>Нет</v>
       </c>
       <c r="P6" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="str">
-        <v>0</v>
+        <v>1740</v>
       </c>
       <c r="R6" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" t="str">
-        <v>2757</v>
+        <v>2210</v>
       </c>
       <c r="U6" t="str">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="V6" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W6" t="str">
-        <v>0</v>
+        <v>1740</v>
       </c>
       <c r="X6" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z6" t="str">
-        <v>2757</v>
+        <v>2210</v>
       </c>
       <c r="AA6" t="str">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="AB6" t="str">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E7" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/2e/9e/71e42c30-4aa3-44ff-b62c-44b50cfdfa3a.png</v>
@@ -1815,13 +1815,13 @@
         <v>Нет</v>
       </c>
       <c r="P7" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="str">
-        <v>605</v>
+        <v>3089</v>
       </c>
       <c r="R7" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S7" t="str">
         <v>0</v>
@@ -1830,16 +1830,16 @@
         <v>0</v>
       </c>
       <c r="U7" t="str">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="V7" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W7" t="str">
-        <v>605</v>
+        <v>3089</v>
       </c>
       <c r="X7" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="str">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="AA7" t="str">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB7" t="str">
         <v>0</v>
@@ -2000,31 +2000,31 @@
         <v>1</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E8" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2b6f374c-300f-4096-bce3-74be8e0aae55.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/cb/7a/6d9ba164-a17b-43f1-9832-48efe4aabf92.png</v>
       </c>
       <c r="F8" t="str">
-        <v>Сыворотка с ретинолом 0,25% для лица от морщин антивозрастная</v>
+        <v>Сыворотка для лица с ниацинамидом для лица антивозрастная, от пигментных пятен, пигментации</v>
       </c>
       <c r="G8" t="str">
-        <v>4 640 523 970 099</v>
+        <v>4 603 312 714 069</v>
       </c>
       <c r="H8" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I8" t="str">
-        <v>MPL580332</v>
+        <v>MPL583154</v>
       </c>
       <c r="J8" t="str">
-        <v>retinait_syvorotka_025_30ml</v>
+        <v>syvorotka_dlya_lica_30ml_v2</v>
       </c>
       <c r="K8" t="str">
         <v>Сыворотка для лица</v>
@@ -2042,40 +2042,40 @@
         <v>Нет</v>
       </c>
       <c r="P8" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="str">
-        <v>722</v>
+        <v>2367</v>
       </c>
       <c r="R8" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="str">
+        <v>1</v>
+      </c>
+      <c r="T8" t="str">
+        <v>584</v>
+      </c>
+      <c r="U8" t="str">
+        <v>141</v>
+      </c>
+      <c r="V8" t="str">
+        <v>4</v>
+      </c>
+      <c r="W8" t="str">
+        <v>2367</v>
+      </c>
+      <c r="X8" t="str">
         <v>2</v>
       </c>
-      <c r="T8" t="str">
-        <v>1672</v>
-      </c>
-      <c r="U8" t="str">
-        <v>69</v>
-      </c>
-      <c r="V8" t="str">
-        <v>1</v>
-      </c>
-      <c r="W8" t="str">
-        <v>722</v>
-      </c>
-      <c r="X8" t="str">
-        <v>0</v>
-      </c>
       <c r="Y8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="str">
-        <v>1672</v>
+        <v>584</v>
       </c>
       <c r="AA8" t="str">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="AB8" t="str">
         <v>0</v>
@@ -2227,31 +2227,31 @@
         <v>1</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E9" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e15e1be0-e1f4-4e80-9e76-e8fc23c616c9.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2b6f374c-300f-4096-bce3-74be8e0aae55.jpg</v>
       </c>
       <c r="F9" t="str">
-        <v>Сыворотка для лица ниацинамидом 5% от прыщей и акне антивозрастная от пигментных пятен</v>
+        <v>Сыворотка с ретинолом 0,25% для лица от морщин антивозрастная</v>
       </c>
       <c r="G9" t="str">
-        <v>4 640 523 970 297</v>
+        <v>4 640 523 970 099</v>
       </c>
       <c r="H9" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I9" t="str">
-        <v>MPL580326</v>
+        <v>MPL580332</v>
       </c>
       <c r="J9" t="str">
-        <v>syvorotka_niacin_05_30ml</v>
+        <v>retinait_syvorotka_025_30ml</v>
       </c>
       <c r="K9" t="str">
         <v>Сыворотка для лица</v>
@@ -2269,40 +2269,40 @@
         <v>Нет</v>
       </c>
       <c r="P9" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="str">
-        <v>612</v>
+        <v>3756</v>
       </c>
       <c r="R9" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="str">
         <v>1</v>
       </c>
       <c r="T9" t="str">
-        <v>612</v>
+        <v>722</v>
       </c>
       <c r="U9" t="str">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="V9" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W9" t="str">
-        <v>612</v>
+        <v>3756</v>
       </c>
       <c r="X9" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="str">
         <v>1</v>
       </c>
       <c r="Z9" t="str">
-        <v>612</v>
+        <v>722</v>
       </c>
       <c r="AA9" t="str">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="AB9" t="str">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="BW9" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2454,13 +2454,13 @@
         <v>1</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E10" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/d9/54/8d4a32cd-2f2a-4689-a8a5-82e0abc22ea3.jpg</v>
@@ -2496,40 +2496,40 @@
         <v>Нет</v>
       </c>
       <c r="P10" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="str">
-        <v>3000</v>
+        <v>1709</v>
       </c>
       <c r="R10" t="str">
         <v>3</v>
       </c>
       <c r="S10" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T10" t="str">
-        <v>765</v>
+        <v>3015</v>
       </c>
       <c r="U10" t="str">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="V10" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W10" t="str">
-        <v>3000</v>
+        <v>1709</v>
       </c>
       <c r="X10" t="str">
         <v>3</v>
       </c>
       <c r="Y10" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z10" t="str">
-        <v>765</v>
+        <v>3015</v>
       </c>
       <c r="AA10" t="str">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AB10" t="str">
         <v>0</v>
@@ -2681,13 +2681,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E11" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/7af399db-987f-4537-8f7c-c33e02778178.jpg</v>
@@ -2723,40 +2723,40 @@
         <v>Нет</v>
       </c>
       <c r="P11" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="str">
-        <v>0</v>
+        <v>1230</v>
       </c>
       <c r="R11" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="str">
         <v>3</v>
       </c>
       <c r="T11" t="str">
-        <v>1776</v>
+        <v>1769</v>
       </c>
       <c r="U11" t="str">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="V11" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" t="str">
-        <v>0</v>
+        <v>1230</v>
       </c>
       <c r="X11" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="str">
         <v>3</v>
       </c>
       <c r="Z11" t="str">
-        <v>1776</v>
+        <v>1769</v>
       </c>
       <c r="AA11" t="str">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="AB11" t="str">
         <v>0</v>
@@ -2908,13 +2908,13 @@
         <v>1</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E12" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/62/50/b959c799-edb3-4886-ab19-732ee8a7f4d6.jpg</v>
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="Q12" t="str">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="R12" t="str">
         <v>0</v>
@@ -2965,13 +2965,13 @@
         <v>0</v>
       </c>
       <c r="U12" t="str">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V12" t="str">
         <v>1</v>
       </c>
       <c r="W12" t="str">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="X12" t="str">
         <v>0</v>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="str">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB12" t="str">
         <v>0</v>
@@ -3135,34 +3135,34 @@
         <v>1</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E13" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/bc1165dc-d231-4cf6-a720-915675cd6e42.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2f7a7537-5358-4736-b3fc-a56a54b2e6b9.jpg</v>
       </c>
       <c r="F13" t="str">
-        <v>Воск стик для укладки и фиксации волос</v>
+        <v>Сыворотка для роста ресниц и бровей, гель для роста</v>
       </c>
       <c r="G13" t="str">
-        <v>4 670 207 150 196</v>
+        <v>4 656 738 598 843</v>
       </c>
       <c r="H13" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I13" t="str">
-        <v>MPL553766</v>
+        <v>MPL536269</v>
       </c>
       <c r="J13" t="str">
-        <v>vosk_stik_15ml</v>
+        <v>syvorotka_dlya_rosta_6ml_v2</v>
       </c>
       <c r="K13" t="str">
-        <v>Воск для укладки волос</v>
+        <v>Гель для роста ресниц и бровей</v>
       </c>
       <c r="L13" t="str">
         <v>В продаже</v>
@@ -3189,10 +3189,10 @@
         <v>2</v>
       </c>
       <c r="T13" t="str">
-        <v>640</v>
+        <v>806</v>
       </c>
       <c r="U13" t="str">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="V13" t="str">
         <v>0</v>
@@ -3207,10 +3207,10 @@
         <v>2</v>
       </c>
       <c r="Z13" t="str">
-        <v>640</v>
+        <v>806</v>
       </c>
       <c r="AA13" t="str">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="AB13" t="str">
         <v>0</v>
@@ -3336,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="BQ13" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR13" t="str">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         <v>1</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E14" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/95/1a/6dd84ed9-0dab-4ad2-8e72-ae7d1736952d.jpg</v>
@@ -3404,40 +3404,40 @@
         <v>Нет</v>
       </c>
       <c r="P14" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="str">
-        <v>3843</v>
+        <v>757</v>
       </c>
       <c r="R14" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S14" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="str">
-        <v>1691</v>
+        <v>2780</v>
       </c>
       <c r="U14" t="str">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="V14" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W14" t="str">
-        <v>3843</v>
+        <v>757</v>
       </c>
       <c r="X14" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z14" t="str">
-        <v>1115</v>
+        <v>2780</v>
       </c>
       <c r="AA14" t="str">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB14" t="str">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="str">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="str">
         <v>1</v>
@@ -3589,13 +3589,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E15" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/54713ce5-1bd3-4ba5-80d2-781e1b551420.jpg</v>
@@ -3631,40 +3631,40 @@
         <v>Нет</v>
       </c>
       <c r="P15" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="str">
+        <v>0</v>
+      </c>
+      <c r="R15" t="str">
+        <v>0</v>
+      </c>
+      <c r="S15" t="str">
+        <v>1</v>
+      </c>
+      <c r="T15" t="str">
         <v>459</v>
       </c>
-      <c r="R15" t="str">
-        <v>0</v>
-      </c>
-      <c r="S15" t="str">
-        <v>2</v>
-      </c>
-      <c r="T15" t="str">
-        <v>804</v>
-      </c>
       <c r="U15" t="str">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V15" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="str">
+        <v>0</v>
+      </c>
+      <c r="X15" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="str">
         <v>459</v>
       </c>
-      <c r="X15" t="str">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="str">
-        <v>2</v>
-      </c>
-      <c r="Z15" t="str">
-        <v>804</v>
-      </c>
       <c r="AA15" t="str">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AB15" t="str">
         <v>0</v>
@@ -3816,34 +3816,34 @@
         <v>1</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E16" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c90ca866-48a4-4af9-8f17-1af620906883.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/4822bd34-9fce-40b0-9167-bf7265647db0.jpg</v>
       </c>
       <c r="F16" t="str">
-        <v>Крем для век и кожи вокруг глаз</v>
+        <v>Скраб пилинг для кожи головы</v>
       </c>
       <c r="G16" t="str">
-        <v>4 670 020 498 918</v>
+        <v>4 660 417 421 476</v>
       </c>
       <c r="H16" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I16" t="str">
-        <v>MPL534118</v>
+        <v>MPL534263</v>
       </c>
       <c r="J16" t="str">
-        <v>krem_dlya_vek_30ml</v>
+        <v>skrab_babl_gam_200ml</v>
       </c>
       <c r="K16" t="str">
-        <v>Крем для лица</v>
+        <v>Скраб для кожи головы</v>
       </c>
       <c r="L16" t="str">
         <v>В продаже</v>
@@ -3861,37 +3861,37 @@
         <v>2</v>
       </c>
       <c r="Q16" t="str">
-        <v>1220</v>
+        <v>1031</v>
       </c>
       <c r="R16" t="str">
         <v>0</v>
       </c>
       <c r="S16" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="str">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="U16" t="str">
-        <v>204</v>
+        <v>66</v>
       </c>
       <c r="V16" t="str">
         <v>2</v>
       </c>
       <c r="W16" t="str">
-        <v>1220</v>
+        <v>1031</v>
       </c>
       <c r="X16" t="str">
         <v>0</v>
       </c>
       <c r="Y16" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="str">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="str">
-        <v>188</v>
+        <v>64</v>
       </c>
       <c r="AB16" t="str">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="str">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="AS16" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="str">
         <v>0</v>
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="BK16" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="str">
         <v>0</v>
@@ -4017,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="BQ16" t="str">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="str">
         <v>0</v>
@@ -4043,34 +4043,34 @@
         <v>1</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E17" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/7b62942f-efab-4a37-bf26-4b4d44ac08ad.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c90ca866-48a4-4af9-8f17-1af620906883.jpg</v>
       </c>
       <c r="F17" t="str">
-        <v>Сыворотка с ретинолом 1% для лица от морщин антивозрастная</v>
+        <v>Крем для век и кожи вокруг глаз</v>
       </c>
       <c r="G17" t="str">
-        <v>4 603 320 465 403</v>
+        <v>4 670 020 498 918</v>
       </c>
       <c r="H17" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I17" t="str">
-        <v>MPL533706</v>
+        <v>MPL534118</v>
       </c>
       <c r="J17" t="str">
-        <v>retinait_syvorotka_1_30ml</v>
+        <v>krem_dlya_vek_30ml</v>
       </c>
       <c r="K17" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L17" t="str">
         <v>В продаже</v>
@@ -4085,13 +4085,13 @@
         <v>Нет</v>
       </c>
       <c r="P17" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="str">
-        <v>1314</v>
+        <v>1995</v>
       </c>
       <c r="R17" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="str">
         <v>0</v>
@@ -4100,16 +4100,16 @@
         <v>0</v>
       </c>
       <c r="U17" t="str">
-        <v>2</v>
+        <v>199</v>
       </c>
       <c r="V17" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W17" t="str">
-        <v>1314</v>
+        <v>1995</v>
       </c>
       <c r="X17" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="str">
         <v>0</v>
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="str">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="AB17" t="str">
         <v>0</v>
@@ -4136,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="AG17" t="str">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH17" t="str">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="AS17" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT17" t="str">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="BK17" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL17" t="str">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="BQ17" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BR17" t="str">
         <v>0</v>
@@ -4270,34 +4270,34 @@
         <v>1</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E18" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9a2f609a-6b3f-4324-872d-a6560c803def.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/7b62942f-efab-4a37-bf26-4b4d44ac08ad.jpg</v>
       </c>
       <c r="F18" t="str">
-        <v>Крем для лица с липосомальным ретинолом 1% Ретинайт</v>
+        <v>Сыворотка с ретинолом 1% для лица от морщин антивозрастная</v>
       </c>
       <c r="G18" t="str">
-        <v>4 660 417 421 605</v>
+        <v>4 603 320 465 403</v>
       </c>
       <c r="H18" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I18" t="str">
-        <v>MPL532549</v>
+        <v>MPL533706</v>
       </c>
       <c r="J18" t="str">
-        <v>retinait_krem_1_50ml</v>
+        <v>retinait_syvorotka_1_30ml</v>
       </c>
       <c r="K18" t="str">
-        <v>Крем для лица</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L18" t="str">
         <v>В продаже</v>
@@ -4312,166 +4312,166 @@
         <v>Нет</v>
       </c>
       <c r="P18" t="str">
+        <v>7</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>4216</v>
+      </c>
+      <c r="R18" t="str">
+        <v>1</v>
+      </c>
+      <c r="S18" t="str">
         <v>2</v>
       </c>
-      <c r="Q18" t="str">
-        <v>1688</v>
-      </c>
-      <c r="R18" t="str">
+      <c r="T18" t="str">
+        <v>1178</v>
+      </c>
+      <c r="U18" t="str">
+        <v>100</v>
+      </c>
+      <c r="V18" t="str">
+        <v>7</v>
+      </c>
+      <c r="W18" t="str">
+        <v>4216</v>
+      </c>
+      <c r="X18" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="str">
         <v>2</v>
       </c>
-      <c r="S18" t="str">
-        <v>1</v>
-      </c>
-      <c r="T18" t="str">
-        <v>775</v>
-      </c>
-      <c r="U18" t="str">
-        <v>129</v>
-      </c>
-      <c r="V18" t="str">
+      <c r="Z18" t="str">
+        <v>1178</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>98</v>
+      </c>
+      <c r="AB18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="str">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="str">
         <v>2</v>
-      </c>
-      <c r="W18" t="str">
-        <v>1688</v>
-      </c>
-      <c r="X18" t="str">
-        <v>2</v>
-      </c>
-      <c r="Y18" t="str">
-        <v>1</v>
-      </c>
-      <c r="Z18" t="str">
-        <v>775</v>
-      </c>
-      <c r="AA18" t="str">
-        <v>100</v>
-      </c>
-      <c r="AB18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="str">
-        <v>9</v>
-      </c>
-      <c r="AH18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="str">
-        <v>2</v>
-      </c>
-      <c r="AN18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="str">
-        <v>1</v>
-      </c>
-      <c r="AT18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="str">
-        <v>2</v>
-      </c>
-      <c r="AZ18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK18" t="str">
-        <v>5</v>
-      </c>
-      <c r="BL18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BM18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BN18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BO18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BP18" t="str">
-        <v>0</v>
-      </c>
-      <c r="BQ18" t="str">
-        <v>10</v>
       </c>
       <c r="BR18" t="str">
         <v>0</v>
@@ -4497,31 +4497,31 @@
         <v>1</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E19" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/ff447efc-130b-40a7-baf9-b3f41132e53d.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9a2f609a-6b3f-4324-872d-a6560c803def.jpg</v>
       </c>
       <c r="F19" t="str">
-        <v>Крем для лица с липосомальным ретинолом 0,25% Ретинайт</v>
+        <v>Крем для лица с липосомальным ретинолом 1% Ретинайт</v>
       </c>
       <c r="G19" t="str">
-        <v>4 660 417 421 599</v>
+        <v>4 660 417 421 605</v>
       </c>
       <c r="H19" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I19" t="str">
-        <v>MPL532421</v>
+        <v>MPL532549</v>
       </c>
       <c r="J19" t="str">
-        <v>retinait_krem_025_50ml</v>
+        <v>retinait_krem_1_50ml</v>
       </c>
       <c r="K19" t="str">
         <v>Крем для лица</v>
@@ -4539,40 +4539,40 @@
         <v>Нет</v>
       </c>
       <c r="P19" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="str">
-        <v>699</v>
+        <v>2842</v>
       </c>
       <c r="R19" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S19" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T19" t="str">
-        <v>699</v>
+        <v>2438</v>
       </c>
       <c r="U19" t="str">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="V19" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W19" t="str">
-        <v>699</v>
+        <v>2842</v>
       </c>
       <c r="X19" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="str">
-        <v>699</v>
+        <v>2438</v>
       </c>
       <c r="AA19" t="str">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="AB19" t="str">
         <v>0</v>
@@ -4590,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AH19" t="str">
         <v>0</v>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="AS19" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AT19" t="str">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AY19" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ19" t="str">
         <v>0</v>
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="BK19" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL19" t="str">
         <v>0</v>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="BQ19" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BR19" t="str">
         <v>0</v>
@@ -4724,31 +4724,31 @@
         <v>1</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E20" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/1b3a299f-fa04-4897-8bd6-2f2523fa8458.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/ff447efc-130b-40a7-baf9-b3f41132e53d.jpg</v>
       </c>
       <c r="F20" t="str">
-        <v>Крем точечный против прыщей, акне, комедонов, угрей и черных точек</v>
+        <v>Крем для лица с липосомальным ретинолом 0,25% Ретинайт</v>
       </c>
       <c r="G20" t="str">
-        <v>4 660 417 420 110</v>
+        <v>4 660 417 421 599</v>
       </c>
       <c r="H20" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I20" t="str">
-        <v>MPL497134</v>
+        <v>MPL532421</v>
       </c>
       <c r="J20" t="str">
-        <v>gel_antiakne_20ml_v2</v>
+        <v>retinait_krem_025_50ml</v>
       </c>
       <c r="K20" t="str">
         <v>Крем для лица</v>
@@ -4766,154 +4766,154 @@
         <v>Нет</v>
       </c>
       <c r="P20" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="str">
-        <v>1532</v>
+        <v>1352</v>
       </c>
       <c r="R20" t="str">
+        <v>2</v>
+      </c>
+      <c r="S20" t="str">
+        <v>0</v>
+      </c>
+      <c r="T20" t="str">
+        <v>0</v>
+      </c>
+      <c r="U20" t="str">
+        <v>132</v>
+      </c>
+      <c r="V20" t="str">
+        <v>2</v>
+      </c>
+      <c r="W20" t="str">
+        <v>1352</v>
+      </c>
+      <c r="X20" t="str">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="str">
+        <v>112</v>
+      </c>
+      <c r="AB20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="str">
         <v>3</v>
       </c>
-      <c r="S20" t="str">
-        <v>7</v>
-      </c>
-      <c r="T20" t="str">
-        <v>2782</v>
-      </c>
-      <c r="U20" t="str">
-        <v>82</v>
-      </c>
-      <c r="V20" t="str">
+      <c r="AH20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="str">
+        <v>2</v>
+      </c>
+      <c r="AN20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="str">
         <v>3</v>
       </c>
-      <c r="W20" t="str">
-        <v>1149</v>
-      </c>
-      <c r="X20" t="str">
+      <c r="AT20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="str">
         <v>3</v>
       </c>
-      <c r="Y20" t="str">
-        <v>7</v>
-      </c>
-      <c r="Z20" t="str">
-        <v>2782</v>
-      </c>
-      <c r="AA20" t="str">
-        <v>74</v>
-      </c>
-      <c r="AB20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="str">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ20" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK20" t="str">
-        <v>0</v>
-      </c>
       <c r="BL20" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM20" t="str">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="BN20" t="str">
         <v>0</v>
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="BQ20" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BR20" t="str">
         <v>0</v>
@@ -4951,34 +4951,34 @@
         <v>1</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E21" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3dab943a-3db8-4732-a73e-22565b77500f.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/1b3a299f-fa04-4897-8bd6-2f2523fa8458.jpg</v>
       </c>
       <c r="F21" t="str">
-        <v>Спрей для роста и от выпадения волос</v>
+        <v>Крем точечный против прыщей, акне, комедонов, угрей и черных точек</v>
       </c>
       <c r="G21" t="str">
-        <v>4 603 320 465 359</v>
+        <v>4 660 417 420 110</v>
       </c>
       <c r="H21" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I21" t="str">
-        <v>MPL484941</v>
+        <v>MPL497134</v>
       </c>
       <c r="J21" t="str">
-        <v>sprei_buster_100ml</v>
+        <v>gel_antiakne_20ml_v2</v>
       </c>
       <c r="K21" t="str">
-        <v>Спрей для ухода за волосами</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L21" t="str">
         <v>В продаже</v>
@@ -4993,40 +4993,40 @@
         <v>Нет</v>
       </c>
       <c r="P21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="str">
-        <v>1010</v>
+        <v>403</v>
       </c>
       <c r="R21" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S21" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T21" t="str">
-        <v>0</v>
+        <v>2318</v>
       </c>
       <c r="U21" t="str">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="V21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W21" t="str">
-        <v>1010</v>
+        <v>403</v>
       </c>
       <c r="X21" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z21" t="str">
-        <v>0</v>
+        <v>2318</v>
       </c>
       <c r="AA21" t="str">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="AB21" t="str">
         <v>0</v>
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="AG21" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="str">
         <v>0</v>
@@ -5080,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="AS21" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="str">
         <v>0</v>
@@ -5098,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="AY21" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="str">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="BK21" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BL21" t="str">
         <v>0</v>
@@ -5143,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="BN21" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO21" t="str">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="BQ21" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BR21" t="str">
         <v>0</v>
@@ -5178,34 +5178,34 @@
         <v>1</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E22" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c244b0f9-e819-4adb-bd5b-f607dbc0cf04.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/63e4e620-5efc-4ad7-bbfb-077d4e99ec12.jpg</v>
       </c>
       <c r="F22" t="str">
-        <v>Крем для кудрявых и вьющихся волос</v>
+        <v>Крем для укладки волос</v>
       </c>
       <c r="G22" t="str">
-        <v>4 603 320 465 441</v>
+        <v>4 603 320 465 304</v>
       </c>
       <c r="H22" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I22" t="str">
-        <v>MPL483098</v>
+        <v>MPL485625</v>
       </c>
       <c r="J22" t="str">
-        <v>curly_method_300ml</v>
+        <v>matte_wax_50ml</v>
       </c>
       <c r="K22" t="str">
-        <v>Крем для укладки волос</v>
+        <v>Воск для укладки волос</v>
       </c>
       <c r="L22" t="str">
         <v>В продаже</v>
@@ -5220,40 +5220,40 @@
         <v>Нет</v>
       </c>
       <c r="P22" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="str">
-        <v>3579</v>
+        <v>449</v>
       </c>
       <c r="R22" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T22" t="str">
-        <v>6680</v>
+        <v>556</v>
       </c>
       <c r="U22" t="str">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="V22" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W22" t="str">
-        <v>3579</v>
+        <v>449</v>
       </c>
       <c r="X22" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="str">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="str">
-        <v>6037</v>
+        <v>556</v>
       </c>
       <c r="AA22" t="str">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="AB22" t="str">
         <v>0</v>
@@ -5265,50 +5265,50 @@
         <v>0</v>
       </c>
       <c r="AE22" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="str">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="str">
+        <v>3</v>
+      </c>
+      <c r="AH22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="str">
         <v>2</v>
       </c>
-      <c r="AH22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="str">
-        <v>4</v>
-      </c>
       <c r="AT22" t="str">
         <v>0</v>
       </c>
@@ -5343,43 +5343,43 @@
         <v>0</v>
       </c>
       <c r="BE22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="str">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="str">
         <v>2</v>
-      </c>
-      <c r="BF22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BL22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BM22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BN22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BO22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BP22" t="str">
-        <v>0</v>
-      </c>
-      <c r="BQ22" t="str">
-        <v>0</v>
       </c>
       <c r="BR22" t="str">
         <v>0</v>
@@ -5405,34 +5405,34 @@
         <v>1</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E23" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/fc7f937b-2361-418e-ae9f-3918b47523d7.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3dab943a-3db8-4732-a73e-22565b77500f.jpg</v>
       </c>
       <c r="F23" t="str">
-        <v>Разглаживающий крем для волос, для непослушных или кудрявых волос для кончиков</v>
+        <v>Спрей для роста и от выпадения волос</v>
       </c>
       <c r="G23" t="str">
-        <v>4 603 320 465 465</v>
+        <v>4 603 320 465 359</v>
       </c>
       <c r="H23" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I23" t="str">
-        <v>MPL477653</v>
+        <v>MPL484941</v>
       </c>
       <c r="J23" t="str">
-        <v>silk_hair_300ml</v>
+        <v>sprei_buster_100ml</v>
       </c>
       <c r="K23" t="str">
-        <v>Крем для укладки волос</v>
+        <v>Спрей для ухода за волосами</v>
       </c>
       <c r="L23" t="str">
         <v>В продаже</v>
@@ -5447,40 +5447,40 @@
         <v>Нет</v>
       </c>
       <c r="P23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="str">
-        <v>452</v>
+        <v>1262</v>
       </c>
       <c r="R23" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S23" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T23" t="str">
-        <v>452</v>
+        <v>1899</v>
       </c>
       <c r="U23" t="str">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="V23" t="str">
         <v>1</v>
       </c>
       <c r="W23" t="str">
-        <v>452</v>
+        <v>631</v>
       </c>
       <c r="X23" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="str">
-        <v>452</v>
+        <v>1899</v>
       </c>
       <c r="AA23" t="str">
-        <v>176</v>
+        <v>66</v>
       </c>
       <c r="AB23" t="str">
         <v>0</v>
@@ -5516,44 +5516,44 @@
         <v>0</v>
       </c>
       <c r="AM23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="str">
         <v>4</v>
       </c>
-      <c r="AN23" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="str">
+      <c r="AT23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="str">
         <v>2</v>
       </c>
-      <c r="AT23" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="str">
-        <v>0</v>
-      </c>
       <c r="AZ23" t="str">
         <v>0</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="BE23" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="str">
         <v>0</v>
@@ -5588,13 +5588,13 @@
         <v>0</v>
       </c>
       <c r="BK23" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL23" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM23" t="str">
-        <v>0</v>
+        <v>631</v>
       </c>
       <c r="BN23" t="str">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="BQ23" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BR23" t="str">
         <v>0</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="BW23" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -5632,34 +5632,34 @@
         <v>1</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E24" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e50770dd-caa8-4478-b9f2-0ac1b5692608.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c244b0f9-e819-4adb-bd5b-f607dbc0cf04.jpg</v>
       </c>
       <c r="F24" t="str">
-        <v>Тоник для лица от прыщей и черных точек очищающий</v>
+        <v>Крем для кудрявых и вьющихся волос</v>
       </c>
       <c r="G24" t="str">
-        <v>4 670 020 498 499</v>
+        <v>4 603 320 465 441</v>
       </c>
       <c r="H24" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I24" t="str">
-        <v>MPL440013</v>
+        <v>MPL483098</v>
       </c>
       <c r="J24" t="str">
-        <v>tonik_dlya_lica_200ml</v>
+        <v>curly_method_300ml</v>
       </c>
       <c r="K24" t="str">
-        <v>Тоник для лица</v>
+        <v>Крем для укладки волос</v>
       </c>
       <c r="L24" t="str">
         <v>В продаже</v>
@@ -5674,40 +5674,40 @@
         <v>Нет</v>
       </c>
       <c r="P24" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="str">
-        <v>0</v>
+        <v>2203</v>
       </c>
       <c r="R24" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S24" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T24" t="str">
-        <v>288</v>
+        <v>3500</v>
       </c>
       <c r="U24" t="str">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="V24" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W24" t="str">
-        <v>0</v>
+        <v>2203</v>
       </c>
       <c r="X24" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z24" t="str">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="AA24" t="str">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AB24" t="str">
         <v>0</v>
@@ -5725,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="AG24" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="str">
         <v>0</v>
@@ -5737,13 +5737,13 @@
         <v>0</v>
       </c>
       <c r="AK24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="str">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="str">
         <v>0</v>
@@ -5761,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="AS24" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT24" t="str">
         <v>0</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="BE24" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF24" t="str">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="BW24" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -5859,34 +5859,34 @@
         <v>1</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E25" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/89bcceec-1c50-47a2-8033-c4a8bed335b7.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/fc7f937b-2361-418e-ae9f-3918b47523d7.jpg</v>
       </c>
       <c r="F25" t="str">
-        <v>Гель для бровей с коллагеном и эластином, фиксация на 24 часа</v>
+        <v>Разглаживающий крем для волос, для непослушных или кудрявых волос для кончиков</v>
       </c>
       <c r="G25" t="str">
-        <v>4 676 574 657 436</v>
+        <v>4 603 320 465 465</v>
       </c>
       <c r="H25" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I25" t="str">
-        <v>MPL411155</v>
+        <v>MPL477653</v>
       </c>
       <c r="J25" t="str">
-        <v>gel_brows_5ml</v>
+        <v>silk_hair_300ml</v>
       </c>
       <c r="K25" t="str">
-        <v>Гель для бровей</v>
+        <v>Крем для укладки волос</v>
       </c>
       <c r="L25" t="str">
         <v>В продаже</v>
@@ -5904,37 +5904,37 @@
         <v>1</v>
       </c>
       <c r="Q25" t="str">
-        <v>338</v>
+        <v>452</v>
       </c>
       <c r="R25" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T25" t="str">
-        <v>0</v>
+        <v>1285</v>
       </c>
       <c r="U25" t="str">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="V25" t="str">
         <v>1</v>
       </c>
       <c r="W25" t="str">
-        <v>338</v>
+        <v>452</v>
       </c>
       <c r="X25" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="str">
-        <v>0</v>
+        <v>1285</v>
       </c>
       <c r="AA25" t="str">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="AB25" t="str">
         <v>0</v>
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="AG25" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="str">
         <v>0</v>
@@ -5970,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="AM25" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN25" t="str">
         <v>0</v>
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="AS25" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT25" t="str">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="BE25" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF25" t="str">
         <v>0</v>
@@ -6042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="BK25" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL25" t="str">
         <v>0</v>
@@ -6060,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="BQ25" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR25" t="str">
         <v>0</v>
@@ -6078,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="BW25" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -6086,34 +6086,34 @@
         <v>1</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E26" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9c79f9bf-96d6-4540-9aab-14f3a9799933.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/89bcceec-1c50-47a2-8033-c4a8bed335b7.jpg</v>
       </c>
       <c r="F26" t="str">
-        <v>Кровавый кислотный пилинг для лица от прыщей с Альфа и бета-гидроксикислотами</v>
+        <v>Гель для бровей с коллагеном и эластином, фиксация на 24 часа</v>
       </c>
       <c r="G26" t="str">
-        <v>4 670 020 498 208</v>
+        <v>4 676 574 657 436</v>
       </c>
       <c r="H26" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I26" t="str">
-        <v>MPL411098</v>
+        <v>MPL411155</v>
       </c>
       <c r="J26" t="str">
-        <v>krovavii_piling_30ml</v>
+        <v>gel_brows_5ml</v>
       </c>
       <c r="K26" t="str">
-        <v>Пилинг для лица</v>
+        <v>Гель для бровей</v>
       </c>
       <c r="L26" t="str">
         <v>В продаже</v>
@@ -6128,166 +6128,166 @@
         <v>Нет</v>
       </c>
       <c r="P26" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="str">
-        <v>1566</v>
+        <v>846</v>
       </c>
       <c r="R26" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="str">
+        <v>0</v>
+      </c>
+      <c r="T26" t="str">
+        <v>0</v>
+      </c>
+      <c r="U26" t="str">
+        <v>15</v>
+      </c>
+      <c r="V26" t="str">
+        <v>2</v>
+      </c>
+      <c r="W26" t="str">
+        <v>846</v>
+      </c>
+      <c r="X26" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="str">
+        <v>8</v>
+      </c>
+      <c r="AB26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="str">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="str">
         <v>6</v>
-      </c>
-      <c r="T26" t="str">
-        <v>3351</v>
-      </c>
-      <c r="U26" t="str">
-        <v>209</v>
-      </c>
-      <c r="V26" t="str">
-        <v>3</v>
-      </c>
-      <c r="W26" t="str">
-        <v>1566</v>
-      </c>
-      <c r="X26" t="str">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="str">
-        <v>5</v>
-      </c>
-      <c r="Z26" t="str">
-        <v>2838</v>
-      </c>
-      <c r="AA26" t="str">
-        <v>179</v>
-      </c>
-      <c r="AB26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="str">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="str">
-        <v>513</v>
-      </c>
-      <c r="AG26" t="str">
-        <v>2</v>
-      </c>
-      <c r="AH26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="str">
-        <v>4</v>
-      </c>
-      <c r="AN26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="str">
-        <v>6</v>
-      </c>
-      <c r="AT26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="str">
-        <v>2</v>
-      </c>
-      <c r="AZ26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK26" t="str">
-        <v>6</v>
-      </c>
-      <c r="BL26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BM26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BN26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BO26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BP26" t="str">
-        <v>0</v>
-      </c>
-      <c r="BQ26" t="str">
-        <v>10</v>
       </c>
       <c r="BR26" t="str">
         <v>0</v>
@@ -6313,34 +6313,34 @@
         <v>1</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E27" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/44834e6a-6c3a-4072-80b2-89989f472f81.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/b7/3a/109f8e49-63d9-4359-967c-defcd581f3a9.jpg</v>
       </c>
       <c r="F27" t="str">
-        <v>Маска для роста волос с перцем</v>
+        <v>Маска для лица очищающая</v>
       </c>
       <c r="G27" t="str">
-        <v>4 603 320 465 366</v>
+        <v>4 670 020 498 741</v>
       </c>
       <c r="H27" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I27" t="str">
-        <v>MPL411097</v>
+        <v>MPL411103</v>
       </c>
       <c r="J27" t="str">
-        <v>maska-batter_dlya_rosta_500ml</v>
+        <v>maska_dlya_lica_100ml</v>
       </c>
       <c r="K27" t="str">
-        <v>Маска для волос</v>
+        <v>Маска для лица</v>
       </c>
       <c r="L27" t="str">
         <v>В продаже</v>
@@ -6358,73 +6358,73 @@
         <v>1</v>
       </c>
       <c r="Q27" t="str">
-        <v>497</v>
+        <v>787</v>
       </c>
       <c r="R27" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="str">
+        <v>0</v>
+      </c>
+      <c r="T27" t="str">
+        <v>0</v>
+      </c>
+      <c r="U27" t="str">
+        <v>174</v>
+      </c>
+      <c r="V27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W27" t="str">
+        <v>787</v>
+      </c>
+      <c r="X27" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="str">
+        <v>156</v>
+      </c>
+      <c r="AB27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="str">
         <v>4</v>
       </c>
-      <c r="T27" t="str">
-        <v>1628</v>
-      </c>
-      <c r="U27" t="str">
-        <v>148</v>
-      </c>
-      <c r="V27" t="str">
-        <v>1</v>
-      </c>
-      <c r="W27" t="str">
-        <v>497</v>
-      </c>
-      <c r="X27" t="str">
-        <v>2</v>
-      </c>
-      <c r="Y27" t="str">
+      <c r="AH27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="str">
         <v>4</v>
-      </c>
-      <c r="Z27" t="str">
-        <v>1628</v>
-      </c>
-      <c r="AA27" t="str">
-        <v>130</v>
-      </c>
-      <c r="AB27" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="str">
-        <v>2</v>
-      </c>
-      <c r="AH27" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="str">
-        <v>2</v>
       </c>
       <c r="AN27" t="str">
         <v>0</v>
@@ -6460,7 +6460,7 @@
         <v>0</v>
       </c>
       <c r="AY27" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ27" t="str">
         <v>0</v>
@@ -6496,7 +6496,7 @@
         <v>0</v>
       </c>
       <c r="BK27" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL27" t="str">
         <v>0</v>
@@ -6514,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="BQ27" t="str">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BR27" t="str">
         <v>0</v>
@@ -6540,34 +6540,34 @@
         <v>1</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E28" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/1e0dc6e9-3db8-4def-b687-323e61f82f64.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9c79f9bf-96d6-4540-9aab-14f3a9799933.jpg</v>
       </c>
       <c r="F28" t="str">
-        <v>Шампунь для роста волос, от выпадения волос профессиональный</v>
+        <v>Кровавый кислотный пилинг для лица от прыщей с Альфа и бета-гидроксикислотами</v>
       </c>
       <c r="G28" t="str">
-        <v>4 670 020 496 747</v>
+        <v>4 670 020 498 208</v>
       </c>
       <c r="H28" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I28" t="str">
-        <v>MPL381169</v>
+        <v>MPL411098</v>
       </c>
       <c r="J28" t="str">
-        <v>shampun_dlya_rosta_250ml</v>
+        <v>krovavii_piling_30ml</v>
       </c>
       <c r="K28" t="str">
-        <v>Шампунь для волос</v>
+        <v>Пилинг для лица</v>
       </c>
       <c r="L28" t="str">
         <v>В продаже</v>
@@ -6582,10 +6582,10 @@
         <v>Нет</v>
       </c>
       <c r="P28" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="str">
-        <v>885</v>
+        <v>5313</v>
       </c>
       <c r="R28" t="str">
         <v>3</v>
@@ -6594,47 +6594,47 @@
         <v>3</v>
       </c>
       <c r="T28" t="str">
-        <v>1296</v>
+        <v>1532</v>
       </c>
       <c r="U28" t="str">
-        <v>194</v>
+        <v>252</v>
       </c>
       <c r="V28" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W28" t="str">
-        <v>885</v>
+        <v>5313</v>
       </c>
       <c r="X28" t="str">
         <v>3</v>
       </c>
       <c r="Y28" t="str">
+        <v>3</v>
+      </c>
+      <c r="Z28" t="str">
+        <v>1532</v>
+      </c>
+      <c r="AA28" t="str">
+        <v>222</v>
+      </c>
+      <c r="AB28" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="str">
         <v>2</v>
       </c>
-      <c r="Z28" t="str">
-        <v>819</v>
-      </c>
-      <c r="AA28" t="str">
-        <v>173</v>
-      </c>
-      <c r="AB28" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="str">
-        <v>3</v>
-      </c>
       <c r="AH28" t="str">
         <v>0</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="AM28" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN28" t="str">
         <v>0</v>
@@ -6687,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="AY28" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ28" t="str">
         <v>0</v>
@@ -6717,13 +6717,13 @@
         <v>0</v>
       </c>
       <c r="BI28" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ28" t="str">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="BK28" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BL28" t="str">
         <v>0</v>
@@ -6741,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="BQ28" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BR28" t="str">
         <v>0</v>
@@ -6767,34 +6767,34 @@
         <v>1</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E29" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c2abf989-9fc4-4168-8006-a2f0a7996e13.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/44834e6a-6c3a-4072-80b2-89989f472f81.jpg</v>
       </c>
       <c r="F29" t="str">
-        <v>Крем для лица с ретинолом, Ретидерм</v>
+        <v>Маска для роста волос с перцем</v>
       </c>
       <c r="G29" t="str">
-        <v>4 610 172 186 219</v>
+        <v>4 603 320 465 366</v>
       </c>
       <c r="H29" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I29" t="str">
-        <v>MPL381168</v>
+        <v>MPL411097</v>
       </c>
       <c r="J29" t="str">
-        <v>retiderm_50ml</v>
+        <v>maska-batter_dlya_rosta_500ml</v>
       </c>
       <c r="K29" t="str">
-        <v>Крем для лица</v>
+        <v>Маска для волос</v>
       </c>
       <c r="L29" t="str">
         <v>В продаже</v>
@@ -6809,40 +6809,40 @@
         <v>Нет</v>
       </c>
       <c r="P29" t="str">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="str">
-        <v>4091</v>
+        <v>1554</v>
       </c>
       <c r="R29" t="str">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="S29" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T29" t="str">
-        <v>2685</v>
+        <v>0</v>
       </c>
       <c r="U29" t="str">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="V29" t="str">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="W29" t="str">
-        <v>4091</v>
+        <v>1554</v>
       </c>
       <c r="X29" t="str">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="str">
-        <v>2685</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="str">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AB29" t="str">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="AG29" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="str">
         <v>0</v>
@@ -6878,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="AM29" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN29" t="str">
         <v>0</v>
@@ -6896,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="AS29" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT29" t="str">
         <v>0</v>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="BK29" t="str">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL29" t="str">
         <v>0</v>
@@ -6959,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="BN29" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO29" t="str">
         <v>0</v>
@@ -6968,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="BQ29" t="str">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BR29" t="str">
         <v>0</v>
@@ -6994,34 +6994,34 @@
         <v>1</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E30" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3b0cad57-5015-4075-b4f5-949c25941740.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/1e0dc6e9-3db8-4def-b687-323e61f82f64.jpg</v>
       </c>
       <c r="F30" t="str">
-        <v>Маска для волос профессиональная с кератином восстанавливающая, бальзам для волос</v>
+        <v>Шампунь для роста волос, от выпадения волос профессиональный</v>
       </c>
       <c r="G30" t="str">
-        <v>4 670 020 497 546</v>
+        <v>4 670 020 496 747</v>
       </c>
       <c r="H30" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I30" t="str">
-        <v>MPL381090</v>
+        <v>MPL381169</v>
       </c>
       <c r="J30" t="str">
-        <v>maska-batter_250ml</v>
+        <v>shampun_dlya_rosta_250ml</v>
       </c>
       <c r="K30" t="str">
-        <v>Маска для волос</v>
+        <v>Шампунь для волос</v>
       </c>
       <c r="L30" t="str">
         <v>В продаже</v>
@@ -7036,46 +7036,46 @@
         <v>Нет</v>
       </c>
       <c r="P30" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="str">
-        <v>479</v>
+        <v>859</v>
       </c>
       <c r="R30" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S30" t="str">
+        <v>5</v>
+      </c>
+      <c r="T30" t="str">
+        <v>1761</v>
+      </c>
+      <c r="U30" t="str">
+        <v>193</v>
+      </c>
+      <c r="V30" t="str">
         <v>2</v>
       </c>
-      <c r="T30" t="str">
-        <v>1123</v>
-      </c>
-      <c r="U30" t="str">
-        <v>146</v>
-      </c>
-      <c r="V30" t="str">
-        <v>0</v>
-      </c>
       <c r="W30" t="str">
-        <v>0</v>
+        <v>859</v>
       </c>
       <c r="X30" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y30" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z30" t="str">
-        <v>646</v>
+        <v>1761</v>
       </c>
       <c r="AA30" t="str">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="AB30" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="str">
-        <v>479</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="str">
         <v>0</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="AG30" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH30" t="str">
         <v>0</v>
@@ -7099,13 +7099,13 @@
         <v>0</v>
       </c>
       <c r="AK30" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="str">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN30" t="str">
         <v>0</v>
@@ -7123,7 +7123,7 @@
         <v>0</v>
       </c>
       <c r="AS30" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT30" t="str">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="AY30" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ30" t="str">
         <v>0</v>
@@ -7159,7 +7159,7 @@
         <v>0</v>
       </c>
       <c r="BE30" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="str">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="BQ30" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BR30" t="str">
         <v>0</v>
@@ -7221,34 +7221,34 @@
         <v>1</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E31" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/bbccc824-8896-4e69-bd67-4be5d9a9aaf7.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/c2abf989-9fc4-4168-8006-a2f0a7996e13.jpg</v>
       </c>
       <c r="F31" t="str">
-        <v>Крем с мочевиной увлажняющий, 10% мочевина</v>
+        <v>Крем для лица с ретинолом, Ретидерм</v>
       </c>
       <c r="G31" t="str">
-        <v>4 611 113 000 977</v>
+        <v>4 610 172 186 219</v>
       </c>
       <c r="H31" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I31" t="str">
-        <v>MPL379168</v>
+        <v>MPL381168</v>
       </c>
       <c r="J31" t="str">
-        <v>kremshelk_100ml</v>
+        <v>retiderm_50ml</v>
       </c>
       <c r="K31" t="str">
-        <v>Крем для тела</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L31" t="str">
         <v>В продаже</v>
@@ -7263,40 +7263,40 @@
         <v>Нет</v>
       </c>
       <c r="P31" t="str">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q31" t="str">
-        <v>0</v>
+        <v>6708</v>
       </c>
       <c r="R31" t="str">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="S31" t="str">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T31" t="str">
-        <v>370</v>
+        <v>2398</v>
       </c>
       <c r="U31" t="str">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="V31" t="str">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W31" t="str">
-        <v>0</v>
+        <v>6708</v>
       </c>
       <c r="X31" t="str">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Y31" t="str">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="str">
-        <v>370</v>
+        <v>2398</v>
       </c>
       <c r="AA31" t="str">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="AB31" t="str">
         <v>0</v>
@@ -7332,7 +7332,7 @@
         <v>0</v>
       </c>
       <c r="AM31" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN31" t="str">
         <v>0</v>
@@ -7422,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="BQ31" t="str">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BR31" t="str">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="BW31" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -7448,34 +7448,34 @@
         <v>1</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E32" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/99bc620d-d1e4-4442-99ce-a427a86be9b8.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/32ea3c9d-10a8-4da9-b546-ac3df4e3e821.jpg</v>
       </c>
       <c r="F32" t="str">
-        <v>Крем от растяжек для беременных и подростков с эластином</v>
+        <v>Масло для бороды, средство для роста, уход за бородой, смягчающее</v>
       </c>
       <c r="G32" t="str">
-        <v>4 670 020 497 898</v>
+        <v>4 610 172 186 882</v>
       </c>
       <c r="H32" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I32" t="str">
-        <v>MPL379167</v>
+        <v>MPL381091</v>
       </c>
       <c r="J32" t="str">
-        <v>krem_ot_rastyazhek</v>
+        <v>maslo_dlya_borodi_50ml</v>
       </c>
       <c r="K32" t="str">
-        <v>Крем для тела</v>
+        <v>Масло для ухода за бородой</v>
       </c>
       <c r="L32" t="str">
         <v>В продаже</v>
@@ -7490,31 +7490,31 @@
         <v>Нет</v>
       </c>
       <c r="P32" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="str">
-        <v>1456</v>
+        <v>1050</v>
       </c>
       <c r="R32" t="str">
+        <v>0</v>
+      </c>
+      <c r="S32" t="str">
+        <v>0</v>
+      </c>
+      <c r="T32" t="str">
+        <v>0</v>
+      </c>
+      <c r="U32" t="str">
+        <v>102</v>
+      </c>
+      <c r="V32" t="str">
         <v>2</v>
       </c>
-      <c r="S32" t="str">
-        <v>0</v>
-      </c>
-      <c r="T32" t="str">
-        <v>0</v>
-      </c>
-      <c r="U32" t="str">
-        <v>128</v>
-      </c>
-      <c r="V32" t="str">
-        <v>3</v>
-      </c>
       <c r="W32" t="str">
-        <v>1456</v>
+        <v>1050</v>
       </c>
       <c r="X32" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="str">
         <v>0</v>
@@ -7523,7 +7523,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="str">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AB32" t="str">
         <v>0</v>
@@ -7577,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="AS32" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT32" t="str">
         <v>0</v>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="BE32" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="str">
         <v>0</v>
@@ -7631,7 +7631,7 @@
         <v>0</v>
       </c>
       <c r="BK32" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL32" t="str">
         <v>0</v>
@@ -7649,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="BQ32" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BR32" t="str">
         <v>0</v>
@@ -7675,34 +7675,34 @@
         <v>1</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E33" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/00ca3a8d-eecb-4cc4-8710-a0b7ddef9727.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3b0cad57-5015-4075-b4f5-949c25941740.jpg</v>
       </c>
       <c r="F33" t="str">
-        <v>Ламеллярный крем для рук с мочевиной, увлажняющий и питательный с маслом кокоса</v>
+        <v>Маска для волос профессиональная с кератином восстанавливающая, бальзам для волос</v>
       </c>
       <c r="G33" t="str">
-        <v>4 660 417 421 889</v>
+        <v>4 670 020 497 546</v>
       </c>
       <c r="H33" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I33" t="str">
-        <v>MPL379165</v>
+        <v>MPL381090</v>
       </c>
       <c r="J33" t="str">
-        <v>krem_dlya_ruk_75ml</v>
+        <v>maska-batter_250ml</v>
       </c>
       <c r="K33" t="str">
-        <v>Крем для рук</v>
+        <v>Маска для волос</v>
       </c>
       <c r="L33" t="str">
         <v>В продаже</v>
@@ -7717,10 +7717,10 @@
         <v>Нет</v>
       </c>
       <c r="P33" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="str">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="R33" t="str">
         <v>0</v>
@@ -7729,28 +7729,28 @@
         <v>1</v>
       </c>
       <c r="T33" t="str">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="U33" t="str">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="V33" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W33" t="str">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="X33" t="str">
         <v>0</v>
       </c>
       <c r="Y33" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="str">
-        <v>0</v>
+        <v>479</v>
       </c>
       <c r="AA33" t="str">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="AB33" t="str">
         <v>0</v>
@@ -7762,104 +7762,104 @@
         <v>0</v>
       </c>
       <c r="AE33" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="str">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="str">
+        <v>5</v>
+      </c>
+      <c r="AN33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="str">
         <v>3</v>
       </c>
-      <c r="AH33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="str">
+      <c r="AT33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="str">
+        <v>3</v>
+      </c>
+      <c r="AZ33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="str">
         <v>2</v>
       </c>
-      <c r="AT33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="str">
+      <c r="BF33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK33" t="str">
         <v>2</v>
       </c>
-      <c r="AZ33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BF33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ33" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK33" t="str">
-        <v>1</v>
-      </c>
       <c r="BL33" t="str">
         <v>0</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>0</v>
       </c>
       <c r="BQ33" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BR33" t="str">
         <v>0</v>
@@ -7902,34 +7902,34 @@
         <v>1</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E34" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/cb/7a/6d9ba164-a17b-43f1-9832-48efe4aabf92.png</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/bbccc824-8896-4e69-bd67-4be5d9a9aaf7.jpg</v>
       </c>
       <c r="F34" t="str">
-        <v>Сыворотка для лица с ниацинамидом для лица антивозрастная, от пигментных пятен, пигментации</v>
+        <v>Крем с мочевиной увлажняющий, 10% мочевина</v>
       </c>
       <c r="G34" t="str">
-        <v>4 603 312 714 069</v>
+        <v>4 611 113 000 977</v>
       </c>
       <c r="H34" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I34" t="str">
-        <v>MPL583154</v>
+        <v>MPL379168</v>
       </c>
       <c r="J34" t="str">
-        <v>syvorotka_dlya_lica_30ml_v2</v>
+        <v>kremshelk_100ml</v>
       </c>
       <c r="K34" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Крем для тела</v>
       </c>
       <c r="L34" t="str">
         <v>В продаже</v>
@@ -7944,184 +7944,184 @@
         <v>Нет</v>
       </c>
       <c r="P34" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="str">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="R34" t="str">
+        <v>1</v>
+      </c>
+      <c r="S34" t="str">
+        <v>0</v>
+      </c>
+      <c r="T34" t="str">
+        <v>0</v>
+      </c>
+      <c r="U34" t="str">
+        <v>142</v>
+      </c>
+      <c r="V34" t="str">
+        <v>1</v>
+      </c>
+      <c r="W34" t="str">
+        <v>441</v>
+      </c>
+      <c r="X34" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="str">
+        <v>140</v>
+      </c>
+      <c r="AB34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BL34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BN34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BQ34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BS34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BT34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BU34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BV34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BW34" t="str">
         <v>2</v>
-      </c>
-      <c r="S34" t="str">
-        <v>0</v>
-      </c>
-      <c r="T34" t="str">
-        <v>0</v>
-      </c>
-      <c r="U34" t="str">
-        <v>91</v>
-      </c>
-      <c r="V34" t="str">
-        <v>0</v>
-      </c>
-      <c r="W34" t="str">
-        <v>0</v>
-      </c>
-      <c r="X34" t="str">
-        <v>2</v>
-      </c>
-      <c r="Y34" t="str">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="str">
-        <v>91</v>
-      </c>
-      <c r="AB34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="str">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BL34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BM34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BN34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BO34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BP34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BQ34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BR34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BS34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BT34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BU34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BV34" t="str">
-        <v>0</v>
-      </c>
-      <c r="BW34" t="str">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -8129,34 +8129,34 @@
         <v>1</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E35" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/2f7a7537-5358-4736-b3fc-a56a54b2e6b9.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/99bc620d-d1e4-4442-99ce-a427a86be9b8.jpg</v>
       </c>
       <c r="F35" t="str">
-        <v>Сыворотка для роста ресниц и бровей, гель для роста</v>
+        <v>Крем от растяжек для беременных и подростков с эластином</v>
       </c>
       <c r="G35" t="str">
-        <v>4 656 738 598 843</v>
+        <v>4 670 020 497 898</v>
       </c>
       <c r="H35" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I35" t="str">
-        <v>MPL536269</v>
+        <v>MPL379167</v>
       </c>
       <c r="J35" t="str">
-        <v>syvorotka_dlya_rosta_6ml_v2</v>
+        <v>krem_ot_rastyazhek</v>
       </c>
       <c r="K35" t="str">
-        <v>Гель для роста ресниц и бровей</v>
+        <v>Крем для тела</v>
       </c>
       <c r="L35" t="str">
         <v>В продаже</v>
@@ -8171,13 +8171,13 @@
         <v>Нет</v>
       </c>
       <c r="P35" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="str">
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="R35" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S35" t="str">
         <v>0</v>
@@ -8186,16 +8186,16 @@
         <v>0</v>
       </c>
       <c r="U35" t="str">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="V35" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W35" t="str">
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="X35" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y35" t="str">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="str">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AB35" t="str">
         <v>0</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="AG35" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH35" t="str">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="AM35" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN35" t="str">
         <v>0</v>
@@ -8258,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="AS35" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT35" t="str">
         <v>0</v>
@@ -8276,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="AY35" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ35" t="str">
         <v>0</v>
@@ -8294,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="BE35" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF35" t="str">
         <v>0</v>
@@ -8312,7 +8312,7 @@
         <v>0</v>
       </c>
       <c r="BK35" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL35" t="str">
         <v>0</v>
@@ -8330,7 +8330,7 @@
         <v>0</v>
       </c>
       <c r="BQ35" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BR35" t="str">
         <v>0</v>
@@ -8356,34 +8356,34 @@
         <v>1</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C36" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E36" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/4822bd34-9fce-40b0-9167-bf7265647db0.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/fb6b51e2-810a-4d7f-8792-27b4578444b2.jpg</v>
       </c>
       <c r="F36" t="str">
-        <v>Скраб пилинг для кожи головы</v>
+        <v>Крем для лица антивозрастной, крем филлер вокруг глаз, с коллагеном с ниацинамидом</v>
       </c>
       <c r="G36" t="str">
-        <v>4 660 417 421 476</v>
+        <v>4 657 786 831 418</v>
       </c>
       <c r="H36" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I36" t="str">
-        <v>MPL534263</v>
+        <v>MPL379166</v>
       </c>
       <c r="J36" t="str">
-        <v>skrab_babl_gam_200ml</v>
+        <v>krem-filler_15ml</v>
       </c>
       <c r="K36" t="str">
-        <v>Скраб для кожи головы</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L36" t="str">
         <v>В продаже</v>
@@ -8407,13 +8407,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T36" t="str">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="U36" t="str">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="V36" t="str">
         <v>0</v>
@@ -8425,13 +8425,13 @@
         <v>0</v>
       </c>
       <c r="Y36" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="str">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="AA36" t="str">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="AB36" t="str">
         <v>0</v>
@@ -8449,44 +8449,44 @@
         <v>0</v>
       </c>
       <c r="AG36" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="str">
         <v>2</v>
       </c>
-      <c r="AH36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="str">
-        <v>0</v>
-      </c>
       <c r="AT36" t="str">
         <v>0</v>
       </c>
@@ -8539,7 +8539,7 @@
         <v>0</v>
       </c>
       <c r="BK36" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL36" t="str">
         <v>0</v>
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="BQ36" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR36" t="str">
         <v>0</v>
@@ -8583,34 +8583,34 @@
         <v>1</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C37" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E37" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/6d0f15ac-c0b3-4b73-a297-8d570a168876.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/00ca3a8d-eecb-4cc4-8710-a0b7ddef9727.jpg</v>
       </c>
       <c r="F37" t="str">
-        <v>Крем для лица увлажняющий питательный с ниацинамидом</v>
+        <v>Ламеллярный крем для рук с мочевиной, увлажняющий и питательный с маслом кокоса</v>
       </c>
       <c r="G37" t="str">
-        <v>4 603 320 465 342</v>
+        <v>4 660 417 421 889</v>
       </c>
       <c r="H37" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I37" t="str">
-        <v>MPL533896</v>
+        <v>MPL379165</v>
       </c>
       <c r="J37" t="str">
-        <v>pink_pepper_50ml</v>
+        <v>krem_dlya_ruk_75ml</v>
       </c>
       <c r="K37" t="str">
-        <v>Крем для лица</v>
+        <v>Крем для рук</v>
       </c>
       <c r="L37" t="str">
         <v>В продаже</v>
@@ -8625,10 +8625,10 @@
         <v>Нет</v>
       </c>
       <c r="P37" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="str">
-        <v>0</v>
+        <v>1183</v>
       </c>
       <c r="R37" t="str">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="str">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="V37" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="str">
-        <v>0</v>
+        <v>735</v>
       </c>
       <c r="X37" t="str">
         <v>0</v>
@@ -8658,7 +8658,7 @@
         <v>0</v>
       </c>
       <c r="AA37" t="str">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="AB37" t="str">
         <v>0</v>
@@ -8676,7 +8676,7 @@
         <v>0</v>
       </c>
       <c r="AG37" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH37" t="str">
         <v>0</v>
@@ -8694,13 +8694,13 @@
         <v>0</v>
       </c>
       <c r="AM37" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN37" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO37" t="str">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AP37" t="str">
         <v>0</v>
@@ -8712,7 +8712,7 @@
         <v>0</v>
       </c>
       <c r="AS37" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT37" t="str">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="AY37" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ37" t="str">
         <v>0</v>
@@ -8766,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="BK37" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL37" t="str">
         <v>0</v>
@@ -8784,7 +8784,7 @@
         <v>0</v>
       </c>
       <c r="BQ37" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BR37" t="str">
         <v>0</v>
@@ -8810,34 +8810,34 @@
         <v>1</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C38" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E38" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/01/b1/a0f0ab5e-7d32-428e-8d45-ea94ae31836d.png</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/26/17/58467fe1-4682-493c-b6fe-7d86223be0d2.jpg</v>
       </c>
       <c r="F38" t="str">
-        <v>Масло для волос несмываемое</v>
+        <v>Крем для лица антивозрастной со спикулами и ПДРН</v>
       </c>
       <c r="G38" t="str">
-        <v>4 610 172 181 559</v>
+        <v>4 660 417 421 933</v>
       </c>
       <c r="H38" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I38" t="str">
-        <v>MPL498116</v>
+        <v>MPL634181</v>
       </c>
       <c r="J38" t="str">
-        <v>maslo_dlya_volos_parf_110ml_</v>
+        <v>krem_dlya_lica_pdrn_50 ml</v>
       </c>
       <c r="K38" t="str">
-        <v>Масло для волос</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L38" t="str">
         <v>В продаже</v>
@@ -8867,7 +8867,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="str">
-        <v>1</v>
+        <v>217</v>
       </c>
       <c r="V38" t="str">
         <v>0</v>
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="AA38" t="str">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="AB38" t="str">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="BW38" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -9037,34 +9037,34 @@
         <v>1</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C39" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E39" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/63e4e620-5efc-4ad7-bbfb-077d4e99ec12.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/e9/29/0552627e-dd63-4b3c-9bac-d180ba298db2.jpg</v>
       </c>
       <c r="F39" t="str">
-        <v>Крем для укладки волос</v>
+        <v>Термозащитное масло для волос</v>
       </c>
       <c r="G39" t="str">
-        <v>4 603 320 465 304</v>
+        <v>4 640 523 970 334</v>
       </c>
       <c r="H39" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I39" t="str">
-        <v>MPL485625</v>
+        <v>MPL589445</v>
       </c>
       <c r="J39" t="str">
-        <v>matte_wax_50ml</v>
+        <v>termo_maslo_100ml</v>
       </c>
       <c r="K39" t="str">
-        <v>Воск для укладки волос</v>
+        <v>Масло для волос</v>
       </c>
       <c r="L39" t="str">
         <v>В продаже</v>
@@ -9094,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="str">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="V39" t="str">
         <v>0</v>
@@ -9112,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="AA39" t="str">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="AB39" t="str">
         <v>0</v>
@@ -9130,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="AG39" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="str">
         <v>0</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="AS39" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="str">
         <v>0</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="BQ39" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR39" t="str">
         <v>0</v>
@@ -9264,34 +9264,34 @@
         <v>1</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C40" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E40" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/a3901563-1960-431d-af08-2b59339f6884.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e15e1be0-e1f4-4e80-9e76-e8fc23c616c9.jpg</v>
       </c>
       <c r="F40" t="str">
-        <v>Гель для душа женский парфюмированный</v>
+        <v>Сыворотка для лица ниацинамидом 5% от прыщей и акне антивозрастная от пигментных пятен</v>
       </c>
       <c r="G40" t="str">
-        <v>4 603 320 465 267</v>
+        <v>4 640 523 970 297</v>
       </c>
       <c r="H40" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I40" t="str">
-        <v>MPL411108</v>
+        <v>MPL580326</v>
       </c>
       <c r="J40" t="str">
-        <v>gel_parfum_tabacco_vanille_450ml</v>
+        <v>syvorotka_niacin_05_30ml</v>
       </c>
       <c r="K40" t="str">
-        <v>Парфюмированный гель для душа</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L40" t="str">
         <v>В продаже</v>
@@ -9312,7 +9312,7 @@
         <v>0</v>
       </c>
       <c r="R40" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="str">
         <v>0</v>
@@ -9321,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="str">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="V40" t="str">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="str">
         <v>0</v>
@@ -9339,7 +9339,7 @@
         <v>0</v>
       </c>
       <c r="AA40" t="str">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="AB40" t="str">
         <v>0</v>
@@ -9465,7 +9465,7 @@
         <v>0</v>
       </c>
       <c r="BQ40" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR40" t="str">
         <v>0</v>
@@ -9483,7 +9483,7 @@
         <v>0</v>
       </c>
       <c r="BW40" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -9491,34 +9491,34 @@
         <v>1</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C41" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E41" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/b7/3a/109f8e49-63d9-4359-967c-defcd581f3a9.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/bc1165dc-d231-4cf6-a720-915675cd6e42.jpg</v>
       </c>
       <c r="F41" t="str">
-        <v>Маска для лица очищающая</v>
+        <v>Воск стик для укладки и фиксации волос</v>
       </c>
       <c r="G41" t="str">
-        <v>4 670 020 498 741</v>
+        <v>4 670 207 150 196</v>
       </c>
       <c r="H41" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I41" t="str">
-        <v>MPL411103</v>
+        <v>MPL553766</v>
       </c>
       <c r="J41" t="str">
-        <v>maska_dlya_lica_100ml</v>
+        <v>vosk_stik_15ml</v>
       </c>
       <c r="K41" t="str">
-        <v>Маска для лица</v>
+        <v>Воск для укладки волос</v>
       </c>
       <c r="L41" t="str">
         <v>В продаже</v>
@@ -9548,7 +9548,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="str">
-        <v>174</v>
+        <v>85</v>
       </c>
       <c r="V41" t="str">
         <v>0</v>
@@ -9566,7 +9566,7 @@
         <v>0</v>
       </c>
       <c r="AA41" t="str">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="AB41" t="str">
         <v>0</v>
@@ -9584,7 +9584,7 @@
         <v>0</v>
       </c>
       <c r="AG41" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="str">
         <v>0</v>
@@ -9602,7 +9602,7 @@
         <v>0</v>
       </c>
       <c r="AM41" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="str">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="AS41" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="str">
         <v>0</v>
@@ -9638,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="AY41" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="str">
         <v>0</v>
@@ -9674,7 +9674,7 @@
         <v>0</v>
       </c>
       <c r="BK41" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL41" t="str">
         <v>0</v>
@@ -9692,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="BQ41" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR41" t="str">
         <v>0</v>
@@ -9718,34 +9718,34 @@
         <v>1</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C42" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E42" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/df/68/aa39874f-cb9a-4865-95c7-af9a92706ab5.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/6d0f15ac-c0b3-4b73-a297-8d570a168876.jpg</v>
       </c>
       <c r="F42" t="str">
-        <v>Солевой спрей для объема и укладки волос с фиксацией</v>
+        <v>Крем для лица увлажняющий питательный с ниацинамидом</v>
       </c>
       <c r="G42" t="str">
-        <v>4 670 020 498 413</v>
+        <v>4 603 320 465 342</v>
       </c>
       <c r="H42" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I42" t="str">
-        <v>MPL411095</v>
+        <v>MPL533896</v>
       </c>
       <c r="J42" t="str">
-        <v>solevoy_sprei_200ml</v>
+        <v>pink_pepper_50ml</v>
       </c>
       <c r="K42" t="str">
-        <v>Спрей для укладки волос</v>
+        <v>Крем для лица</v>
       </c>
       <c r="L42" t="str">
         <v>В продаже</v>
@@ -9775,7 +9775,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="str">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="V42" t="str">
         <v>0</v>
@@ -9811,7 +9811,7 @@
         <v>0</v>
       </c>
       <c r="AG42" t="str">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="str">
         <v>0</v>
@@ -9829,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="AM42" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="str">
         <v>0</v>
@@ -9883,7 +9883,7 @@
         <v>0</v>
       </c>
       <c r="BE42" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="str">
         <v>0</v>
@@ -9919,7 +9919,7 @@
         <v>0</v>
       </c>
       <c r="BQ42" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BR42" t="str">
         <v>0</v>
@@ -9945,34 +9945,34 @@
         <v>1</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C43" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E43" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e8b7722e-10fd-4f95-8988-f043f9a8d54a.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/01/b1/a0f0ab5e-7d32-428e-8d45-ea94ae31836d.png</v>
       </c>
       <c r="F43" t="str">
-        <v>Термозащита для волос профессиональная с кератином, cыворотка для волос</v>
+        <v>Масло для волос несмываемое</v>
       </c>
       <c r="G43" t="str">
-        <v>4 670 020 497 980</v>
+        <v>4 610 172 181 559</v>
       </c>
       <c r="H43" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I43" t="str">
-        <v>MPL381178</v>
+        <v>MPL498116</v>
       </c>
       <c r="J43" t="str">
-        <v>termo_sprei_200ml</v>
+        <v>maslo_dlya_volos_parf_110ml_</v>
       </c>
       <c r="K43" t="str">
-        <v>Спрей для ухода за волосами</v>
+        <v>Масло для волос</v>
       </c>
       <c r="L43" t="str">
         <v>В продаже</v>
@@ -10172,34 +10172,34 @@
         <v>1</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C44" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E44" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/db6a42fd-0944-471f-966b-32f2132fa06d.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e50770dd-caa8-4478-b9f2-0ac1b5692608.jpg</v>
       </c>
       <c r="F44" t="str">
-        <v>Сыворотка с витамином с, гиалуроновая кислота</v>
+        <v>Тоник для лица от прыщей и черных точек очищающий</v>
       </c>
       <c r="G44" t="str">
-        <v>4 670 020 498 093</v>
+        <v>4 670 020 498 499</v>
       </c>
       <c r="H44" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I44" t="str">
-        <v>MPL381177</v>
+        <v>MPL440013</v>
       </c>
       <c r="J44" t="str">
-        <v>syvorotka_guk_30ml</v>
+        <v>tonik_dlya_lica_200ml</v>
       </c>
       <c r="K44" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Тоник для лица</v>
       </c>
       <c r="L44" t="str">
         <v>В продаже</v>
@@ -10229,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="str">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="V44" t="str">
         <v>0</v>
@@ -10301,7 +10301,7 @@
         <v>0</v>
       </c>
       <c r="AS44" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="str">
         <v>0</v>
@@ -10319,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="AY44" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="str">
         <v>0</v>
@@ -10337,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="BE44" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="str">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="BK44" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL44" t="str">
         <v>0</v>
@@ -10373,7 +10373,7 @@
         <v>0</v>
       </c>
       <c r="BQ44" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR44" t="str">
         <v>0</v>
@@ -10399,34 +10399,34 @@
         <v>1</v>
       </c>
       <c r="B45" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C45" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E45" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/4e59ebb9-c860-44ad-ab36-d1cd7b03c07c.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/a3901563-1960-431d-af08-2b59339f6884.jpg</v>
       </c>
       <c r="F45" t="str">
-        <v>Сыворотка для лица с ниацинамидом от прыщей пигментации</v>
+        <v>Гель для душа женский парфюмированный</v>
       </c>
       <c r="G45" t="str">
-        <v>4 670 020 497 034</v>
+        <v>4 603 320 465 267</v>
       </c>
       <c r="H45" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I45" t="str">
-        <v>MPL381175</v>
+        <v>MPL411108</v>
       </c>
       <c r="J45" t="str">
-        <v>syvorotka_dlya_lica_30ml</v>
+        <v>gel_parfum_tabacco_vanille_450ml</v>
       </c>
       <c r="K45" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Парфюмированный гель для душа</v>
       </c>
       <c r="L45" t="str">
         <v>В продаже</v>
@@ -10456,7 +10456,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V45" t="str">
         <v>0</v>
@@ -10600,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="BQ45" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR45" t="str">
         <v>0</v>
@@ -10626,34 +10626,34 @@
         <v>1</v>
       </c>
       <c r="B46" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C46" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E46" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/ff069309-0bd5-496a-9db7-5d55bfca9f49.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/df/68/aa39874f-cb9a-4865-95c7-af9a92706ab5.jpg</v>
       </c>
       <c r="F46" t="str">
-        <v>Крем-стик для ног от натирания, карандаш от мозолей, мозольный пластырь</v>
+        <v>Солевой спрей для объема и укладки волос с фиксацией</v>
       </c>
       <c r="G46" t="str">
-        <v>4 690 222 978 568</v>
+        <v>4 670 020 498 413</v>
       </c>
       <c r="H46" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I46" t="str">
-        <v>MPL381174</v>
+        <v>MPL411095</v>
       </c>
       <c r="J46" t="str">
-        <v>stik_ot_mozoley</v>
+        <v>solevoy_sprei_200ml</v>
       </c>
       <c r="K46" t="str">
-        <v>Пластырь мозольный</v>
+        <v>Спрей для укладки волос</v>
       </c>
       <c r="L46" t="str">
         <v>В продаже</v>
@@ -10683,116 +10683,116 @@
         <v>0</v>
       </c>
       <c r="U46" t="str">
+        <v>18</v>
+      </c>
+      <c r="V46" t="str">
+        <v>0</v>
+      </c>
+      <c r="W46" t="str">
+        <v>0</v>
+      </c>
+      <c r="X46" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="str">
+        <v>5</v>
+      </c>
+      <c r="AH46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="str">
+        <v>3</v>
+      </c>
+      <c r="AN46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="str">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="str">
         <v>2</v>
       </c>
-      <c r="V46" t="str">
-        <v>0</v>
-      </c>
-      <c r="W46" t="str">
-        <v>0</v>
-      </c>
-      <c r="X46" t="str">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="str">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AY46" t="str">
-        <v>0</v>
-      </c>
-      <c r="AZ46" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA46" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB46" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD46" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE46" t="str">
-        <v>0</v>
-      </c>
       <c r="BF46" t="str">
         <v>0</v>
       </c>
@@ -10827,7 +10827,7 @@
         <v>0</v>
       </c>
       <c r="BQ46" t="str">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BR46" t="str">
         <v>0</v>
@@ -10845,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="BW46" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -10853,34 +10853,34 @@
         <v>1</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C47" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E47" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e300d073-2466-4d42-b162-188d6e4c89a6.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e8b7722e-10fd-4f95-8988-f043f9a8d54a.jpg</v>
       </c>
       <c r="F47" t="str">
-        <v>Шампунь от перхоти с климбазолом</v>
+        <v>Термозащита для волос профессиональная с кератином, cыворотка для волос</v>
       </c>
       <c r="G47" t="str">
-        <v>4 670 020 496 679</v>
+        <v>4 670 020 497 980</v>
       </c>
       <c r="H47" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I47" t="str">
-        <v>MPL381173</v>
+        <v>MPL381178</v>
       </c>
       <c r="J47" t="str">
-        <v>shampun_protiv_perhoti_250ml</v>
+        <v>termo_sprei_200ml</v>
       </c>
       <c r="K47" t="str">
-        <v>Шампунь для волос</v>
+        <v>Спрей для ухода за волосами</v>
       </c>
       <c r="L47" t="str">
         <v>В продаже</v>
@@ -11054,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="BQ47" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR47" t="str">
         <v>0</v>
@@ -11072,7 +11072,7 @@
         <v>0</v>
       </c>
       <c r="BW47" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -11080,34 +11080,34 @@
         <v>1</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C48" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E48" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/796c257d-557a-4cbd-a342-dac9361e9ce2.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/db6a42fd-0944-471f-966b-32f2132fa06d.jpg</v>
       </c>
       <c r="F48" t="str">
-        <v>Ремувер для снятия ресниц</v>
+        <v>Сыворотка с витамином с, гиалуроновая кислота</v>
       </c>
       <c r="G48" t="str">
-        <v>4 629 945 399 213</v>
+        <v>4 670 020 498 093</v>
       </c>
       <c r="H48" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I48" t="str">
-        <v>MPL381167</v>
+        <v>MPL381177</v>
       </c>
       <c r="J48" t="str">
-        <v>nabor_remuver_kremovii</v>
+        <v>syvorotka_guk_30ml</v>
       </c>
       <c r="K48" t="str">
-        <v>Ремувер для снятия нарощенных ресниц</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L48" t="str">
         <v>В продаже</v>
@@ -11137,7 +11137,7 @@
         <v>0</v>
       </c>
       <c r="U48" t="str">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="V48" t="str">
         <v>0</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="AA48" t="str">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="str">
         <v>0</v>
@@ -11173,7 +11173,7 @@
         <v>0</v>
       </c>
       <c r="AG48" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="str">
         <v>0</v>
@@ -11191,7 +11191,7 @@
         <v>0</v>
       </c>
       <c r="AM48" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AN48" t="str">
         <v>0</v>
@@ -11209,7 +11209,7 @@
         <v>0</v>
       </c>
       <c r="AS48" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AT48" t="str">
         <v>0</v>
@@ -11227,7 +11227,7 @@
         <v>0</v>
       </c>
       <c r="AY48" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ48" t="str">
         <v>0</v>
@@ -11245,7 +11245,7 @@
         <v>0</v>
       </c>
       <c r="BE48" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF48" t="str">
         <v>0</v>
@@ -11263,7 +11263,7 @@
         <v>0</v>
       </c>
       <c r="BK48" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL48" t="str">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>0</v>
       </c>
       <c r="BQ48" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BR48" t="str">
         <v>0</v>
@@ -11307,34 +11307,34 @@
         <v>1</v>
       </c>
       <c r="B49" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C49" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E49" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/43e5f404-ab6b-47c4-8f2b-da61e673c04d.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/4e59ebb9-c860-44ad-ab36-d1cd7b03c07c.jpg</v>
       </c>
       <c r="F49" t="str">
-        <v>Гель для удаления кутикулы, ремувер для кутикулы</v>
+        <v>Сыворотка для лица с ниацинамидом от прыщей пигментации</v>
       </c>
       <c r="G49" t="str">
-        <v>4 607 050 974 747</v>
+        <v>4 670 020 497 034</v>
       </c>
       <c r="H49" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I49" t="str">
-        <v>MPL381166</v>
+        <v>MPL381175</v>
       </c>
       <c r="J49" t="str">
-        <v>nabor_remuver_40ml</v>
+        <v>syvorotka_dlya_lica_30ml</v>
       </c>
       <c r="K49" t="str">
-        <v>Гель для удаления кутикулы</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L49" t="str">
         <v>В продаже</v>
@@ -11364,7 +11364,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V49" t="str">
         <v>0</v>
@@ -11508,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="BQ49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR49" t="str">
         <v>0</v>
@@ -11534,34 +11534,34 @@
         <v>1</v>
       </c>
       <c r="B50" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C50" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E50" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9a35a678-ddd0-4f4c-92c1-71678e998c87.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/ff069309-0bd5-496a-9db7-5d55bfca9f49.jpg</v>
       </c>
       <c r="F50" t="str">
-        <v>Пилинг для кожи головы профессиональный скраб от перхоти</v>
+        <v>Крем-стик для ног от натирания, карандаш от мозолей, мозольный пластырь</v>
       </c>
       <c r="G50" t="str">
-        <v>4 670 020 496 761</v>
+        <v>4 690 222 978 568</v>
       </c>
       <c r="H50" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I50" t="str">
-        <v>MPL381095</v>
+        <v>MPL381174</v>
       </c>
       <c r="J50" t="str">
-        <v>piling_100ml</v>
+        <v>stik_ot_mozoley</v>
       </c>
       <c r="K50" t="str">
-        <v>Пилинг для кожи головы</v>
+        <v>Пластырь мозольный</v>
       </c>
       <c r="L50" t="str">
         <v>В продаже</v>
@@ -11591,7 +11591,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V50" t="str">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         <v>0</v>
       </c>
       <c r="BW50" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -11761,34 +11761,34 @@
         <v>1</v>
       </c>
       <c r="B51" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C51" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E51" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e1035672-2f2c-40fe-bdd1-29e73f438dda.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e300d073-2466-4d42-b162-188d6e4c89a6.jpg</v>
       </c>
       <c r="F51" t="str">
-        <v>Пенка для умывания, для снятия макияжа, от постакне</v>
+        <v>Шампунь от перхоти с климбазолом</v>
       </c>
       <c r="G51" t="str">
-        <v>4 630 084 864 777</v>
+        <v>4 670 020 496 679</v>
       </c>
       <c r="H51" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I51" t="str">
-        <v>MPL381093</v>
+        <v>MPL381173</v>
       </c>
       <c r="J51" t="str">
-        <v>penka_160ml</v>
+        <v>shampun_protiv_perhoti_250ml</v>
       </c>
       <c r="K51" t="str">
-        <v>Пенка для снятия макияжа</v>
+        <v>Шампунь для волос</v>
       </c>
       <c r="L51" t="str">
         <v>В продаже</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="BQ51" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR51" t="str">
         <v>0</v>
@@ -11980,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="BW51" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -11988,34 +11988,34 @@
         <v>1</v>
       </c>
       <c r="B52" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C52" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E52" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/32ea3c9d-10a8-4da9-b546-ac3df4e3e821.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/796c257d-557a-4cbd-a342-dac9361e9ce2.jpg</v>
       </c>
       <c r="F52" t="str">
-        <v>Масло для бороды, средство для роста, уход за бородой, смягчающее</v>
+        <v>Ремувер для снятия ресниц</v>
       </c>
       <c r="G52" t="str">
-        <v>4 610 172 186 882</v>
+        <v>4 629 945 399 213</v>
       </c>
       <c r="H52" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I52" t="str">
-        <v>MPL381091</v>
+        <v>MPL381167</v>
       </c>
       <c r="J52" t="str">
-        <v>maslo_dlya_borodi_50ml</v>
+        <v>nabor_remuver_kremovii</v>
       </c>
       <c r="K52" t="str">
-        <v>Масло для ухода за бородой</v>
+        <v>Ремувер для снятия нарощенных ресниц</v>
       </c>
       <c r="L52" t="str">
         <v>В продаже</v>
@@ -12045,7 +12045,7 @@
         <v>0</v>
       </c>
       <c r="U52" t="str">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="V52" t="str">
         <v>0</v>
@@ -12063,7 +12063,7 @@
         <v>0</v>
       </c>
       <c r="AA52" t="str">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AB52" t="str">
         <v>0</v>
@@ -12081,7 +12081,7 @@
         <v>0</v>
       </c>
       <c r="AG52" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH52" t="str">
         <v>0</v>
@@ -12117,7 +12117,7 @@
         <v>0</v>
       </c>
       <c r="AS52" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT52" t="str">
         <v>0</v>
@@ -12135,61 +12135,61 @@
         <v>0</v>
       </c>
       <c r="AY52" t="str">
+        <v>1</v>
+      </c>
+      <c r="AZ52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BB52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BC52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BD52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BE52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BI52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BJ52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BK52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BL52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BM52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BN52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BO52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BP52" t="str">
+        <v>0</v>
+      </c>
+      <c r="BQ52" t="str">
         <v>2</v>
-      </c>
-      <c r="AZ52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BA52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BB52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BC52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BD52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BE52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BF52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BG52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BH52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BI52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BJ52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BK52" t="str">
-        <v>3</v>
-      </c>
-      <c r="BL52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BM52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BN52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BO52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BP52" t="str">
-        <v>0</v>
-      </c>
-      <c r="BQ52" t="str">
-        <v>14</v>
       </c>
       <c r="BR52" t="str">
         <v>0</v>
@@ -12215,34 +12215,34 @@
         <v>1</v>
       </c>
       <c r="B53" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C53" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E53" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/fb6b51e2-810a-4d7f-8792-27b4578444b2.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/43e5f404-ab6b-47c4-8f2b-da61e673c04d.jpg</v>
       </c>
       <c r="F53" t="str">
-        <v>Крем для лица антивозрастной, крем филлер вокруг глаз, с коллагеном с ниацинамидом</v>
+        <v>Гель для удаления кутикулы, ремувер для кутикулы</v>
       </c>
       <c r="G53" t="str">
-        <v>4 657 786 831 418</v>
+        <v>4 607 050 974 747</v>
       </c>
       <c r="H53" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I53" t="str">
-        <v>MPL379166</v>
+        <v>MPL381166</v>
       </c>
       <c r="J53" t="str">
-        <v>krem-filler_15ml</v>
+        <v>nabor_remuver_40ml</v>
       </c>
       <c r="K53" t="str">
-        <v>Крем для лица</v>
+        <v>Гель для удаления кутикулы</v>
       </c>
       <c r="L53" t="str">
         <v>В продаже</v>
@@ -12272,7 +12272,7 @@
         <v>0</v>
       </c>
       <c r="U53" t="str">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="V53" t="str">
         <v>0</v>
@@ -12290,7 +12290,7 @@
         <v>0</v>
       </c>
       <c r="AA53" t="str">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="str">
         <v>0</v>
@@ -12308,7 +12308,7 @@
         <v>0</v>
       </c>
       <c r="AG53" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="str">
         <v>0</v>
@@ -12344,7 +12344,7 @@
         <v>0</v>
       </c>
       <c r="AS53" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT53" t="str">
         <v>0</v>
@@ -12398,7 +12398,7 @@
         <v>0</v>
       </c>
       <c r="BK53" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL53" t="str">
         <v>0</v>
@@ -12416,7 +12416,7 @@
         <v>0</v>
       </c>
       <c r="BQ53" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR53" t="str">
         <v>0</v>
@@ -12442,34 +12442,34 @@
         <v>1</v>
       </c>
       <c r="B54" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C54" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E54" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/6b2c57d3-a40c-42b1-be7c-16e926442f48.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/9a35a678-ddd0-4f4c-92c1-71678e998c87.jpg</v>
       </c>
       <c r="F54" t="str">
-        <v>Гель для бровей с эффектом ламинирования</v>
+        <v>Пилинг для кожи головы профессиональный скраб от перхоти</v>
       </c>
       <c r="G54" t="str">
-        <v>4 609 893 777 394</v>
+        <v>4 670 020 496 761</v>
       </c>
       <c r="H54" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I54" t="str">
-        <v>MPL378889</v>
+        <v>MPL381095</v>
       </c>
       <c r="J54" t="str">
-        <v>gel_dlya_brovei_6ml</v>
+        <v>piling_100ml</v>
       </c>
       <c r="K54" t="str">
-        <v>Гель для бровей</v>
+        <v>Пилинг для кожи головы</v>
       </c>
       <c r="L54" t="str">
         <v>В продаже</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="BQ54" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR54" t="str">
         <v>0</v>
@@ -12661,7 +12661,7 @@
         <v>0</v>
       </c>
       <c r="BW54" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -12669,34 +12669,34 @@
         <v>1</v>
       </c>
       <c r="B55" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C55" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E55" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3f7506e1-6d7b-4bee-ab9f-f0ef40a8a272.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/e1035672-2f2c-40fe-bdd1-29e73f438dda.jpg</v>
       </c>
       <c r="F55" t="str">
-        <v>Энзимная пудра для умывания лица и тела</v>
+        <v>Пенка для умывания, для снятия макияжа, от постакне</v>
       </c>
       <c r="G55" t="str">
-        <v>4 670 020 498 017</v>
+        <v>4 630 084 864 777</v>
       </c>
       <c r="H55" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I55" t="str">
-        <v>MPL378812</v>
+        <v>MPL381093</v>
       </c>
       <c r="J55" t="str">
-        <v>enzim_pudra_80gr</v>
+        <v>penka_160ml</v>
       </c>
       <c r="K55" t="str">
-        <v>Пудра для умывания</v>
+        <v>Пенка для снятия макияжа</v>
       </c>
       <c r="L55" t="str">
         <v>В продаже</v>
@@ -12726,7 +12726,7 @@
         <v>0</v>
       </c>
       <c r="U55" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V55" t="str">
         <v>0</v>
@@ -12780,7 +12780,7 @@
         <v>0</v>
       </c>
       <c r="AM55" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="str">
         <v>0</v>
@@ -12896,34 +12896,34 @@
         <v>1</v>
       </c>
       <c r="B56" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C56" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E56" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/13/4c/1fd02476-339d-45f4-abca-db41c844b1b7.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/6b2c57d3-a40c-42b1-be7c-16e926442f48.jpg</v>
       </c>
       <c r="F56" t="str">
-        <v>Сыворотка для лица увлажняющая с PDRN 10000 ppm</v>
+        <v>Гель для бровей с эффектом ламинирования</v>
       </c>
       <c r="G56" t="str">
-        <v>4 660 417 421 896</v>
+        <v>4 609 893 777 394</v>
       </c>
       <c r="H56" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I56" t="str">
-        <v>MPL667736</v>
+        <v>MPL378889</v>
       </c>
       <c r="J56" t="str">
-        <v>spray-syvorotka_pdrn_100ml</v>
+        <v>gel_dlya_brovei_6ml</v>
       </c>
       <c r="K56" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Гель для бровей</v>
       </c>
       <c r="L56" t="str">
         <v>В продаже</v>
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="U56" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" t="str">
         <v>0</v>
@@ -13097,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="BQ56" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR56" t="str">
         <v>0</v>
@@ -13123,34 +13123,34 @@
         <v>1</v>
       </c>
       <c r="B57" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C57" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E57" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/91847533-cb64-4445-99b2-78cd6d971bb8.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/3f7506e1-6d7b-4bee-ab9f-f0ef40a8a272.jpg</v>
       </c>
       <c r="F57" t="str">
-        <v>Шампунь разглаживающий с BADD для восстановления волос</v>
+        <v>Энзимная пудра для умывания лица и тела</v>
       </c>
       <c r="G57" t="str">
-        <v>7 693 733 020 006</v>
+        <v>4 670 020 498 017</v>
       </c>
       <c r="H57" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I57" t="str">
-        <v>MPL666498</v>
+        <v>MPL378812</v>
       </c>
       <c r="J57" t="str">
-        <v>shampun_BADD_500ml</v>
+        <v>enzim_pudra_80gr</v>
       </c>
       <c r="K57" t="str">
-        <v>Шампунь для волос</v>
+        <v>Пудра для умывания</v>
       </c>
       <c r="L57" t="str">
         <v>В продаже</v>
@@ -13180,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="U57" t="str">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V57" t="str">
         <v>0</v>
@@ -13234,7 +13234,7 @@
         <v>0</v>
       </c>
       <c r="AM57" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN57" t="str">
         <v>0</v>
@@ -13342,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="BW57" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -13350,34 +13350,34 @@
         <v>1</v>
       </c>
       <c r="B58" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C58" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E58" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/c0/79/74ec1d22-a2e4-4738-940b-34d263f718bf.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/13/4c/1fd02476-339d-45f4-abca-db41c844b1b7.jpg</v>
       </c>
       <c r="F58" t="str">
-        <v>Пробиотическая гель-пенка для умывания проблемной кожи</v>
+        <v>Сыворотка для лица увлажняющая с PDRN 10000 ppm</v>
       </c>
       <c r="G58" t="str">
-        <v>4 660 417 422 022</v>
+        <v>4 660 417 421 896</v>
       </c>
       <c r="H58" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I58" t="str">
-        <v>MPL666298</v>
+        <v>MPL667736</v>
       </c>
       <c r="J58" t="str">
-        <v>gel-penka_dlya_lica_150ml</v>
+        <v>spray-syvorotka_pdrn_100ml</v>
       </c>
       <c r="K58" t="str">
-        <v>Пенка для умывания</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L58" t="str">
         <v>В продаже</v>
@@ -13577,34 +13577,34 @@
         <v>1</v>
       </c>
       <c r="B59" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C59" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E59" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/f2/31/37575b2b-76ab-4d35-9929-aa2dfcdf7bf6.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/91847533-cb64-4445-99b2-78cd6d971bb8.jpg</v>
       </c>
       <c r="F59" t="str">
-        <v>Маска-пленка для лица с PDRN, коллагеном и гиалуроновой кислотой, с пептидами</v>
+        <v>Шампунь разглаживающий с BADD для восстановления волос</v>
       </c>
       <c r="G59" t="str">
-        <v>4 660 417 421 964</v>
+        <v>7 693 733 020 006</v>
       </c>
       <c r="H59" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I59" t="str">
-        <v>MPL650362</v>
+        <v>MPL666498</v>
       </c>
       <c r="J59" t="str">
-        <v>lifting_maska_pdrn_75ml</v>
+        <v>shampun_BADD_500ml</v>
       </c>
       <c r="K59" t="str">
-        <v>Маска для лица</v>
+        <v>Шампунь для волос</v>
       </c>
       <c r="L59" t="str">
         <v>В продаже</v>
@@ -13804,34 +13804,34 @@
         <v>1</v>
       </c>
       <c r="B60" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C60" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E60" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/fc/f6/be192d64-456d-4082-892e-58b3852bb6f3.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/c0/79/74ec1d22-a2e4-4738-940b-34d263f718bf.jpg</v>
       </c>
       <c r="F60" t="str">
-        <v>Сыворотка для лица, Интенсивное увлажнение</v>
+        <v>Пробиотическая гель-пенка для умывания проблемной кожи</v>
       </c>
       <c r="G60" t="str">
-        <v>4 660 417 422 008</v>
+        <v>4 660 417 422 022</v>
       </c>
       <c r="H60" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I60" t="str">
-        <v>MPL650361</v>
+        <v>MPL666298</v>
       </c>
       <c r="J60" t="str">
-        <v>syvorotka_dlya_lica_intens_uvl_30ml</v>
+        <v>gel-penka_dlya_lica_150ml</v>
       </c>
       <c r="K60" t="str">
-        <v>Сыворотка для лица</v>
+        <v>Пенка для умывания</v>
       </c>
       <c r="L60" t="str">
         <v>В продаже</v>
@@ -14031,34 +14031,34 @@
         <v>1</v>
       </c>
       <c r="B61" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C61" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E61" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/c2/09/206c885d-46ee-4221-8068-e5e20d1fafba.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/f2/31/37575b2b-76ab-4d35-9929-aa2dfcdf7bf6.jpg</v>
       </c>
       <c r="F61" t="str">
-        <v>Гель для кудрявых волос</v>
+        <v>Маска-пленка для лица с PDRN, коллагеном и гиалуроновой кислотой, с пептидами</v>
       </c>
       <c r="G61" t="str">
-        <v>4 660 417 422 039</v>
+        <v>4 660 417 421 964</v>
       </c>
       <c r="H61" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I61" t="str">
-        <v>MPL650360</v>
+        <v>MPL650362</v>
       </c>
       <c r="J61" t="str">
-        <v>gel_kudryavii_metod_300ml</v>
+        <v>lifting_maska_pdrn_75ml</v>
       </c>
       <c r="K61" t="str">
-        <v>Гель для укладки волос</v>
+        <v>Маска для лица</v>
       </c>
       <c r="L61" t="str">
         <v>В продаже</v>
@@ -14258,34 +14258,34 @@
         <v>1</v>
       </c>
       <c r="B62" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C62" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E62" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/26/17/58467fe1-4682-493c-b6fe-7d86223be0d2.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/fc/f6/be192d64-456d-4082-892e-58b3852bb6f3.jpg</v>
       </c>
       <c r="F62" t="str">
-        <v>Крем для лица антивозрастной со спикулами и ПДРН</v>
+        <v>Сыворотка для лица, Интенсивное увлажнение</v>
       </c>
       <c r="G62" t="str">
-        <v>4 660 417 421 933</v>
+        <v>4 660 417 422 008</v>
       </c>
       <c r="H62" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I62" t="str">
-        <v>MPL634181</v>
+        <v>MPL650361</v>
       </c>
       <c r="J62" t="str">
-        <v>krem_dlya_lica_pdrn_50 ml</v>
+        <v>syvorotka_dlya_lica_intens_uvl_30ml</v>
       </c>
       <c r="K62" t="str">
-        <v>Крем для лица</v>
+        <v>Сыворотка для лица</v>
       </c>
       <c r="L62" t="str">
         <v>В продаже</v>
@@ -14485,34 +14485,34 @@
         <v>1</v>
       </c>
       <c r="B63" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C63" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E63" t="str">
-        <v>https://seller-media.letu.ru/prod/pim/products/4003/e9/29/0552627e-dd63-4b3c-9bac-d180ba298db2.jpg</v>
+        <v>https://seller-media.letu.ru/prod/pim/products/4003/c2/09/206c885d-46ee-4221-8068-e5e20d1fafba.jpg</v>
       </c>
       <c r="F63" t="str">
-        <v>Термозащитное масло для волос</v>
+        <v>Гель для кудрявых волос</v>
       </c>
       <c r="G63" t="str">
-        <v>4 640 523 970 334</v>
+        <v>4 660 417 422 039</v>
       </c>
       <c r="H63" t="str">
         <v>АЛТЕЯ</v>
       </c>
       <c r="I63" t="str">
-        <v>MPL589445</v>
+        <v>MPL650360</v>
       </c>
       <c r="J63" t="str">
-        <v>termo_maslo_100ml</v>
+        <v>gel_kudryavii_metod_300ml</v>
       </c>
       <c r="K63" t="str">
-        <v>Масло для волос</v>
+        <v>Гель для укладки волос</v>
       </c>
       <c r="L63" t="str">
         <v>В продаже</v>
@@ -14712,13 +14712,13 @@
         <v>1</v>
       </c>
       <c r="B64" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C64" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E64" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/49/ec/4efc7277-a846-43d6-9cf8-8bf4da9c0b43.png</v>
@@ -14939,13 +14939,13 @@
         <v>1</v>
       </c>
       <c r="B65" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C65" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E65" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/7d/8f/6308e0cd-1281-4291-b6a2-e033c0496987.png</v>
@@ -15166,13 +15166,13 @@
         <v>1</v>
       </c>
       <c r="B66" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C66" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E66" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/33/42/29be8dc2-5569-4753-b4ea-fecfc4c1befc.jpg</v>
@@ -15393,13 +15393,13 @@
         <v>1</v>
       </c>
       <c r="B67" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C67" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E67" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/6b/47/4fc77091-eef9-4c17-a375-3e5fddac18ba.png</v>
@@ -15620,13 +15620,13 @@
         <v>1</v>
       </c>
       <c r="B68" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C68" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E68" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/1b/13/4d1d3551-7e04-4a23-83c1-02e6de3d304b.png</v>
@@ -15847,13 +15847,13 @@
         <v>1</v>
       </c>
       <c r="B69" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C69" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E69" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/7a/bc/b90cc621-17b9-4a6b-bbe5-5b96ab70d97b.png</v>
@@ -16074,13 +16074,13 @@
         <v>1</v>
       </c>
       <c r="B70" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C70" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E70" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/bc/66/ce5d0003-e31e-44a0-8886-3bcc7a09c230.png</v>
@@ -16301,13 +16301,13 @@
         <v>1</v>
       </c>
       <c r="B71" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C71" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E71" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/51/92/6fdb97d7-0c18-4cf5-b27b-98c1e58f126b.png</v>
@@ -16528,13 +16528,13 @@
         <v>1</v>
       </c>
       <c r="B72" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C72" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E72" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/36/fd/fef136d7-44af-4d9a-b127-fe9c96f44802.jpg</v>
@@ -16755,13 +16755,13 @@
         <v>1</v>
       </c>
       <c r="B73" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C73" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E73" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/ac/bb/069ebeb7-cacb-480b-a0ae-b9b3f9618e75.png</v>
@@ -16982,13 +16982,13 @@
         <v>1</v>
       </c>
       <c r="B74" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C74" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E74" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/f9/e4/8a36e421-834c-4220-99ab-f5e60d7902e3.png</v>
@@ -17209,13 +17209,13 @@
         <v>1</v>
       </c>
       <c r="B75" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C75" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E75" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/c6/5d/235e7692-36db-4a03-8ad4-3a438f44675e.png</v>
@@ -17436,13 +17436,13 @@
         <v>1</v>
       </c>
       <c r="B76" t="str">
-        <v>2026-07-29</v>
+        <v>2026-07-30</v>
       </c>
       <c r="C76" t="str">
-        <v>2026-07-30</v>
+        <v>2026-07-31</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-07-29-2026-07-29</v>
+        <v>2026-07-30-2026-07-30</v>
       </c>
       <c r="E76" t="str">
         <v>https://seller-media.letu.ru/prod/pim/products/4003/16/28/d514e8ae-6afc-470a-b2e0-4d81ff9eda79.png</v>
@@ -17667,7 +17667,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17713,7 +17713,7 @@
         <v>1</v>
       </c>
       <c r="O1" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="2">
@@ -17730,28 +17730,28 @@
         <v>4670020498208</v>
       </c>
       <c r="E2" t="str">
-        <v>13092</v>
+        <v>9917</v>
       </c>
       <c r="F2" t="str">
         <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>11765</v>
+        <v>9249</v>
       </c>
       <c r="H2" t="str">
-        <v>1327</v>
+        <v>668</v>
       </c>
       <c r="I2" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J2" t="str">
         <v>0</v>
       </c>
       <c r="K2" t="str">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="str">
         <v>0</v>
@@ -17760,39 +17760,39 @@
         <v>1</v>
       </c>
       <c r="O2" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Пенка для укладки волос</v>
+        <v>Продукция косметическая для ухода за кожей, в том числе в наборах: Маска для проблемной кожи лица м</v>
       </c>
       <c r="B3" t="str">
-        <v>99000125266</v>
+        <v>99000114727</v>
       </c>
       <c r="C3" t="str">
-        <v>penka_kudryavii_meto</v>
+        <v>maska_dlya_lica_100m</v>
       </c>
       <c r="D3" t="str">
-        <v>4670020498611</v>
+        <v>4670020498741</v>
       </c>
       <c r="E3" t="str">
-        <v>8000</v>
+        <v>8776</v>
       </c>
       <c r="F3" t="str">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>7250</v>
+        <v>8776</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J3" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="str">
         <v>10</v>
@@ -17807,45 +17807,45 @@
         <v>1</v>
       </c>
       <c r="O3" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Крем для лица с ретинолом 0.5, сыворотка от морщин и пигментных пятен, Алтея, Ретидерм, 50 мл</v>
+        <v>Алтея Сыворотка для лица сыворотка для лица с ниацинамидом для лица антивозрастная, от пигментных пя</v>
       </c>
       <c r="B4" t="str">
-        <v>99000076216</v>
+        <v>99000182844</v>
       </c>
       <c r="C4" t="str">
-        <v>retiderm_50ml</v>
+        <v>syvorotka_dlya_lica_</v>
       </c>
       <c r="D4" t="str">
-        <v>4610172186219</v>
+        <v>4603312714069</v>
       </c>
       <c r="E4" t="str">
-        <v>6153</v>
+        <v>6497</v>
       </c>
       <c r="F4" t="str">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>5902</v>
+        <v>5849</v>
       </c>
       <c r="H4" t="str">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="I4" t="str">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="str">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L4" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="str">
         <v>0</v>
@@ -17854,7 +17854,7 @@
         <v>1</v>
       </c>
       <c r="O4" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="5">
@@ -17871,22 +17871,22 @@
         <v>4660417421605</v>
       </c>
       <c r="E5" t="str">
-        <v>6150</v>
+        <v>6278</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>1025</v>
       </c>
       <c r="G5" t="str">
-        <v>6150</v>
+        <v>5253</v>
       </c>
       <c r="H5" t="str">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="str">
         <v>6</v>
@@ -17901,42 +17901,42 @@
         <v>1</v>
       </c>
       <c r="O5" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Продукция косметическая для ухода за кожей, в том числе в наборах: Маска для проблемной кожи лица м</v>
+        <v>Крем для лица с ретинолом 0.5, сыворотка от морщин и пигментных пятен, Алтея, Ретидерм, 50 мл</v>
       </c>
       <c r="B6" t="str">
-        <v>99000114727</v>
+        <v>99000076216</v>
       </c>
       <c r="C6" t="str">
-        <v>maska_dlya_lica_100m</v>
+        <v>retiderm_50ml</v>
       </c>
       <c r="D6" t="str">
-        <v>4670020498741</v>
+        <v>4610172186219</v>
       </c>
       <c r="E6" t="str">
-        <v>6059</v>
+        <v>4695</v>
       </c>
       <c r="F6" t="str">
         <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>6059</v>
+        <v>4695</v>
       </c>
       <c r="H6" t="str">
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J6" t="str">
         <v>0</v>
       </c>
       <c r="K6" t="str">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="L6" t="str">
         <v>0</v>
@@ -17948,45 +17948,45 @@
         <v>1</v>
       </c>
       <c r="O6" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Крем-шелк для сухой кожи ног</v>
+        <v>Пенка для укладки волос</v>
       </c>
       <c r="B7" t="str">
-        <v>99000076225</v>
+        <v>99000125266</v>
       </c>
       <c r="C7" t="str">
-        <v>kremshelk_100ml</v>
+        <v>penka_kudryavii_meto</v>
       </c>
       <c r="D7" t="str">
-        <v>4670020498437</v>
+        <v>4670020498611</v>
       </c>
       <c r="E7" t="str">
-        <v>5138</v>
+        <v>3735</v>
       </c>
       <c r="F7" t="str">
         <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>4635</v>
+        <v>3735</v>
       </c>
       <c r="H7" t="str">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J7" t="str">
         <v>0</v>
       </c>
       <c r="K7" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L7" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="str">
         <v>0</v>
@@ -17995,7 +17995,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="8">
@@ -18012,28 +18012,28 @@
         <v>4660417420110</v>
       </c>
       <c r="E8" t="str">
-        <v>3884</v>
+        <v>3697</v>
       </c>
       <c r="F8" t="str">
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>3504</v>
+        <v>3697</v>
       </c>
       <c r="H8" t="str">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="I8" t="str">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J8" t="str">
         <v>0</v>
       </c>
       <c r="K8" t="str">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L8" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="str">
         <v>0</v>
@@ -18042,30 +18042,30 @@
         <v>1</v>
       </c>
       <c r="O8" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Крем для волос Упругий завиток, 300 мл</v>
+        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз, 30мл</v>
       </c>
       <c r="B9" t="str">
-        <v>99000114726</v>
+        <v>99000154005</v>
       </c>
       <c r="C9" t="str">
-        <v>curly_method_300ml</v>
+        <v>retinol_boost_krem_d</v>
       </c>
       <c r="D9" t="str">
-        <v>4603320465441</v>
+        <v>4660417421636</v>
       </c>
       <c r="E9" t="str">
-        <v>3590</v>
+        <v>3154</v>
       </c>
       <c r="F9" t="str">
         <v>0</v>
       </c>
       <c r="G9" t="str">
-        <v>3590</v>
+        <v>3154</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
@@ -18089,42 +18089,42 @@
         <v>1</v>
       </c>
       <c r="O9" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз, 30мл</v>
+        <v>РЕТИНАЙТ сыворотка для лица 30 мл</v>
       </c>
       <c r="B10" t="str">
-        <v>99000154005</v>
+        <v>99000125142</v>
       </c>
       <c r="C10" t="str">
-        <v>retinol_boost_krem_d</v>
+        <v>retinait_syvorotka_1</v>
       </c>
       <c r="D10" t="str">
-        <v>4660417421636</v>
+        <v>4603320465403</v>
       </c>
       <c r="E10" t="str">
-        <v>2679</v>
+        <v>3120</v>
       </c>
       <c r="F10" t="str">
         <v>0</v>
       </c>
       <c r="G10" t="str">
-        <v>2679</v>
+        <v>3120</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="str">
         <v>0</v>
       </c>
       <c r="K10" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" t="str">
         <v>0</v>
@@ -18136,42 +18136,42 @@
         <v>1</v>
       </c>
       <c r="O10" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Крем от растяжек, Алтея, 200 мл</v>
+        <v>Крем-шелк для сухой кожи ног</v>
       </c>
       <c r="B11" t="str">
-        <v>99000114731</v>
+        <v>99000076225</v>
       </c>
       <c r="C11" t="str">
-        <v>krem_ot_rastyazhek</v>
+        <v>kremshelk_100ml</v>
       </c>
       <c r="D11" t="str">
-        <v>4670020497898</v>
+        <v>4670020498437</v>
       </c>
       <c r="E11" t="str">
-        <v>2484</v>
+        <v>2924</v>
       </c>
       <c r="F11" t="str">
         <v>0</v>
       </c>
       <c r="G11" t="str">
-        <v>2484</v>
+        <v>2924</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J11" t="str">
         <v>0</v>
       </c>
       <c r="K11" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L11" t="str">
         <v>0</v>
@@ -18183,7 +18183,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="12">
@@ -18200,25 +18200,25 @@
         <v>4603320465359</v>
       </c>
       <c r="E12" t="str">
-        <v>2260</v>
+        <v>2782</v>
       </c>
       <c r="F12" t="str">
         <v>0</v>
       </c>
       <c r="G12" t="str">
-        <v>2260</v>
+        <v>2782</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12" t="str">
         <v>0</v>
       </c>
       <c r="K12" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L12" t="str">
         <v>0</v>
@@ -18230,42 +18230,42 @@
         <v>1</v>
       </c>
       <c r="O12" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Крем специального назначения «Псоридонт» 50 мл</v>
+        <v>Средство косметическое: Воск для волос торговой марки: «Алтея» 15гр</v>
       </c>
       <c r="B13" t="str">
-        <v>99000125141</v>
+        <v>99000131672</v>
       </c>
       <c r="C13" t="str">
-        <v>psoral_50ml</v>
+        <v>vosk_stik_15ml</v>
       </c>
       <c r="D13" t="str">
-        <v>4660417421087</v>
+        <v>4670207150196</v>
       </c>
       <c r="E13" t="str">
-        <v>1520</v>
+        <v>2465</v>
       </c>
       <c r="F13" t="str">
         <v>0</v>
       </c>
       <c r="G13" t="str">
-        <v>1520</v>
+        <v>2465</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13" t="str">
         <v>0</v>
       </c>
       <c r="K13" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L13" t="str">
         <v>0</v>
@@ -18277,42 +18277,42 @@
         <v>1</v>
       </c>
       <c r="O13" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Средство косметическое: Воск для волос торговой марки: «Алтея» 15гр</v>
+        <v>Лосьон для волос бальзам для кудрявых волос, 500 мл</v>
       </c>
       <c r="B14" t="str">
-        <v>99000131672</v>
+        <v>99000177794</v>
       </c>
       <c r="C14" t="str">
-        <v>vosk_stik_15ml</v>
+        <v>balzam_kudryavii_met</v>
       </c>
       <c r="D14" t="str">
-        <v>4670207150196</v>
+        <v>4640523970327</v>
       </c>
       <c r="E14" t="str">
-        <v>1395</v>
+        <v>2256</v>
       </c>
       <c r="F14" t="str">
         <v>0</v>
       </c>
       <c r="G14" t="str">
-        <v>1395</v>
+        <v>2256</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
       </c>
       <c r="I14" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="str">
         <v>0</v>
       </c>
       <c r="K14" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" t="str">
         <v>0</v>
@@ -18324,42 +18324,42 @@
         <v>1</v>
       </c>
       <c r="O14" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Алтея Сыворотка для лица сыворотка для лица с ниацинамидом для лица антивозрастная, от пигментных пя</v>
+        <v>Крем от растяжек, Алтея, 200 мл</v>
       </c>
       <c r="B15" t="str">
-        <v>99000182844</v>
+        <v>99000114731</v>
       </c>
       <c r="C15" t="str">
-        <v>syvorotka_dlya_lica_</v>
+        <v>krem_ot_rastyazhek</v>
       </c>
       <c r="D15" t="str">
-        <v>4603312714069</v>
+        <v>4670020497898</v>
       </c>
       <c r="E15" t="str">
-        <v>1280</v>
+        <v>2165</v>
       </c>
       <c r="F15" t="str">
         <v>0</v>
       </c>
       <c r="G15" t="str">
-        <v>1280</v>
+        <v>2165</v>
       </c>
       <c r="H15" t="str">
         <v>0</v>
       </c>
       <c r="I15" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="str">
         <v>0</v>
       </c>
       <c r="K15" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" t="str">
         <v>0</v>
@@ -18371,42 +18371,42 @@
         <v>1</v>
       </c>
       <c r="O15" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Лосьон для волос бальзам для кудрявых волос, 500 мл</v>
+        <v>Продукция косметическая для ухода за кожей для взрослых: гелевая маска со спикулами торговой марки А</v>
       </c>
       <c r="B16" t="str">
-        <v>99000177794</v>
+        <v>99000177799</v>
       </c>
       <c r="C16" t="str">
-        <v>balzam_kudryavii_met</v>
+        <v>spicul_gel_mask_75ml</v>
       </c>
       <c r="D16" t="str">
-        <v>4640523970327</v>
+        <v>4660417421858</v>
       </c>
       <c r="E16" t="str">
-        <v>1263</v>
+        <v>1993</v>
       </c>
       <c r="F16" t="str">
         <v>0</v>
       </c>
       <c r="G16" t="str">
-        <v>1263</v>
+        <v>1993</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
       </c>
       <c r="I16" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="str">
         <v>0</v>
       </c>
       <c r="K16" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" t="str">
         <v>0</v>
@@ -18418,42 +18418,42 @@
         <v>1</v>
       </c>
       <c r="O16" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Cыворотка SPICULBOOST торговой марки Алтея, 30 мл</v>
+        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея, 50 мл</v>
       </c>
       <c r="B17" t="str">
-        <v>99000179436</v>
+        <v>99000176496</v>
       </c>
       <c r="C17" t="str">
-        <v>spiculboost_30ml</v>
+        <v>retinait_krem_1_5_50</v>
       </c>
       <c r="D17" t="str">
-        <v>4630446231421</v>
+        <v>4660417421827</v>
       </c>
       <c r="E17" t="str">
-        <v>897</v>
+        <v>1782</v>
       </c>
       <c r="F17" t="str">
         <v>0</v>
       </c>
       <c r="G17" t="str">
-        <v>897</v>
+        <v>1782</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
       </c>
       <c r="I17" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="str">
         <v>0</v>
       </c>
       <c r="K17" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="str">
         <v>0</v>
@@ -18465,42 +18465,42 @@
         <v>1</v>
       </c>
       <c r="O17" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Продукция косметическая для ухода за кожей для взрослых: гелевая маска со спикулами торговой марки А</v>
+        <v>Шампунь для роста волос, от выпадения волос профессиональный, Алтея, 250 мл</v>
       </c>
       <c r="B18" t="str">
-        <v>99000177799</v>
+        <v>99000076213</v>
       </c>
       <c r="C18" t="str">
-        <v>spicul_gel_mask_75ml</v>
+        <v>shampun_dlya_rosta_2</v>
       </c>
       <c r="D18" t="str">
-        <v>4660417421858</v>
+        <v>4670020496747</v>
       </c>
       <c r="E18" t="str">
-        <v>847</v>
+        <v>1638</v>
       </c>
       <c r="F18" t="str">
         <v>0</v>
       </c>
       <c r="G18" t="str">
-        <v>847</v>
+        <v>1638</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
       </c>
       <c r="I18" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J18" t="str">
         <v>0</v>
       </c>
       <c r="K18" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="str">
         <v>0</v>
@@ -18512,30 +18512,30 @@
         <v>1</v>
       </c>
       <c r="O18" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Крем с липомосомальным ретинолом (0,1% - 3%), торговая марка Алтея</v>
+        <v>Крем для лица с ПДРН (PDRN) и спикулами, 50 мл</v>
       </c>
       <c r="B19" t="str">
-        <v>99000124418</v>
+        <v>99000184675</v>
       </c>
       <c r="C19" t="str">
-        <v>retinait_krem_025_50</v>
+        <v>krem_dlya_lica_pdrn_</v>
       </c>
       <c r="D19" t="str">
-        <v>4660417421599</v>
+        <v>4660417421933</v>
       </c>
       <c r="E19" t="str">
-        <v>844</v>
+        <v>1599</v>
       </c>
       <c r="F19" t="str">
         <v>0</v>
       </c>
       <c r="G19" t="str">
-        <v>844</v>
+        <v>1599</v>
       </c>
       <c r="H19" t="str">
         <v>0</v>
@@ -18559,42 +18559,42 @@
         <v>1</v>
       </c>
       <c r="O19" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Ретинайт 0,5 экспресс-омоложение Anti-Age Липосомальный комплекс ретинола 0,5 + Ниацинамид 50 мл</v>
+        <v>Шампунь для кудрявых волос торговой марки Алтея, 500 мл</v>
       </c>
       <c r="B20" t="str">
-        <v>99000131675</v>
+        <v>99000179424</v>
       </c>
       <c r="C20" t="str">
-        <v>retinait_krem_05_50m</v>
+        <v>shampun_kudryavii_me</v>
       </c>
       <c r="D20" t="str">
-        <v>4660417421759</v>
+        <v>4640523970310</v>
       </c>
       <c r="E20" t="str">
-        <v>744</v>
+        <v>1536</v>
       </c>
       <c r="F20" t="str">
         <v>0</v>
       </c>
       <c r="G20" t="str">
-        <v>744</v>
+        <v>1536</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
       </c>
       <c r="I20" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="str">
         <v>0</v>
       </c>
       <c r="K20" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="str">
         <v>0</v>
@@ -18606,30 +18606,30 @@
         <v>1</v>
       </c>
       <c r="O20" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Гель для бровей с коллагеном и эластином, фиксация на 24 часа, Алтея, 5 мл</v>
+        <v>Спрей-сыворотка для волос маркировки Алтея</v>
       </c>
       <c r="B21" t="str">
-        <v>99000114725</v>
+        <v>99000076226</v>
       </c>
       <c r="C21" t="str">
-        <v>gel_brows_5ml</v>
+        <v>termo_sprei_200ml</v>
       </c>
       <c r="D21" t="str">
-        <v>4676574657436</v>
+        <v>4670020497980</v>
       </c>
       <c r="E21" t="str">
-        <v>660</v>
+        <v>916</v>
       </c>
       <c r="F21" t="str">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="G21" t="str">
-        <v>660</v>
+        <v>445</v>
       </c>
       <c r="H21" t="str">
         <v>0</v>
@@ -18638,10 +18638,10 @@
         <v>2</v>
       </c>
       <c r="J21" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" t="str">
         <v>0</v>
@@ -18653,30 +18653,30 @@
         <v>1</v>
       </c>
       <c r="O21" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Спрей-сыворотка для волос маркировки Алтея</v>
+        <v>Крем для волос Упругий завиток, 300 мл</v>
       </c>
       <c r="B22" t="str">
-        <v>99000076226</v>
+        <v>99000114726</v>
       </c>
       <c r="C22" t="str">
-        <v>termo_sprei_200ml</v>
+        <v>curly_method_300ml</v>
       </c>
       <c r="D22" t="str">
-        <v>4670020497980</v>
+        <v>4603320465441</v>
       </c>
       <c r="E22" t="str">
-        <v>472</v>
+        <v>892</v>
       </c>
       <c r="F22" t="str">
         <v>0</v>
       </c>
       <c r="G22" t="str">
-        <v>472</v>
+        <v>892</v>
       </c>
       <c r="H22" t="str">
         <v>0</v>
@@ -18700,7 +18700,7 @@
         <v>1</v>
       </c>
       <c r="O22" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
       </c>
     </row>
     <row r="23">
@@ -18717,25 +18717,25 @@
         <v>4660417421452</v>
       </c>
       <c r="E23" t="str">
-        <v>371</v>
+        <v>776</v>
       </c>
       <c r="F23" t="str">
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>371</v>
+        <v>776</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
       </c>
       <c r="I23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="str">
         <v>0</v>
       </c>
       <c r="K23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" t="str">
         <v>0</v>
@@ -18747,19 +18747,160 @@
         <v>1</v>
       </c>
       <c r="O23" t="str">
-        <v>29.7.2026</v>
+        <v>30.7.2026</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Гель для бровей с коллагеном и эластином, фиксация на 24 часа, Алтея, 5 мл</v>
+      </c>
+      <c r="B24" t="str">
+        <v>99000114725</v>
+      </c>
+      <c r="C24" t="str">
+        <v>gel_brows_5ml</v>
+      </c>
+      <c r="D24" t="str">
+        <v>4676574657436</v>
+      </c>
+      <c r="E24" t="str">
+        <v>765</v>
+      </c>
+      <c r="F24" t="str">
+        <v>0</v>
+      </c>
+      <c r="G24" t="str">
+        <v>765</v>
+      </c>
+      <c r="H24" t="str">
+        <v>0</v>
+      </c>
+      <c r="I24" t="str">
+        <v>2</v>
+      </c>
+      <c r="J24" t="str">
+        <v>0</v>
+      </c>
+      <c r="K24" t="str">
+        <v>2</v>
+      </c>
+      <c r="L24" t="str">
+        <v>0</v>
+      </c>
+      <c r="M24" t="str">
+        <v>0</v>
+      </c>
+      <c r="N24" t="str">
+        <v>1</v>
+      </c>
+      <c r="O24" t="str">
+        <v>30.7.2026</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Средство косметическое для ухода за волосами: маска для волос восстанавливающая с авокадо и маслом о</v>
+      </c>
+      <c r="B25" t="str">
+        <v>99000076210</v>
+      </c>
+      <c r="C25" t="str">
+        <v>maska-batter_250ml</v>
+      </c>
+      <c r="D25" t="str">
+        <v>4670020497546</v>
+      </c>
+      <c r="E25" t="str">
+        <v>688</v>
+      </c>
+      <c r="F25" t="str">
+        <v>0</v>
+      </c>
+      <c r="G25" t="str">
+        <v>688</v>
+      </c>
+      <c r="H25" t="str">
+        <v>0</v>
+      </c>
+      <c r="I25" t="str">
+        <v>1</v>
+      </c>
+      <c r="J25" t="str">
+        <v>0</v>
+      </c>
+      <c r="K25" t="str">
+        <v>1</v>
+      </c>
+      <c r="L25" t="str">
+        <v>0</v>
+      </c>
+      <c r="M25" t="str">
+        <v>0</v>
+      </c>
+      <c r="N25" t="str">
+        <v>1</v>
+      </c>
+      <c r="O25" t="str">
+        <v>30.7.2026</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Продукция косметическая для ухода за кожей: Пилинг для кожи головы.</v>
+      </c>
+      <c r="B26" t="str">
+        <v>99000076204</v>
+      </c>
+      <c r="C26" t="str">
+        <v>piling_100ml</v>
+      </c>
+      <c r="D26" t="str">
+        <v>4670020496761</v>
+      </c>
+      <c r="E26" t="str">
+        <v>488</v>
+      </c>
+      <c r="F26" t="str">
+        <v>0</v>
+      </c>
+      <c r="G26" t="str">
+        <v>488</v>
+      </c>
+      <c r="H26" t="str">
+        <v>0</v>
+      </c>
+      <c r="I26" t="str">
+        <v>1</v>
+      </c>
+      <c r="J26" t="str">
+        <v>0</v>
+      </c>
+      <c r="K26" t="str">
+        <v>1</v>
+      </c>
+      <c r="L26" t="str">
+        <v>0</v>
+      </c>
+      <c r="M26" t="str">
+        <v>0</v>
+      </c>
+      <c r="N26" t="str">
+        <v>1</v>
+      </c>
+      <c r="O26" t="str">
+        <v>30.7.2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O26"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -18793,7 +18934,7 @@
         <v>1</v>
       </c>
       <c r="K1" t="str">
-        <v>29.07.2026</v>
+        <v>30.07.2026</v>
       </c>
     </row>
     <row r="2">
@@ -18828,15 +18969,15 @@
         <v>1</v>
       </c>
       <c r="K2" t="str">
-        <v>29.07.2026</v>
+        <v>30.07.2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>АЛТЕЯ-PSORAL5</v>
+        <v>АЛТЕЯ-RTBOOST</v>
       </c>
       <c r="B3" t="str">
-        <v>Мазь от псориаза и дерматита крем от зуда Алтея Псорал 50 мл</v>
+        <v>Крем c ретинолом для век антивозрастной для кожи и кожи вокруг глаз Алтея 30 мл</v>
       </c>
       <c r="C3" t="str">
         <v>2</v>
@@ -18845,68 +18986,68 @@
         <v>0</v>
       </c>
       <c r="E3" t="str">
-        <v>782</v>
+        <v>1513,6</v>
       </c>
       <c r="F3" t="str">
-        <v>262,84</v>
+        <v>294,72</v>
       </c>
       <c r="G3" t="str">
-        <v>508,3</v>
+        <v>983,84</v>
       </c>
       <c r="H3" t="str">
-        <v>273,7</v>
+        <v>529,76</v>
       </c>
       <c r="I3" t="str">
-        <v>psoral_50ml</v>
+        <v>retinol_boost_krem_dlya_vek_30ml</v>
       </c>
       <c r="J3" t="str">
         <v>1</v>
       </c>
       <c r="K3" t="str">
-        <v>29.07.2026</v>
+        <v>30.07.2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>АЛТЕЯ-GELDLBR</v>
+        <v>АЛТЕЯ-RETINKR</v>
       </c>
       <c r="B4" t="str">
-        <v>Гель для бритья мужской охлаждающий с ментолом Алтея 300 мл</v>
+        <v>Крем для лица с липосомальным ретинолом 1% Ретинайт</v>
       </c>
       <c r="C4" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="str">
         <v>0</v>
       </c>
       <c r="E4" t="str">
-        <v>529,25</v>
+        <v>1648,1</v>
       </c>
       <c r="F4" t="str">
-        <v>125,68</v>
+        <v>198,8</v>
       </c>
       <c r="G4" t="str">
-        <v>381,06</v>
+        <v>1186,64</v>
       </c>
       <c r="H4" t="str">
-        <v>148,19</v>
+        <v>461,46</v>
       </c>
       <c r="I4" t="str">
-        <v>gel_dlya_britya_300ml</v>
+        <v>retinait_krem_1_50ml</v>
       </c>
       <c r="J4" t="str">
         <v>1</v>
       </c>
       <c r="K4" t="str">
-        <v>29.07.2026</v>
+        <v>30.07.2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>АЛТЕЯ-PENKAKD</v>
+        <v>АЛТЕЯ-RETINT1</v>
       </c>
       <c r="B5" t="str">
-        <v>Пенка для укладки кудрявых волос Алтея 150 мл</v>
+        <v>Сыворотка с ретинолом 1% для лица от морщин антивозрастная Алтея 30 мл</v>
       </c>
       <c r="C5" t="str">
         <v>1</v>
@@ -18915,33 +19056,33 @@
         <v>0</v>
       </c>
       <c r="E5" t="str">
-        <v>527,45</v>
+        <v>660</v>
       </c>
       <c r="F5" t="str">
-        <v>137,7</v>
+        <v>143,82</v>
       </c>
       <c r="G5" t="str">
-        <v>379,76</v>
+        <v>429</v>
       </c>
       <c r="H5" t="str">
-        <v>147,69</v>
+        <v>231</v>
       </c>
       <c r="I5" t="str">
-        <v>penka_kudryavii_metod_150ml</v>
+        <v>retinait_syvorotka_1_30ml</v>
       </c>
       <c r="J5" t="str">
         <v>1</v>
       </c>
       <c r="K5" t="str">
-        <v>29.07.2026</v>
+        <v>30.07.2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>АЛТЕЯ-RETIDER</v>
+        <v>АЛТЕЯ-KREMBUS</v>
       </c>
       <c r="B6" t="str">
-        <v>Крем для лица с ретинолом 0.5 антивозрастной от морщин Алтея Ретидерм 50 мл</v>
+        <v>Антицеллюлитный крем для тела Алтея 250 мл</v>
       </c>
       <c r="C6" t="str">
         <v>1</v>
@@ -18950,33 +19091,33 @@
         <v>0</v>
       </c>
       <c r="E6" t="str">
-        <v>249,45</v>
+        <v>403,05</v>
       </c>
       <c r="F6" t="str">
-        <v>91,54</v>
+        <v>127,95</v>
       </c>
       <c r="G6" t="str">
-        <v>179,6</v>
+        <v>290,2</v>
       </c>
       <c r="H6" t="str">
-        <v>69,85</v>
+        <v>112,85</v>
       </c>
       <c r="I6" t="str">
-        <v>retiderm_50ml</v>
+        <v>krem_buster_250ml</v>
       </c>
       <c r="J6" t="str">
         <v>1</v>
       </c>
       <c r="K6" t="str">
-        <v>29.07.2026</v>
+        <v>30.07.2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>АЛТЕЯ-SHPPERH</v>
+        <v>АЛТЕЯ-PENKAKD</v>
       </c>
       <c r="B7" t="str">
-        <v>Шампунь от перхоти лечебный с климбазолом Алтея 250 мл</v>
+        <v>Пенка для укладки кудрявых волос Алтея 150 мл</v>
       </c>
       <c r="C7" t="str">
         <v>1</v>
@@ -18985,30 +19126,205 @@
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>388,45</v>
+        <v>527,45</v>
       </c>
       <c r="F7" t="str">
-        <v>106,2</v>
+        <v>137,7</v>
       </c>
       <c r="G7" t="str">
-        <v>279,68</v>
+        <v>379,76</v>
       </c>
       <c r="H7" t="str">
-        <v>108,77</v>
+        <v>147,69</v>
       </c>
       <c r="I7" t="str">
-        <v>shampun_protiv_perhoti_250ml</v>
+        <v>penka_kudryavii_metod_150ml</v>
       </c>
       <c r="J7" t="str">
         <v>1</v>
       </c>
       <c r="K7" t="str">
-        <v>29.07.2026</v>
+        <v>30.07.2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>АЛТЕЯ-MASKARS</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Маска для роста волос с перцем Алтея 500 мл</v>
+      </c>
+      <c r="C8" t="str">
+        <v>1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>0</v>
+      </c>
+      <c r="E8" t="str">
+        <v>384</v>
+      </c>
+      <c r="F8" t="str">
+        <v>136,15</v>
+      </c>
+      <c r="G8" t="str">
+        <v>291,84</v>
+      </c>
+      <c r="H8" t="str">
+        <v>92,16</v>
+      </c>
+      <c r="I8" t="str">
+        <v>maska-batter_dlya_rosta_500ml</v>
+      </c>
+      <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>30.07.2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>АЛТЕЯ-PENKARS</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Пенка для нарощенных ресниц и для бровей для умывания и очищения ресниц Алтея 150 мл</v>
+      </c>
+      <c r="C9" t="str">
+        <v>1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>0</v>
+      </c>
+      <c r="E9" t="str">
+        <v>433,1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>90,65</v>
+      </c>
+      <c r="G9" t="str">
+        <v>281,52</v>
+      </c>
+      <c r="H9" t="str">
+        <v>151,58</v>
+      </c>
+      <c r="I9" t="str">
+        <v>nabor_penka_dlya_resnic</v>
+      </c>
+      <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>30.07.2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>АЛТЕЯ-KREMRST</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Крем масло от растяжек для беременных и подростков с эластином Алтея 200 мл</v>
+      </c>
+      <c r="C10" t="str">
+        <v>1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>0</v>
+      </c>
+      <c r="E10" t="str">
+        <v>355</v>
+      </c>
+      <c r="F10" t="str">
+        <v>151,2</v>
+      </c>
+      <c r="G10" t="str">
+        <v>255,6</v>
+      </c>
+      <c r="H10" t="str">
+        <v>99,4</v>
+      </c>
+      <c r="I10" t="str">
+        <v>krem_ot_rastyazhek</v>
+      </c>
+      <c r="J10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>30.07.2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>АЛТЕЯ-SYVTL30</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Сыворотка для лица с ниацинамидом антивозрастная от акне пигментации Алтея 30 мл</v>
+      </c>
+      <c r="C11" t="str">
+        <v>1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>0</v>
+      </c>
+      <c r="E11" t="str">
+        <v>577,05</v>
+      </c>
+      <c r="F11" t="str">
+        <v>148,9</v>
+      </c>
+      <c r="G11" t="str">
+        <v>375,08</v>
+      </c>
+      <c r="H11" t="str">
+        <v>201,97</v>
+      </c>
+      <c r="I11" t="str">
+        <v>syvorotka_dlya_lica_30ml</v>
+      </c>
+      <c r="J11" t="str">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
+        <v>30.07.2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>АЛТЕЯ-RETIDER</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Крем для лица с ретинолом 0.5 антивозрастной от морщин Алтея Ретидерм 50 мл</v>
+      </c>
+      <c r="C12" t="str">
+        <v>6</v>
+      </c>
+      <c r="D12" t="str">
+        <v>0</v>
+      </c>
+      <c r="E12" t="str">
+        <v>1496,7</v>
+      </c>
+      <c r="F12" t="str">
+        <v>549,24</v>
+      </c>
+      <c r="G12" t="str">
+        <v>1077,62</v>
+      </c>
+      <c r="H12" t="str">
+        <v>419,08</v>
+      </c>
+      <c r="I12" t="str">
+        <v>retiderm_50ml</v>
+      </c>
+      <c r="J12" t="str">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
+        <v>30.07.2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
   </ignoredErrors>
 </worksheet>
 </file>